--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint plan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hiring" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Future" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sprint plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Hiring" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Backlog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Architecture" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Future" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$76</definedName>
@@ -874,7 +874,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>DATOMS API docs</t>
+          <t>DATOMS sample bulk response + bulk field list (Q21, Q22)</t>
         </is>
       </c>
       <c r="F4" s="19">
@@ -929,7 +929,7 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>DATOMS API docs + key</t>
+          <t>DATOMS sample + field list (Q21, Q22) + key</t>
         </is>
       </c>
       <c r="F5" s="19">
@@ -984,7 +984,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>Asset location + status in API</t>
+          <t>Bulk field names for location + status (Q22)</t>
         </is>
       </c>
       <c r="F6" s="19">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>Site totals in API</t>
+          <t>Whether DATOMS has site totals and ownership (Q3); field names (Q22)</t>
         </is>
       </c>
       <c r="F7" s="19">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>Notifications in API</t>
+          <t>Alert field names in the bulk response (Q22)</t>
         </is>
       </c>
       <c r="F8" s="19">
@@ -1381,6 +1381,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="14">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -2090,21 +2091,21 @@
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>Entra ID app registrations (API + web app), app roles, Nexus security groups</t>
+          <t>Entra ID app registrations (API + web app), Nexus security groups, app-assigned groups claim</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
           <t>1. In Entra ID, register two apps: 'Nexus API' and 'Nexus Web'.
-2. On Nexus API, define app roles: Admin, Leadership, ProjectDirector, ProjectManager, HSE, Plant, Procurement.
-3. Create security groups (e.g. Nexus-Admins) and assign them to the roles.
+2. Create the Nexus security groups (docs/08 section 1; e.g. Nexus-Admins). Roles are mapped from groups in the Nexus database (docs/08 section 3), not defined as Entra app roles. The final role list is Q17.
+3. On Nexus API, set the groups claim to 'Groups assigned to the application' (ADR 0008). Assign the Nexus groups to the enterprise app; users must be direct members. No Graph permission or secret.
 4. Turn on 'assignment required' so only group members can sign in.
 5. Share client IDs with the frontend.</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>Sign-in apps and roles ready; test users in each group</t>
+          <t>Sign-in apps and groups ready; test users in each group</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -2125,7 +2126,7 @@
       <c r="K5" s="19" t="n"/>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>Entra admin consent</t>
+          <t>Entra admin consent; Entra ID P1 licence and setup confirmed by Innovo IT (Q16)</t>
         </is>
       </c>
       <c r="M5" s="19" t="n">
@@ -2138,7 +2139,7 @@
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t>Test users in each group can get a token with the right role</t>
+          <t>Test users in each group get a token whose groups claim contains only their app-assigned Nexus group(s)</t>
         </is>
       </c>
     </row>
@@ -3183,16 +3184,16 @@
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>DATOMS API client: auth, paging, retries, rate-limit handling</t>
+          <t>DATOMS API client: bulk endpoint, paging, retries, rate-limit and credit handling</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>1. Read the DATOMS API docs (once received).
-2. Build a DATOMS client module: login/token, list sites, list devices, get values.
-3. Handle paging, retries and rate limits.
-4. Test against GHAFWOODS on dev.
-If docs are not here yet: build with a mock and swap later.</t>
+          <t>1. Read the v4 PDF, plus the DATOMS sample bulk response (Q21) and bulk field list (Q22) once received.
+2. Build packages/datoms-client: list assets (catalogue) and the bulk endpoint (fleet and id mode) as the ONLY telemetry source (ADR 0010). data/latest is for CLI checks only.
+3. Put ALL field mapping in src/mapping.ts. Until the sample arrives, build against the v4 PDF shape. Save the sample to fixtures/ with tokens removed.
+4. Handle paging, 422 halving (with the learned page size), retries, rate limits, and the credit budget with budget.max_share (ADR 0005).
+5. Test against GHAFWOODS on dev using fixtures or a small id-mode subset (never the full fleet from dev).</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
@@ -3218,7 +3219,7 @@
       <c r="K20" s="19" t="n"/>
       <c r="L20" s="19" t="inlineStr">
         <is>
-          <t>DATOMS API docs + read-only key</t>
+          <t>DATOMS sample bulk response (Q21) + bulk field list (Q22) + read-only key. Needed before this task starts; they do not block S0 or S1.</t>
         </is>
       </c>
       <c r="M20" s="19" t="n">
@@ -3231,7 +3232,7 @@
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>Client reads GHAFWOODS sites and devices in dev</t>
+          <t>Client reads the GHAFWOODS demo fleet (generators and tower cranes) through the bulk endpoint in dev; DATOMS field names exist only in src/mapping.ts</t>
         </is>
       </c>
     </row>
@@ -3557,9 +3558,10 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>1. Scheduled job in apps/worker, every hour.
-2. Read all DATOMS sites, devices and parameters (name, unit).
-3. Insert new ones, update changed ones in the database.</t>
+          <t>1. Scheduled job in apps/worker, every hour (and early when the poll sees unknown ids).
+2. Read all DATOMS assets (list assets: names, nameplate). Sites, asset types and parameters (name, unit) come in the bulk rows. The live poll (S3-03) upserts them the same way, so the catalogue job spends no bulk credits.
+3. Insert new ones, update changed ones in the database.
+4. Retire safely (docs/07 section 6): only after a complete walk; only rows missed in 2 consecutive complete walks; retire nothing and alert if more than 5% would go.</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -3589,7 +3591,7 @@
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
-          <t>DATOMS API docs + read-only key</t>
+          <t>DATOMS sample + field list (Q21, Q22) + read-only key; id stability (Q11)</t>
         </is>
       </c>
       <c r="M25" s="19" t="n">
@@ -3702,20 +3704,20 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>Live sync (every minute): latest values and statuses to readings + latest value table</t>
+          <t>Live sync (every minute by default): bulk endpoint → packets, latest values, statuses, locations, alerts</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>1. Job every minute: get latest values and statuses for all devices.
-2. Write them to 'reading' (history) and 'latest_value' (current).
-3. Insert in batches.
-4. Log how long each run takes.</t>
+          <t>1. Job every 60 s by default (per-type interval, ADR 0006): bulk endpoint only (ADR 0010). Fleet mode when every asset is due, otherwise id mode. In dev, only the configured subset (ADR 0005).
+2. Write telemetry.packet (history) and telemetry.latest_packet (current); status, location and alerts on change only.
+3. Insert in batches. No per-poll bookkeeping writes (asset_parameter is insert-only; status observed_at only on change).
+4. Log how long each run takes and the credits used per window.</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>Live DATOMS data in Nexus within 60 seconds</t>
+          <t>Live DATOMS data in Nexus within about 2 poll intervals</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
@@ -3749,7 +3751,7 @@
       </c>
       <c r="O27" s="19" t="inlineStr">
         <is>
-          <t>Value in Nexus within 60 s of DATOMS</t>
+          <t>Value in Nexus within 2 poll intervals of DATOMS (N-03)</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3778,7 @@
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>History backfill and gap repair after outages</t>
+          <t>History backfill and gap repair after outages (ON HOLD)</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -3812,13 +3814,17 @@
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L28" s="19" t="n"/>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>ON HOLD (decided 2026-10-08). The bulk endpoint has no history (ADR 0010); Nexus builds its own history from polls from day one. Needs a DATOMS history feed (Q12) and a new ADR to use it. Until then, gaps stay gaps and charts show coverage (ADR 0007).</t>
+        </is>
+      </c>
       <c r="M28" s="19" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="25" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -4073,8 +4079,9 @@
       <c r="F32" s="19" t="inlineStr">
         <is>
           <t>1. Use the rollup functions in db/schema.sql: telemetry.refresh_rollup_5m and refresh_rollup_combine (1 h, 1 day in Asia/Dubai).
-2. Worker rollups job runs every minute for the recent window and re-runs for late data.
-3. Check a 30-day query returns in under 1 second.</t>
+2. Worker rollups job (ADR 0007): refresh_rollup_5m once per CLOSED 5-minute bucket, 2 poll intervals after it ends; re-run only for closed buckets that get late packets; 1 h after the hour's last bucket; 1 d after the Dubai day. No sliding window, no in-memory accumulators.
+3. Return data coverage (packets / expectedPackets) with each bucket.
+4. Check a 30-day query returns in under 1 second.</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
@@ -4145,8 +4152,9 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>1. When the worker sees a status or value change, publish a message to Azure Web PubSub (per project channel).
-2. API gives the browser a Web PubSub token for only the projects it may see.</t>
+          <t>1. When the worker sees a status or location change, publish a slim message to Azure Web PubSub (per project group): no parameter values; values.updated hint; summary.updated; chunked well under 1 MB (docs/10, ADR 0008).
+2. API gives the browser a Web PubSub token with no group-join rights. POST /v1/live/subscriptions checks permission and scope, then joins the connection to project groups on the server.
+3. On any Nexus access change, close the affected live connections so clients re-subscribe through the scope check. Settle with the security-reviewer how the API confirms a connectionId belongs to the caller.</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -4185,7 +4193,7 @@
       </c>
       <c r="O33" s="19" t="inlineStr">
         <is>
-          <t>Pin colour changes without refresh</t>
+          <t>Pin colour changes without refresh; a user whose project access is removed stops receiving that project's messages at once; nothing project-specific is sent to the portfolio group</t>
         </is>
       </c>
     </row>
@@ -4212,18 +4220,18 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>Project summary API for the equipment and energy info boxes</t>
+          <t>Project summary APIs for the equipment and energy info boxes</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>1. Endpoint GET /projects/{id}/summary returning the equipment and energy info boxes.
-2. Fill them from latest DATOMS values. Manpower and materials are added later once their source is known.</t>
+          <t>1. Endpoints GET /projects/{id}/equipment/summary (Box 2) and GET /projects/{id}/energy/summary (Box 3), as in docs/10.
+2. Fill them from the latest DATOMS values: equipment counts from kind = 'physical' assets; energy site totals from site_metric records when DATOMS provides them. Manpower and materials are not built (slots only).</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>One call loads the project page</t>
+          <t>The project page loads its boxes</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
@@ -4257,7 +4265,7 @@
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
-          <t>One call returns all four boxes</t>
+          <t>The two endpoints return Box 2 and Box 3 as reported; Boxes 1 and 4 are "coming later" slots</t>
         </is>
       </c>
     </row>
@@ -4362,10 +4370,10 @@
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>1. Draw one pin per asset at its DATOMS location.
-2. Icon by type: tower crane, hoist, equipment, generator.
+          <t>1. Draw one pin per equipment asset (kind = 'physical') at its DATOMS location; no location = "Not on map".
+2. Icon by type: tower crane, hoist, equipment, generator; unknown types use the generic icon.
 3. Colour by DATOMS status: Running green, Idle amber, Maintenance red, Off grey.
-4. Turn on clustering and a Map/Satellite switch.</t>
+4. Turn on clustering and a Map/Satellite switch. 3D uses the same icons with no callouts or pulse (ADR 0008).</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">
@@ -4395,7 +4403,7 @@
       </c>
       <c r="L36" s="19" t="inlineStr">
         <is>
-          <t>DATOMS: does API return location + status?</t>
+          <t>Bulk field names for location + status (Q22; DATOMS confirmed the data is in the bulk response); blink vs pulse (Q19)</t>
         </is>
       </c>
       <c r="M36" s="19" t="n">
@@ -4584,7 +4592,7 @@
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>1. Endpoint returning per project: generators (running/total), solar generation, mains, total load, loads by area, site totals and CO2 exactly as DATOMS gives them.
+          <t>1. Endpoint returning per project: generators (running/total), solar generation, mains, total load, loads by area, site totals and CO2 exactly as DATOMS gives them in the bulk response. Site totals are read from site_metric records (ADR 0009); anything missing shows "no data yet".
 2. Compare with the DATOMS Site View for GHAFWOODS; numbers must match.</t>
         </is>
       </c>
@@ -4615,7 +4623,7 @@
       </c>
       <c r="L39" s="19" t="inlineStr">
         <is>
-          <t>DATOMS: are site totals in the API?</t>
+          <t>Whether DATOMS has site totals (Q3); bulk field names (Q22)</t>
         </is>
       </c>
       <c r="M39" s="19" t="n">
@@ -4661,7 +4669,7 @@
       <c r="F40" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing energy equipment: DG ID, description, type (DG/solar/mains), status, owned or hired.
-2. Ownership comes from the Nexus asset register.</t>
+2. Ownership comes from a DATOMS field (R-31). If DATOMS lacks it, the column is hidden and reported (Q3). Nexus doesn't keep its own ownership register.</t>
         </is>
       </c>
       <c r="G40" s="19" t="inlineStr">
@@ -4733,7 +4741,7 @@
       <c r="F41" s="19" t="inlineStr">
         <is>
           <t>1. Endpoints for trends by day, week, month, year.
-2. Read from the summaries in S5-01, never raw readings.</t>
+2. Read from the rollup tables (S4-01), never raw readings for ranges over 6 h. 5-minute data only within 60 days; older ranges use hourly. Return the resolution used and data coverage per bucket.</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
@@ -5161,8 +5169,8 @@
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>1. Endpoint listing equipment per project: ID, name, type, make/model, current status.
-2. Include every extra parameter DATOMS sends for that device.</t>
+          <t>1. Endpoint listing equipment per project (kind = 'physical' only): ID, name, type, make/model, current status, plus extra nameplate fields as optional columns.
+2. Every parameter DATOMS sends for a device is available from GET /assets/{id} (device card). The list endpoint carries no live values (ADR 0008).</t>
         </is>
       </c>
       <c r="G47" s="19" t="inlineStr">
@@ -5234,7 +5242,7 @@
       <c r="F48" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint for one device: latest values of every parameter.
-2. Today's timeline of status changes (running, idle, off) from DATOMS events.</t>
+2. Today's timeline of status changes (running, idle, off) as observed by Nexus in polls, labelled "observed by Nexus" (ADR 0007). DATOMS's own status history is used only if a later ADR adds it.</t>
         </is>
       </c>
       <c r="G48" s="19" t="inlineStr">
@@ -5273,7 +5281,7 @@
       </c>
       <c r="O48" s="19" t="inlineStr">
         <is>
-          <t>Timeline matches DATOMS events</t>
+          <t>Timeline shows the status changes Nexus observed, labelled "observed by Nexus", accurate to one poll interval</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5313,7 @@
       </c>
       <c r="F49" s="19" t="inlineStr">
         <is>
-          <t>1. Counts per project: tower cranes total/idle, hoists total/idle, all equipment total/idle, using DATOMS statuses.
+          <t>1. Counts per project (kind = 'physical' only): tower cranes total/idle, hoists total/idle, all equipment total/idle, using DATOMS statuses.
 2. Add to the project summary (S5-03).</t>
         </is>
       </c>
@@ -5372,13 +5380,13 @@
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>Notifications sync from DATOMS and API (filter by site, asset, type)</t>
+          <t>Notifications from the DATOMS bulk response, and API (filter by site, asset, type)</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>1. Worker job every minute: fetch DATOMS notifications and faults.
-2. Store them; endpoint to list with filters: site, asset, type, date.
+          <t>1. In the live poll: take DATOMS alerts and faults from the bulk response (ADR 0010; no separate events job).
+2. Store them; endpoint to list with filters: site, asset, type, date. "Mark all read" moves a read marker (docs/06 section 3, item 11).
 3. Show them exactly as DATOMS sends them.</t>
         </is>
       </c>
@@ -5404,12 +5412,12 @@
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>S3-01</t>
+          <t>S3-03</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr">
         <is>
-          <t>DATOMS: notifications in API?</t>
+          <t>Alert field names in the bulk response (Q22)</t>
         </is>
       </c>
       <c r="M50" s="19" t="n">
@@ -6728,7 +6736,7 @@
       </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
-          <t>1. Give pilot users access on GHAFWOODS.
+          <t>1. Give pilot users access on GHAFWOODS in **prod** (there is no test environment, ADR 0008): only pilot users are assigned to the Entra app during the pilot.
 2. Walk through each screen with them.
 3. Record issues in the backlog.</t>
         </is>
@@ -7246,6 +7254,7 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
     <row r="78" ht="15" customHeight="1" s="14">
       <c r="L78" s="16" t="inlineStr">
         <is>

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -1381,7 +1381,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="14">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -7254,7 +7253,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
     <row r="78" ht="15" customHeight="1" s="14">
       <c r="L78" s="16" t="inlineStr">
         <is>
@@ -7427,7 +7425,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Same codebase, separate process: catalogue hourly, live values and notifications every minute, history backfill, gap repair</t>
+          <t>Same codebase, separate process: catalogue hourly, live values and notifications every minute (history backfill on hold, see S3-04)</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -5794,7 +5794,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="35.05" customHeight="1" s="14">
+    <row r="56" ht="79.84999999999999" customHeight="1" s="14">
       <c r="A56" s="19" t="inlineStr">
         <is>
           <t>S7-02</t>
@@ -5817,19 +5817,20 @@
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>Security hardening: private endpoints, key rotation, firewall rules</t>
+          <t>Security hardening: private endpoints, key rotation, firewall rules, web security headers</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
         <is>
           <t>1. Put PostgreSQL and Blob behind private endpoints.
 2. Rotate keys in Key Vault.
-3. Firewall: only Container Apps can reach the database.</t>
+3. Firewall: only Container Apps can reach the database.
+4. Web app security headers and CSP (docs/08 §6) in staticwebapp.config.json: a CSP that allows only the MSAL (Entra) and ArcGIS domains plus the API and Web PubSub hosts; HSTS, X-Content-Type-Options, Referrer-Policy, frame-ancestors none. (Added by the S0 plan, 2026-10-09.)</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>Data not reachable from the internet</t>
+          <t>Data not reachable from the internet; the web app sends a CSP and security headers</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
@@ -5859,7 +5860,7 @@
       </c>
       <c r="O56" s="19" t="inlineStr">
         <is>
-          <t>Databases unreachable from internet</t>
+          <t>Databases unreachable from internet; a header scan of the prod web URL shows the CSP and security headers, and sign-in and the map still work with the CSP on</t>
         </is>
       </c>
     </row>

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Future" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -768,27 +768,27 @@
         </is>
       </c>
       <c r="F2" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A2)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A2)</f>
         <v/>
       </c>
       <c r="G2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A2,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A2,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A2,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J2" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A2,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A2,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A2,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L2" s="20">
@@ -823,27 +823,27 @@
         </is>
       </c>
       <c r="F3" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A3)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A3)</f>
         <v/>
       </c>
       <c r="G3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A3,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A3,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A3,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A3,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A3,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A3,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L3" s="20">
@@ -878,27 +878,27 @@
         </is>
       </c>
       <c r="F4" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A4)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A4)</f>
         <v/>
       </c>
       <c r="G4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A4,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A4,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A4,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J4" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A4,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A4,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A4,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L4" s="20">
@@ -933,27 +933,27 @@
         </is>
       </c>
       <c r="F5" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A5)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A5)</f>
         <v/>
       </c>
       <c r="G5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A5,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A5,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A5,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J5" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A5,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A5,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A5,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L5" s="20">
@@ -988,27 +988,27 @@
         </is>
       </c>
       <c r="F6" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A6)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A6)</f>
         <v/>
       </c>
       <c r="G6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A6,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A6,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A6,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J6" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A6,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A6,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A6,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L6" s="20">
@@ -1043,27 +1043,27 @@
         </is>
       </c>
       <c r="F7" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A7)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A7)</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A7,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A7,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A7,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J7" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A7,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A7,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A7,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L7" s="20">
@@ -1098,27 +1098,27 @@
         </is>
       </c>
       <c r="F8" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A8)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A8)</f>
         <v/>
       </c>
       <c r="G8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A8,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A8,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A8,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J8" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A8,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A8,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A8,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L8" s="20">
@@ -1153,27 +1153,27 @@
         </is>
       </c>
       <c r="F9" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A9)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A9)</f>
         <v/>
       </c>
       <c r="G9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A9,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A9,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A9,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J9" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A9,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A9,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A9,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L9" s="20">
@@ -1208,27 +1208,27 @@
         </is>
       </c>
       <c r="F10" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A10)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A10)</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A10,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A10,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A10,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J10" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A10,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A10,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A10,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L10" s="20">
@@ -1263,27 +1263,27 @@
         </is>
       </c>
       <c r="F11" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A11)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A11)</f>
         <v/>
       </c>
       <c r="G11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A11,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A11,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A11,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J11" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A11,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A11,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A11,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L11" s="20">
@@ -1318,27 +1318,27 @@
         </is>
       </c>
       <c r="F12" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$76,A12)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$77,A12)</f>
         <v/>
       </c>
       <c r="G12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A12,Backlog!$I$2:$I$76,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$I$2:$I$77,"You (backend)")</f>
         <v/>
       </c>
       <c r="H12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A12,Backlog!$I$2:$I$76,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A12,Backlog!$I$2:$I$76,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$I$2:$I$77,"Both")</f>
         <v/>
       </c>
       <c r="J12" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$76,A12,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$B$2:$B$77,A12,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="K12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$76,Backlog!$B$2:$B$76,A12,Backlog!$N$2:$N$76,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$N$2:$N$77,"Done")</f>
         <v/>
       </c>
       <c r="L12" s="20">
@@ -1476,11 +1476,11 @@
         </is>
       </c>
       <c r="E4" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B4)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B4)</f>
         <v/>
       </c>
       <c r="F4" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B4,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B4,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="E5" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B5)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B5)</f>
         <v/>
       </c>
       <c r="F5" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B5,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B5,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -1542,11 +1542,11 @@
         </is>
       </c>
       <c r="E6" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B6)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B6)</f>
         <v/>
       </c>
       <c r="F6" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B6,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B6,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -1575,11 +1575,11 @@
         </is>
       </c>
       <c r="E7" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B7)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B7)</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B7,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B7,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="E8" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B8)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B8)</f>
         <v/>
       </c>
       <c r="F8" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B8,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B8,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1641,11 +1641,11 @@
         </is>
       </c>
       <c r="E9" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B9)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B9)</f>
         <v/>
       </c>
       <c r="F9" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B9,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B9,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="E10" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B10)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B10)</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B10,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B10,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="E11" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$76,B11)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$77,B11)</f>
         <v/>
       </c>
       <c r="F11" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$76,B11,Backlog!$M$2:$M$76)</f>
+        <f>SUMIF(Backlog!$H$2:$H$77,B11,Backlog!$M$2:$M$77)</f>
         <v/>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1754,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="13" min="1" max="1"/>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="91" customHeight="1" s="14">
+    <row r="11" ht="124.65" customHeight="1" s="14">
       <c r="A11" s="19" t="inlineStr">
         <is>
           <t>S1-01</t>
@@ -2540,7 +2540,8 @@
 2. Turn db/schema.sql into migration 0001_init.sql (up + down); add db/roles.sql grants.
 3. Raw telemetry is telemetry.packet: one jsonb row per asset packet, daily partitions (no TimescaleDB).
 4. Every asset has project_id and optional building/level/zone ids (what BIM links to later).
-5. Add pnpm db:migrate / db:check / db:seed; run the 100-site seed and record query timings.</t>
+5. Add pnpm db:migrate / db:check / db:seed; run the 100-site seed and record query timings.
+6. From the S1-02 security review (L3, accepted for now): when roles, project scope or active status change, clear the access cache on every API instance (Postgres LISTEN/NOTIFY or a per-user access version), check is_active on a cache hit, and never cache a load that started before the change.</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -3086,33 +3087,109 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="68.65000000000001" customHeight="1" s="14">
+    <row r="19" ht="91.05" customHeight="1" s="14">
       <c r="A19" s="19" t="inlineStr">
         <is>
+          <t>S1-09</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>API baseline protections: helmet, CORS for Nexus web origins only, per-user rate limit, request size limit, Swagger UI off in prod</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>1. Add helmet (@fastify/helmet) so every API response carries secure headers.
+2. Enable CORS only for the Nexus web origins, read from config per environment (no wildcard); add the variable to .env.example and docs/04.
+3. Add a per-user rate limit keyed on the Entra oid (by IP before sign-in); over the limit gives 429 problem+json with Retry-After; limits come from config.
+4. Set a request body size limit (Fastify bodyLimit) from config; larger bodies get 413.
+5. Serve Swagger UI only when APP_ENV is not prod.
+6. Update docs/08 §6 and docs/10. Needed before S2-01 (security review of S1-02, item I6).</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>The API refuses other origins, oversized bodies and excessive requests, and sends secure headers</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: security</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="inlineStr">
+        <is>
+          <t>S1-02</t>
+        </is>
+      </c>
+      <c r="L19" s="19" t="n"/>
+      <c r="M19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O19" s="19" t="inlineStr">
+        <is>
+          <t>Automated tests: a non-Nexus origin gets no CORS headers; a user over the limit gets 429 with Retry-After; an oversized body gets 413; secure headers on every response; Swagger UI gives 404 when APP_ENV=prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="68.65000000000001" customHeight="1" s="14">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>Projects API: list, filter (status, type, district), search, scoped to user</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>1. Create GET /projects with filters: status, type, district, search text.
 2. Apply the project-scope filter from S1-02.
@@ -3120,73 +3197,73 @@
 4. Add seed data for 5 sample sites so the frontend can work before DATOMS is connected.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>Projects list endpoint the map uses</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="J20" s="19" t="inlineStr">
         <is>
           <t>Sheet: Top level</t>
         </is>
       </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>S1-02</t>
-        </is>
-      </c>
-      <c r="L19" s="19" t="n"/>
-      <c r="M19" s="19" t="n">
+      <c r="K20" s="19" t="inlineStr">
+        <is>
+          <t>S1-02, S1-09</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="25" t="inlineStr">
+      <c r="N20" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O19" s="19" t="inlineStr">
+      <c r="O20" s="19" t="inlineStr">
         <is>
           <t>Returns only the user's projects; search under 300 ms</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="68.65000000000001" customHeight="1" s="14">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="21" ht="68.65000000000001" customHeight="1" s="14">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>S2-02</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>DATOMS API client: bulk endpoint, paging, retries, rate-limit and credit handling</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>1. Read the v4 PDF, plus the DATOMS sample bulk response (Q21) and bulk field list (Q22) once received.
 2. Build packages/datoms-client: list assets (catalogue) and the bulk endpoint (fleet and id mode) as the ONLY telemetry source (ADR 0010). data/latest is for CLI checks only.
@@ -3195,73 +3272,73 @@
 5. Test against GHAFWOODS on dev using fixtures or a small id-mode subset (never the full fleet from dev).</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>Code that can talk to DATOMS</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>Brief: energy, crane utilisation</t>
         </is>
       </c>
-      <c r="K20" s="19" t="n"/>
-      <c r="L20" s="19" t="inlineStr">
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="inlineStr">
         <is>
           <t>DATOMS sample bulk response (Q21) + bulk field list (Q22) + read-only key. Needed before this task starts; they do not block S0 or S1.</t>
         </is>
       </c>
-      <c r="M20" s="19" t="n">
+      <c r="M21" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N20" s="25" t="inlineStr">
+      <c r="N21" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O20" s="19" t="inlineStr">
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>Client reads the GHAFWOODS demo fleet (generators and tower cranes) through the bulk endpoint in dev; DATOMS field names exist only in src/mapping.ts</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="79.84999999999999" customHeight="1" s="14">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="22" ht="79.84999999999999" customHeight="1" s="14">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>S2-03</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Portfolio map (chosen provider, through the map wrapper): one pin per DATOMS site, coloured Active green, Central Store blue, Finished grey, In bid yellow where DATOMS gives the status</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>1. Use the MapView wrapper with the ArcGIS adapter from S0-09.
 2. Show a UAE map.
@@ -3270,292 +3347,292 @@
 5. Click a pin = zoom to that project.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>Top-level portfolio map</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>Sheet: Top level</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr">
+      <c r="K22" s="19" t="inlineStr">
         <is>
           <t>S0-09</t>
         </is>
       </c>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n">
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="25" t="inlineStr">
+      <c r="N22" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>All projects shown; colours match the sheet; click zooms to project</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="46.25" customHeight="1" s="14">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="23" ht="46.25" customHeight="1" s="14">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>S2-04</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>Project list panel and summary tiles (projects, districts)</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1. Left panel: list of sites with the details DATOMS provides (name, location, type, status).
 2. Two summary tiles at the top: number of projects, number of districts.
 3. Click a project in the list = same as clicking its pin.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>Project list beside the map</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>Brief mockups</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr">
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="L22" s="19" t="n"/>
-      <c r="M22" s="19" t="n">
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N22" s="25" t="inlineStr">
+      <c r="N23" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>List matches mockup: name, district, type tag, client, consultant, PM</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="35.05" customHeight="1" s="14">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24" ht="35.05" customHeight="1" s="14">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>S2-05</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Search and filters</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>1. Search box filters the list and pins by name.
 2. Filter chips: status, type, district.
 3. Filters call GET /projects with parameters.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>Users can find any project fast</t>
         </is>
       </c>
-      <c r="H23" s="19" t="inlineStr">
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>Brief mockups</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n">
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="25" t="inlineStr">
+      <c r="N24" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="O24" s="19" t="inlineStr">
         <is>
           <t>Filter by status, type, district; search by name</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="46.25" customHeight="1" s="14">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="25" ht="46.25" customHeight="1" s="14">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>Users and roles API: group-to-role mapping, project assignment, extra permissions</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing Entra groups and their Nexus role.
 2. Endpoints to assign users to projects. Keep room for extra permissions that later modules will need.
 3. Admin only; every change goes to the audit log.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>Backend for managing access</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="K25" s="19" t="inlineStr">
         <is>
           <t>S1-02</t>
         </is>
       </c>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n">
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="25" t="inlineStr">
+      <c r="N25" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O24" s="19" t="inlineStr">
+      <c r="O25" s="19" t="inlineStr">
         <is>
           <t>Changes take effect on next request</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="35.05" customHeight="1" s="14">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26" ht="35.05" customHeight="1" s="14">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>Catalogue sync (hourly): sites, devices, parameters, units</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>1. Scheduled job in apps/worker, every hour (and early when the poll sees unknown ids).
 2. Read all DATOMS assets (list assets: names, nameplate). Sites, asset types and parameters (name, unit) come in the bulk rows. The live poll (S3-03) upserts them the same way, so the catalogue job spends no bulk credits.
@@ -3563,150 +3640,150 @@
 4. Retire safely (docs/07 section 6): only after a complete walk; only rows missed in 2 consecutive complete walks; retire nothing and alert if more than 5% would go.</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>Nexus always knows every DATOMS site and device</t>
         </is>
       </c>
-      <c r="H25" s="19" t="inlineStr">
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K25" s="19" t="inlineStr">
+      <c r="K26" s="19" t="inlineStr">
         <is>
           <t>S2-02</t>
         </is>
       </c>
-      <c r="L25" s="19" t="inlineStr">
+      <c r="L26" s="19" t="inlineStr">
         <is>
           <t>DATOMS sample + field list (Q21, Q22) + read-only key; id stability (Q11)</t>
         </is>
       </c>
-      <c r="M25" s="19" t="n">
+      <c r="M26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="25" t="inlineStr">
+      <c r="N26" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O25" s="19" t="inlineStr">
+      <c r="O26" s="19" t="inlineStr">
         <is>
           <t>New DATOMS site appears in Nexus within 1 hour</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="46.25" customHeight="1" s="14">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="27" ht="46.25" customHeight="1" s="14">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>S3-02</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>Auto-link new sites and devices on exact match; others to admin to-do list</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1. When a new DATOMS site appears, link it to a Nexus project if the name matches exactly.
 2. Otherwise add it to an 'unlinked' list for admins.
 3. Same for devices → assets.</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>New sites appear automatically, no guessing</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H27" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J27" s="19" t="inlineStr">
         <is>
           <t>Innovo: sites added automatically</t>
         </is>
       </c>
-      <c r="K26" s="19" t="inlineStr">
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="L26" s="19" t="n"/>
-      <c r="M26" s="19" t="n">
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="25" t="inlineStr">
+      <c r="N27" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O26" s="19" t="inlineStr">
+      <c r="O27" s="19" t="inlineStr">
         <is>
           <t>No guessed links; unmatched items listed</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="46.25" customHeight="1" s="14">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="28" ht="46.25" customHeight="1" s="14">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>Live sync (every minute by default): bulk endpoint → packets, latest values, statuses, locations, alerts</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1. Job every 60 s by default (per-type interval, ADR 0006): bulk endpoint only (ADR 0010). Fleet mode when every asset is due, otherwise id mode. In dev, only the configured subset (ADR 0005).
 2. Write telemetry.packet (history) and telemetry.latest_packet (current); status, location and alerts on change only.
@@ -3714,73 +3791,73 @@
 4. Log how long each run takes and the credits used per window.</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>Live DATOMS data in Nexus within about 2 poll intervals</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J27" s="19" t="inlineStr">
+      <c r="J28" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K27" s="19" t="inlineStr">
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n">
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="25" t="inlineStr">
+      <c r="N28" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O27" s="19" t="inlineStr">
+      <c r="O28" s="19" t="inlineStr">
         <is>
           <t>Value in Nexus within 2 poll intervals of DATOMS (N-03)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="57.45" customHeight="1" s="14">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="29" ht="57.45" customHeight="1" s="14">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>S3-04</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>History backfill and gap repair after outages (ON HOLD)</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>1. On first run, copy all past data from DATOMS (since Jul 2026 for GHAFWOODS).
 2. Record the last time synced per device.
@@ -3788,294 +3865,294 @@
 4. Test by stopping the worker for an hour.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Full history, no gaps after outages</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="J29" s="19" t="inlineStr">
         <is>
           <t>Brief: trends</t>
         </is>
       </c>
-      <c r="K28" s="19" t="inlineStr">
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L28" s="19" t="inlineStr">
+      <c r="L29" s="19" t="inlineStr">
         <is>
           <t>ON HOLD (decided 2026-10-08). The bulk endpoint has no history (ADR 0010); Nexus builds its own history from polls from day one. Needs a DATOMS history feed (Q12) and a new ADR to use it. Until then, gaps stay gaps and charts show coverage (ADR 0007).</t>
         </is>
       </c>
-      <c r="M28" s="19" t="n">
+      <c r="M29" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="25" t="inlineStr">
+      <c r="N29" s="25" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O28" s="19" t="inlineStr">
+      <c r="O29" s="19" t="inlineStr">
         <is>
           <t>GHAFWOODS history since Jul 2026 loaded; gaps refilled after a forced outage</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="23.85" customHeight="1" s="14">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="30" ht="23.85" customHeight="1" s="14">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>S3-05</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>Device linking to-do list</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1. Page listing unlinked DATOMS sites/devices (from S4-02).
 2. Admin picks the project/asset to link each one to.</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Admins link anything not matched automatically</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="J30" s="19" t="inlineStr">
         <is>
           <t>Innovo: sites added automatically</t>
         </is>
       </c>
-      <c r="K29" s="19" t="inlineStr">
+      <c r="K30" s="19" t="inlineStr">
         <is>
           <t>S3-02</t>
         </is>
       </c>
-      <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n">
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="25" t="inlineStr">
+      <c r="N30" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O29" s="19" t="inlineStr">
+      <c r="O30" s="19" t="inlineStr">
         <is>
           <t>Admin links an unmatched device to a project</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="35.05" customHeight="1" s="14">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="31" ht="35.05" customHeight="1" s="14">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>S3-06</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>Integration health page: last sync, errors, delay</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>1. Page showing: last successful sync time, number of errors, delay in minutes.
 2. Red warning if the sync has stopped.</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Admins see if DATOMS data is flowing</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I30" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>Risks: DATOMS outage</t>
         </is>
       </c>
-      <c r="K30" s="19" t="inlineStr">
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L30" s="19" t="n"/>
-      <c r="M30" s="19" t="n">
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="25" t="inlineStr">
+      <c r="N31" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O30" s="19" t="inlineStr">
+      <c r="O31" s="19" t="inlineStr">
         <is>
           <t>Shows a stopped sync clearly</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="35.05" customHeight="1" s="14">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="32" ht="35.05" customHeight="1" s="14">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>S3-07</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>Users and roles screen: group-to-role mapping, project assignment</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>1. Page listing groups and roles (from S3-09).
 2. Assign users to projects.
 3. Show each user's role and projects.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Admins manage who sees what</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="H32" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I32" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J32" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K31" s="19" t="inlineStr">
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n">
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="25" t="inlineStr">
+      <c r="N32" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O31" s="19" t="inlineStr">
+      <c r="O32" s="19" t="inlineStr">
         <is>
           <t>Admin assigns a user to a project</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="46.25" customHeight="1" s="14">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="33" ht="46.25" customHeight="1" s="14">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>Chart summaries (5-minute, 1-hour, 1-day) as Nexus rollup tables</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>1. Use the rollup functions in db/schema.sql: telemetry.refresh_rollup_5m and refresh_rollup_combine (1 h, 1 day in Asia/Dubai).
 2. Worker rollups job (ADR 0007): refresh_rollup_5m once per CLOSED 5-minute bucket, 2 poll intervals after it ends; re-run only for closed buckets that get late packets; 1 h after the hour's last bucket; 1 d after the Dubai day. No sliding window, no in-memory accumulators.
@@ -4083,169 +4160,97 @@
 4. Check a 30-day query returns in under 1 second.</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Fast data for every chart</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H33" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I32" s="19" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>Brief: trends</t>
         </is>
       </c>
-      <c r="K32" s="19" t="inlineStr">
+      <c r="K33" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L32" s="19" t="n"/>
-      <c r="M32" s="19" t="n">
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="25" t="inlineStr">
+      <c r="N33" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O32" s="19" t="inlineStr">
+      <c r="O33" s="19" t="inlineStr">
         <is>
           <t>30-day chart query under 1 s</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="46.25" customHeight="1" s="14">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="34" ht="46.25" customHeight="1" s="14">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>S4-02</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>Live push: status changes sent to open browsers (Web PubSub)</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>1. When the worker sees a status or location change, publish a slim message to Azure Web PubSub (per project group): no parameter values; values.updated hint; summary.updated; chunked well under 1 MB (docs/10, ADR 0008).
 2. API gives the browser a Web PubSub token with no group-join rights. POST /v1/live/subscriptions checks permission and scope, then joins the connection to project groups on the server.
 3. On any Nexus access change, close the affected live connections so clients re-subscribe through the scope check. Settle with the security-reviewer how the API confirms a connectionId belongs to the caller.</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>Changes pushed to browsers live</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr">
+      <c r="H34" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I34" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="J34" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
-        </is>
-      </c>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>S3-03</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O33" s="19" t="inlineStr">
-        <is>
-          <t>Pin colour changes without refresh; a user whose project access is removed stops receiving that project's messages at once; nothing project-specific is sent to the portfolio group</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46.25" customHeight="1" s="14">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>S4-03</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>Project page</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>Project summary APIs for the equipment and energy info boxes</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>1. Endpoints GET /projects/{id}/equipment/summary (Box 2) and GET /projects/{id}/energy/summary (Box 3), as in docs/10.
-2. Fill them from the latest DATOMS values: equipment counts from kind = 'physical' assets; energy site totals from site_metric records when DATOMS provides them. Manpower and materials are not built (slots only).</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="inlineStr">
-        <is>
-          <t>The project page loads its boxes</t>
-        </is>
-      </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L1 Info boxes</t>
         </is>
       </c>
       <c r="K34" s="19" t="inlineStr">
@@ -4264,110 +4269,182 @@
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
+          <t>Pin colour changes without refresh; a user whose project access is removed stops receiving that project's messages at once; nothing project-specific is sent to the portfolio group</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="46.25" customHeight="1" s="14">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>S4-03</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Project page</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>Project summary APIs for the equipment and energy info boxes</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>1. Endpoints GET /projects/{id}/equipment/summary (Box 2) and GET /projects/{id}/energy/summary (Box 3), as in docs/10.
+2. Fill them from the latest DATOMS values: equipment counts from kind = 'physical' assets; energy site totals from site_metric records when DATOMS provides them. Manpower and materials are not built (slots only).</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>The project page loads its boxes</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L1 Info boxes</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>S3-03</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O35" s="19" t="inlineStr">
+        <is>
           <t>The two endpoints return Box 2 and Box 3 as reported; Boxes 1 and 4 are "coming later" slots</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="57.45" customHeight="1" s="14">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="36" ht="57.45" customHeight="1" s="14">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>S4-04</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>Project page layout: site map, side panel, equipment and energy info boxes (space kept for manpower and materials later)</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>1. Project page: site map in the centre, equipment and energy info boxes on the right (as structure sheet level 1); leave space for manpower and materials.
 2. Load data from S5-03.
 3. Back button returns to the portfolio map.</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>Level 1 project page</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H36" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I36" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="J36" s="19" t="inlineStr">
         <is>
           <t>Sheet: Level 1</t>
         </is>
       </c>
-      <c r="K35" s="19" t="inlineStr">
+      <c r="K36" s="19" t="inlineStr">
         <is>
           <t>S4-03</t>
         </is>
       </c>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n">
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N35" s="25" t="inlineStr">
+      <c r="N36" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O35" s="19" t="inlineStr">
+      <c r="O36" s="19" t="inlineStr">
         <is>
           <t>Matches structure sheet level 1</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="57.45" customHeight="1" s="14">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37" ht="57.45" customHeight="1" s="14">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>S4-05</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>Asset pins: icon per type, colour per DATOMS status, clustering, map/satellite switch</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>1. Draw one pin per equipment asset (kind = 'physical') at its DATOMS location; no location = "Not on map".
 2. Icon by type: tower crane, hoist, equipment, generator; unknown types use the generic icon.
@@ -4375,177 +4452,105 @@
 4. Turn on clustering and a Map/Satellite switch. 3D uses the same icons with no callouts or pulse (ADR 0008).</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Live equipment pins on the site map</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H37" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr">
+      <c r="I37" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="J37" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 blinkers on map</t>
         </is>
       </c>
-      <c r="K36" s="19" t="inlineStr">
+      <c r="K37" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L36" s="19" t="inlineStr">
+      <c r="L37" s="19" t="inlineStr">
         <is>
           <t>Bulk field names for location + status (Q22; DATOMS confirmed the data is in the bulk response); blink vs pulse (Q19)</t>
         </is>
       </c>
-      <c r="M36" s="19" t="n">
+      <c r="M37" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="25" t="inlineStr">
+      <c r="N37" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O36" s="19" t="inlineStr">
+      <c r="O37" s="19" t="inlineStr">
         <is>
           <t>Running green, Idle amber, Maintenance red, Off grey as reported</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="35.05" customHeight="1" s="14">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="38" ht="35.05" customHeight="1" s="14">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>S4-06</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Live updates on pins and boxes (WebSocket)</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>1. Connect to Web PubSub with the token from the API.
 2. When a message arrives, update that pin's colour and the info box numbers without reloading.</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Map and boxes update live</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H38" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr">
+      <c r="I38" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J37" s="19" t="inlineStr">
+      <c r="J38" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K37" s="19" t="inlineStr">
+      <c r="K38" s="19" t="inlineStr">
         <is>
           <t>S4-02</t>
-        </is>
-      </c>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O37" s="19" t="inlineStr">
-        <is>
-          <t>Update visible within a minute</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="35.05" customHeight="1" s="14">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>S4-07</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>Project page</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>Asset side panel: live readings, faults, last run</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>1. Click a pin = side panel with the asset's latest readings, faults and last run.
-2. Link to the equipment detail page.</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>Asset details on click</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="inlineStr">
-        <is>
-          <t>DATOMS parity</t>
-        </is>
-      </c>
-      <c r="K38" s="19" t="inlineStr">
-        <is>
-          <t>S4-03</t>
         </is>
       </c>
       <c r="L38" s="19" t="n"/>
@@ -4559,283 +4564,287 @@
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
+          <t>Update visible within a minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="35.05" customHeight="1" s="14">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>S4-07</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Project page</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>Asset side panel: live readings, faults, last run</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>1. Click a pin = side panel with the asset's latest readings, faults and last run.
+2. Link to the equipment detail page.</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>Asset details on click</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>DATOMS parity</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="inlineStr">
+        <is>
+          <t>S4-03</t>
+        </is>
+      </c>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O39" s="19" t="inlineStr">
+        <is>
           <t>Opens on pin click</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="57.45" customHeight="1" s="14">
-      <c r="A39" s="19" t="inlineStr">
+    <row r="40" ht="57.45" customHeight="1" s="14">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>S5-01</t>
         </is>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>Energy API: generators, solar, mains, loads by area, site totals and CO2 as reported by DATOMS</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint returning per project: generators (running/total), solar generation, mains, total load, loads by area, site totals and CO2 exactly as DATOMS gives them in the bulk response. Site totals are read from site_metric records (ADR 0009); anything missing shows "no data yet".
 2. Compare with the DATOMS Site View for GHAFWOODS; numbers must match.</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
         <is>
           <t>Energy data for box 3 and the energy page</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr">
+      <c r="H40" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J39" s="19" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
         <is>
           <t>Brief: energy monitoring; Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K39" s="19" t="inlineStr">
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L39" s="19" t="inlineStr">
+      <c r="L40" s="19" t="inlineStr">
         <is>
           <t>Whether DATOMS has site totals (Q3); bulk field names (Q22)</t>
         </is>
       </c>
-      <c r="M39" s="19" t="n">
+      <c r="M40" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N39" s="25" t="inlineStr">
+      <c r="N40" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O39" s="19" t="inlineStr">
+      <c r="O40" s="19" t="inlineStr">
         <is>
           <t>Figures match DATOMS Site View for GHAFWOODS</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="35.05" customHeight="1" s="14">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="41" ht="35.05" customHeight="1" s="14">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>S5-02</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>Energy equipment table data incl. owned / hired</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing energy equipment: DG ID, description, type (DG/solar/mains), status, owned or hired.
 2. Ownership comes from a DATOMS field (R-31). If DATOMS lacks it, the column is hidden and reported (Q3). Nexus doesn't keep its own ownership register.</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
         <is>
           <t>Data for the energy table</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J40" s="19" t="inlineStr">
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K40" s="19" t="inlineStr">
+      <c r="K41" s="19" t="inlineStr">
         <is>
           <t>S5-01</t>
         </is>
       </c>
-      <c r="L40" s="19" t="n"/>
-      <c r="M40" s="19" t="n">
+      <c r="L41" s="19" t="n"/>
+      <c r="M41" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="25" t="inlineStr">
+      <c r="N41" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O40" s="19" t="inlineStr">
+      <c r="O41" s="19" t="inlineStr">
         <is>
           <t>DG ID, description, status, ownership returned</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="23.85" customHeight="1" s="14">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="42" ht="23.85" customHeight="1" s="14">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>S5-03</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>Trend endpoints: day, week, month, year from summaries</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>1. Endpoints for trends by day, week, month, year.
 2. Read from the rollup tables (S4-01), never raw readings for ranges over 6 h. 5-minute data only within 60 days; older ranges use hourly. Return the resolution used and data coverage per bucket.</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Trend data for charts</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="H42" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="I42" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J41" s="19" t="inlineStr">
+      <c r="J42" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 trend graphs</t>
         </is>
       </c>
-      <c r="K41" s="19" t="inlineStr">
+      <c r="K42" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="L41" s="19" t="n"/>
-      <c r="M41" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N41" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O41" s="19" t="inlineStr">
-        <is>
-          <t>Each range under 1 s</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="35.05" customHeight="1" s="14">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>S5-04</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>Load-test harness: simulate 100+ sites and 1,000 users</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>1. Write a script (e.g. k6) that simulates 100+ sites of data and 1,000 users opening pages.
-2. Run it against dev and record response times.</t>
-        </is>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
-        <is>
-          <t>Repeatable load test</t>
-        </is>
-      </c>
-      <c r="H42" s="19" t="inlineStr">
-        <is>
-          <t>QA engineer</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>Innovo: scalable</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="n"/>
       <c r="L42" s="19" t="n"/>
       <c r="M42" s="19" t="n">
         <v>2</v>
@@ -4847,137 +4856,133 @@
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
-          <t>Repeatable test script in repo</t>
+          <t>Each range under 1 s</t>
         </is>
       </c>
     </row>
     <row r="43" ht="35.05" customHeight="1" s="14">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t>S5-04</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>Load-test harness: simulate 100+ sites and 1,000 users</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>1. Write a script (e.g. k6) that simulates 100+ sites of data and 1,000 users opening pages.
+2. Run it against dev and record response times.</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>Repeatable load test</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>QA engineer</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: scalable</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O43" s="19" t="inlineStr">
+        <is>
+          <t>Repeatable test script in repo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="35.05" customHeight="1" s="14">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
           <t>S5-05</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>Info box 3 Energy</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>1. Info box 3 on the project page: DGs running/total, total energy load, solar generation, main:solar ratio (structure sheet).
 2. Click = open energy detail.</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G44" s="19" t="inlineStr">
         <is>
           <t>Energy info box</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="H44" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I44" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="J44" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 3</t>
         </is>
       </c>
-      <c r="K43" s="19" t="inlineStr">
+      <c r="K44" s="19" t="inlineStr">
         <is>
           <t>S4-03</t>
-        </is>
-      </c>
-      <c r="L43" s="19" t="n"/>
-      <c r="M43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O43" s="19" t="inlineStr">
-        <is>
-          <t>DG running state, energy load, solar, main:solar ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="23.85" customHeight="1" s="14">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>S5-06</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>Energy detail: top ribbon of metrics</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>1. Top ribbon on the energy page with the key energy numbers.
-2. Data from S6-01.</t>
-        </is>
-      </c>
-      <c r="G44" s="19" t="inlineStr">
-        <is>
-          <t>Energy summary ribbon</t>
-        </is>
-      </c>
-      <c r="H44" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I44" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J44" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Energy</t>
-        </is>
-      </c>
-      <c r="K44" s="19" t="inlineStr">
-        <is>
-          <t>S5-01</t>
         </is>
       </c>
       <c r="L44" s="19" t="n"/>
@@ -4991,282 +4996,282 @@
       </c>
       <c r="O44" s="19" t="inlineStr">
         <is>
-          <t>Matches sheet</t>
+          <t>DG running state, energy load, solar, main:solar ratio</t>
         </is>
       </c>
     </row>
     <row r="45" ht="23.85" customHeight="1" s="14">
       <c r="A45" s="19" t="inlineStr">
         <is>
+          <t>S5-06</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>Energy detail: top ribbon of metrics</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>1. Top ribbon on the energy page with the key energy numbers.
+2. Data from S6-01.</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>Energy summary ribbon</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L2 Energy</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="inlineStr">
+        <is>
+          <t>S5-01</t>
+        </is>
+      </c>
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O45" s="19" t="inlineStr">
+        <is>
+          <t>Matches sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="23.85" customHeight="1" s="14">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
           <t>S5-07</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>Energy equipment table</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>1. Table: DG ID, description, status, ownership (owned/hired), running/off.
 2. Sort and filter.</t>
         </is>
       </c>
-      <c r="G45" s="19" t="inlineStr">
+      <c r="G46" s="19" t="inlineStr">
         <is>
           <t>Energy equipment table</t>
         </is>
       </c>
-      <c r="H45" s="19" t="inlineStr">
+      <c r="H46" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I45" s="19" t="inlineStr">
+      <c r="I46" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J45" s="19" t="inlineStr">
+      <c r="J46" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K45" s="19" t="inlineStr">
+      <c r="K46" s="19" t="inlineStr">
         <is>
           <t>S5-02</t>
         </is>
       </c>
-      <c r="L45" s="19" t="n"/>
-      <c r="M45" s="19" t="n">
+      <c r="L46" s="19" t="n"/>
+      <c r="M46" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N45" s="25" t="inlineStr">
+      <c r="N46" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O45" s="19" t="inlineStr">
+      <c r="O46" s="19" t="inlineStr">
         <is>
           <t>Sortable; status live</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="35.05" customHeight="1" s="14">
-      <c r="A46" s="19" t="inlineStr">
+    <row r="47" ht="35.05" customHeight="1" s="14">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>S5-08</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>Energy charts: load trends, distribution, solar trends</t>
         </is>
       </c>
-      <c r="F46" s="19" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>1. Charts: load trend, load distribution, solar trend.
 2. Range buttons: day, week, month, year.
 3. Data from S6-03.</t>
         </is>
       </c>
-      <c r="G46" s="19" t="inlineStr">
+      <c r="G47" s="19" t="inlineStr">
         <is>
           <t>Energy charts</t>
         </is>
       </c>
-      <c r="H46" s="19" t="inlineStr">
+      <c r="H47" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I46" s="19" t="inlineStr">
+      <c r="I47" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J46" s="19" t="inlineStr">
+      <c r="J47" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K46" s="19" t="inlineStr">
+      <c r="K47" s="19" t="inlineStr">
         <is>
           <t>S5-03</t>
         </is>
       </c>
-      <c r="L46" s="19" t="n"/>
-      <c r="M46" s="19" t="n">
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N46" s="25" t="inlineStr">
+      <c r="N47" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O46" s="19" t="inlineStr">
+      <c r="O47" s="19" t="inlineStr">
         <is>
           <t>Range switch day/week/month/year</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="35.05" customHeight="1" s="14">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="48" ht="35.05" customHeight="1" s="14">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>Equipment API: ID, name, type, make/model, status + native DATOMS fields</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing equipment per project (kind = 'physical' only): ID, name, type, make/model, current status, plus extra nameplate fields as optional columns.
 2. Every parameter DATOMS sends for a device is available from GET /assets/{id} (device card). The list endpoint carries no live values (ADR 0008).</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="G48" s="19" t="inlineStr">
         <is>
           <t>Data for the equipment table</t>
         </is>
       </c>
-      <c r="H47" s="19" t="inlineStr">
+      <c r="H48" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I47" s="19" t="inlineStr">
+      <c r="I48" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="J48" s="19" t="inlineStr">
         <is>
           <t>Brief: crane utilisation, asset tracking; Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K47" s="19" t="inlineStr">
+      <c r="K48" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
-        </is>
-      </c>
-      <c r="L47" s="19" t="n"/>
-      <c r="M47" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O47" s="19" t="inlineStr">
-        <is>
-          <t>All DATOMS parameters available per asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="35.05" customHeight="1" s="14">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>S6-02</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>Device card API: latest values, today's running timeline</t>
-        </is>
-      </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>1. Endpoint for one device: latest values of every parameter.
-2. Today's timeline of status changes (running, idle, off) as observed by Nexus in polls, labelled "observed by Nexus" (ADR 0007). DATOMS's own status history is used only if a later ADR adds it.</t>
-        </is>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>Data for the device card</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Equipment</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>S6-01</t>
         </is>
       </c>
       <c r="L48" s="19" t="n"/>
@@ -5280,358 +5285,358 @@
       </c>
       <c r="O48" s="19" t="inlineStr">
         <is>
-          <t>Timeline shows the status changes Nexus observed, labelled "observed by Nexus", accurate to one poll interval</t>
+          <t>All DATOMS parameters available per asset</t>
         </is>
       </c>
     </row>
     <row r="49" ht="35.05" customHeight="1" s="14">
       <c r="A49" s="19" t="inlineStr">
         <is>
+          <t>S6-02</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>Device card API: latest values, today's running timeline</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>1. Endpoint for one device: latest values of every parameter.
+2. Today's timeline of status changes (running, idle, off) as observed by Nexus in polls, labelled "observed by Nexus" (ADR 0007). DATOMS's own status history is used only if a later ADR adds it.</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>Data for the device card</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L2 Equipment</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>S6-01</t>
+        </is>
+      </c>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O49" s="19" t="inlineStr">
+        <is>
+          <t>Timeline shows the status changes Nexus observed, labelled "observed by Nexus", accurate to one poll interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35.05" customHeight="1" s="14">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
           <t>S6-03</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>Info box 2 counts: tower cranes, hoists, all equipment (total / idle)</t>
         </is>
       </c>
-      <c r="F49" s="19" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>1. Counts per project (kind = 'physical' only): tower cranes total/idle, hoists total/idle, all equipment total/idle, using DATOMS statuses.
 2. Add to the project summary (S5-03).</t>
         </is>
       </c>
-      <c r="G49" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>Numbers for info box 2</t>
         </is>
       </c>
-      <c r="H49" s="19" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I49" s="19" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 2</t>
         </is>
       </c>
-      <c r="K49" s="19" t="inlineStr">
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="L49" s="19" t="n"/>
-      <c r="M49" s="19" t="n">
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N49" s="25" t="inlineStr">
+      <c r="N50" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O49" s="19" t="inlineStr">
+      <c r="O50" s="19" t="inlineStr">
         <is>
           <t>Counts follow DATOMS statuses</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="35.05" customHeight="1" s="14">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="51" ht="35.05" customHeight="1" s="14">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>S6-04</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>Notifications from the DATOMS bulk response, and API (filter by site, asset, type)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>1. In the live poll: take DATOMS alerts and faults from the bulk response (ADR 0010; no separate events job).
 2. Store them; endpoint to list with filters: site, asset, type, date. "Mark all read" moves a read marker (docs/06 section 3, item 11).
 3. Show them exactly as DATOMS sends them.</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>Notifications in Nexus</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J50" s="19" t="inlineStr">
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t>Innovo: alerts as they come</t>
         </is>
       </c>
-      <c r="K50" s="19" t="inlineStr">
+      <c r="K51" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L50" s="19" t="inlineStr">
+      <c r="L51" s="19" t="inlineStr">
         <is>
           <t>Alert field names in the bulk response (Q22)</t>
         </is>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="M51" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N50" s="25" t="inlineStr">
+      <c r="N51" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O50" s="19" t="inlineStr">
+      <c r="O51" s="19" t="inlineStr">
         <is>
           <t>Same notifications as DATOMS, newest first</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="35.05" customHeight="1" s="14">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="52" ht="35.05" customHeight="1" s="14">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>S6-05</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>Info box 2 component</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>1. Info box 2: tower cranes count/idle, hoists count/idle, total equipment/idle (structure sheet).
 2. Click = open equipment detail.</t>
         </is>
       </c>
-      <c r="G51" s="19" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>Equipment info box</t>
         </is>
       </c>
-      <c r="H51" s="19" t="inlineStr">
+      <c r="H52" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I51" s="19" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J51" s="19" t="inlineStr">
+      <c r="J52" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 2</t>
         </is>
       </c>
-      <c r="K51" s="19" t="inlineStr">
+      <c r="K52" s="19" t="inlineStr">
         <is>
           <t>S6-03</t>
         </is>
       </c>
-      <c r="L51" s="19" t="n"/>
-      <c r="M51" s="19" t="n">
+      <c r="L52" s="19" t="n"/>
+      <c r="M52" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N51" s="25" t="inlineStr">
+      <c r="N52" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O51" s="19" t="inlineStr">
+      <c r="O52" s="19" t="inlineStr">
         <is>
           <t>Count / idle per type</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="35.05" customHeight="1" s="14">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="53" ht="35.05" customHeight="1" s="14">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>S6-06</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D52" s="19" t="inlineStr">
+      <c r="D53" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E53" s="24" t="inlineStr">
         <is>
           <t>Equipment detail table: sort, filter by type and status</t>
         </is>
       </c>
-      <c r="F52" s="19" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>1. Table with Equipment ID, Name, Type, Model/Make, Current Status + extra DATOMS fields.
 2. Filter by type and status; sort; search.</t>
         </is>
       </c>
-      <c r="G52" s="19" t="inlineStr">
+      <c r="G53" s="19" t="inlineStr">
         <is>
           <t>Equipment detail page</t>
         </is>
       </c>
-      <c r="H52" s="19" t="inlineStr">
+      <c r="H53" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I52" s="19" t="inlineStr">
+      <c r="I53" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="J53" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K52" s="19" t="inlineStr">
+      <c r="K53" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
-        </is>
-      </c>
-      <c r="L52" s="19" t="n"/>
-      <c r="M52" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O52" s="19" t="inlineStr">
-        <is>
-          <t>All sheet columns plus native fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="23.85" customHeight="1" s="14">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>S6-07</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>Device card</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>1. Card opened from a table row or a map pin.
-2. Shows all latest values and today's timeline.</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="inlineStr">
-        <is>
-          <t>Device card</t>
-        </is>
-      </c>
-      <c r="H53" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I53" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Equipment</t>
-        </is>
-      </c>
-      <c r="K53" s="19" t="inlineStr">
-        <is>
-          <t>S6-02</t>
         </is>
       </c>
       <c r="L53" s="19" t="n"/>
@@ -5645,14 +5650,14 @@
       </c>
       <c r="O53" s="19" t="inlineStr">
         <is>
-          <t>Opens from table row or pin</t>
+          <t>All sheet columns plus native fields</t>
         </is>
       </c>
     </row>
     <row r="54" ht="23.85" customHeight="1" s="14">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>S6-08</t>
+          <t>S6-07</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
@@ -5667,23 +5672,23 @@
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
         <is>
-          <t>Notifications bell and list with filters</t>
+          <t>Device card</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>1. Bell in header shows unread count.
-2. Click = list of notifications, newest first, with filters.</t>
+          <t>1. Card opened from a table row or a map pin.
+2. Shows all latest values and today's timeline.</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>Notifications in the header</t>
+          <t>Device card</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
@@ -5698,12 +5703,12 @@
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>Innovo: alerts as they come</t>
+          <t>Sheet: L2 Equipment</t>
         </is>
       </c>
       <c r="K54" s="19" t="inlineStr">
         <is>
-          <t>S6-04</t>
+          <t>S6-02</t>
         </is>
       </c>
       <c r="L54" s="19" t="n"/>
@@ -5717,110 +5722,182 @@
       </c>
       <c r="O54" s="19" t="inlineStr">
         <is>
+          <t>Opens from table row or pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="23.85" customHeight="1" s="14">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>S6-08</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>Notifications bell and list with filters</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>1. Bell in header shows unread count.
+2. Click = list of notifications, newest first, with filters.</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>Notifications in the header</t>
+        </is>
+      </c>
+      <c r="H55" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: alerts as they come</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="inlineStr">
+        <is>
+          <t>S6-04</t>
+        </is>
+      </c>
+      <c r="L55" s="19" t="n"/>
+      <c r="M55" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O55" s="19" t="inlineStr">
+        <is>
           <t>Unread count; filter by site and asset</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="46.25" customHeight="1" s="14">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="56" ht="46.25" customHeight="1" s="14">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>S7-01</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>DATOMS explorer</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>Explorer API: any device, any parameter, time range, min / avg / max, compare</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint: for any device, list its parameters.
 2. Endpoint: values for chosen parameters and time range, with min / average / max.
 3. Works for any new parameter without code changes.</t>
         </is>
       </c>
-      <c r="G55" s="19" t="inlineStr">
+      <c r="G56" s="19" t="inlineStr">
         <is>
           <t>Data for 'all DATOMS data'</t>
         </is>
       </c>
-      <c r="H55" s="19" t="inlineStr">
+      <c r="H56" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I55" s="19" t="inlineStr">
+      <c r="I56" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K55" s="19" t="inlineStr">
+      <c r="K56" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="L55" s="19" t="n"/>
-      <c r="M55" s="19" t="n">
+      <c r="L56" s="19" t="n"/>
+      <c r="M56" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N55" s="25" t="inlineStr">
+      <c r="N56" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O55" s="19" t="inlineStr">
+      <c r="O56" s="19" t="inlineStr">
         <is>
           <t>New parameter types appear with no code change</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="79.84999999999999" customHeight="1" s="14">
-      <c r="A56" s="19" t="inlineStr">
+    <row r="57" ht="79.84999999999999" customHeight="1" s="14">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>S7-02</t>
         </is>
       </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C56" s="19" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>Security hardening: private endpoints, key rotation, firewall rules, web security headers</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>1. Put PostgreSQL and Blob behind private endpoints.
 2. Rotate keys in Key Vault.
@@ -5828,69 +5905,69 @@
 4. Web app security headers and CSP (docs/08 §6) in staticwebapp.config.json: a CSP that allows only the MSAL (Entra) and ArcGIS domains plus the API and Web PubSub hosts; HSTS, X-Content-Type-Options, Referrer-Policy, frame-ancestors none. (Added by the S0 plan, 2026-10-09.)</t>
         </is>
       </c>
-      <c r="G56" s="19" t="inlineStr">
+      <c r="G57" s="19" t="inlineStr">
         <is>
           <t>Data not reachable from the internet; the web app sends a CSP and security headers</t>
         </is>
       </c>
-      <c r="H56" s="19" t="inlineStr">
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I56" s="19" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J56" s="19" t="inlineStr">
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>Innovo: security</t>
         </is>
       </c>
-      <c r="K56" s="19" t="n"/>
-      <c r="L56" s="19" t="n"/>
-      <c r="M56" s="19" t="n">
+      <c r="K57" s="19" t="n"/>
+      <c r="L57" s="19" t="n"/>
+      <c r="M57" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N56" s="25" t="inlineStr">
+      <c r="N57" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O56" s="19" t="inlineStr">
+      <c r="O57" s="19" t="inlineStr">
         <is>
           <t>Databases unreachable from internet; a header scan of the prod web URL shows the CSP and security headers, and sign-in and the map still work with the CSP on</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="57.45" customHeight="1" s="14">
-      <c r="A57" s="19" t="inlineStr">
+    <row r="58" ht="57.45" customHeight="1" s="14">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>S7-03</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>DATOMS explorer</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E58" s="24" t="inlineStr">
         <is>
           <t>Explorer screens: site and device picker, parameter tiles, chart with ranges and compare</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>1. Pick site, then device.
 2. Tiles with latest value of every parameter.
@@ -5898,309 +5975,240 @@
 4. Compare several parameters on one chart.</t>
         </is>
       </c>
-      <c r="G57" s="19" t="inlineStr">
+      <c r="G58" s="19" t="inlineStr">
         <is>
           <t>Explorer showing all DATOMS data</t>
         </is>
       </c>
-      <c r="H57" s="19" t="inlineStr">
+      <c r="H58" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I57" s="19" t="inlineStr">
+      <c r="I58" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J57" s="19" t="inlineStr">
+      <c r="J58" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K57" s="19" t="inlineStr">
+      <c r="K58" s="19" t="inlineStr">
         <is>
           <t>S7-01</t>
         </is>
       </c>
-      <c r="L57" s="19" t="n"/>
-      <c r="M57" s="19" t="n">
+      <c r="L58" s="19" t="n"/>
+      <c r="M58" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N57" s="25" t="inlineStr">
+      <c r="N58" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O57" s="19" t="inlineStr">
+      <c r="O58" s="19" t="inlineStr">
         <is>
           <t>Matches DATOMS parameter view</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="35.05" customHeight="1" s="14">
-      <c r="A58" s="19" t="inlineStr">
+    <row r="59" ht="35.05" customHeight="1" s="14">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>S7-04</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E59" s="24" t="inlineStr">
         <is>
           <t>Automated permission tests for every role</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>1. Create a test user for each role.
 2. Automated tests: each role can open what it should, and is refused everything else.</t>
         </is>
       </c>
-      <c r="G58" s="19" t="inlineStr">
+      <c r="G59" s="19" t="inlineStr">
         <is>
           <t>Permissions proven by tests</t>
         </is>
       </c>
-      <c r="H58" s="19" t="inlineStr">
+      <c r="H59" s="19" t="inlineStr">
         <is>
           <t>QA engineer</t>
         </is>
       </c>
-      <c r="I58" s="19" t="inlineStr">
+      <c r="I59" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J58" s="19" t="inlineStr">
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K58" s="19" t="inlineStr">
+      <c r="K59" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="L58" s="19" t="n"/>
-      <c r="M58" s="19" t="n">
+      <c r="L59" s="19" t="n"/>
+      <c r="M59" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N58" s="25" t="inlineStr">
+      <c r="N59" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O58" s="19" t="inlineStr">
+      <c r="O59" s="19" t="inlineStr">
         <is>
           <t>Every role's allowed and denied paths covered</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="23.85" customHeight="1" s="14">
-      <c r="A59" s="19" t="inlineStr">
+    <row r="60" ht="23.85" customHeight="1" s="14">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>S7-05</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E60" s="24" t="inlineStr">
         <is>
           <t>Production environment from code</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>1. Deploy 'nexus-prod' from the same Bicep files.
 2. Separate keys and Entra settings for production.</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
+      <c r="G60" s="19" t="inlineStr">
         <is>
           <t>Production environment ready</t>
         </is>
       </c>
-      <c r="H59" s="19" t="inlineStr">
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I59" s="19" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J59" s="19" t="inlineStr">
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="K59" s="19" t="inlineStr">
+      <c r="K60" s="19" t="inlineStr">
         <is>
           <t>S0-02</t>
         </is>
       </c>
-      <c r="L59" s="19" t="n"/>
-      <c r="M59" s="19" t="n">
+      <c r="L60" s="19" t="n"/>
+      <c r="M60" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N59" s="25" t="inlineStr">
+      <c r="N60" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O59" s="19" t="inlineStr">
+      <c r="O60" s="19" t="inlineStr">
         <is>
           <t>Prod built from the same Bicep files</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="23.85" customHeight="1" s="14">
-      <c r="A60" s="19" t="inlineStr">
+    <row r="61" ht="23.85" customHeight="1" s="14">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>S7-06</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E60" s="24" t="inlineStr">
+      <c r="E61" s="24" t="inlineStr">
         <is>
           <t>Tablet and mobile polish</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>1. Test every screen on a phone and a tablet.
 2. Fix layouts, touch targets, drawers.</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="G61" s="19" t="inlineStr">
         <is>
           <t>Polished tablet and mobile</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="J61" s="19" t="inlineStr">
         <is>
           <t>Innovo: devices</t>
-        </is>
-      </c>
-      <c r="K60" s="19" t="n"/>
-      <c r="L60" s="19" t="n"/>
-      <c r="M60" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N60" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O60" s="19" t="inlineStr">
-        <is>
-          <t>All screens usable on phone and tablet</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="35.05" customHeight="1" s="14">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>S7-07</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E61" s="24" t="inlineStr">
-        <is>
-          <t>Stale and missing data states: last updated, gaps shown as gaps</t>
-        </is>
-      </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>1. Show 'last updated' on every live box.
-2. Show missing data as a gap in charts, never as zero.
-3. Grey 'offline' state when DATOMS reports it.</t>
-        </is>
-      </c>
-      <c r="G61" s="19" t="inlineStr">
-        <is>
-          <t>Users can trust what they see</t>
-        </is>
-      </c>
-      <c r="H61" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I61" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J61" s="19" t="inlineStr">
-        <is>
-          <t>Risks: data quality</t>
         </is>
       </c>
       <c r="K61" s="19" t="n"/>
@@ -6215,202 +6223,202 @@
       </c>
       <c r="O61" s="19" t="inlineStr">
         <is>
-          <t>No zeros shown for missing data</t>
+          <t>All screens usable on phone and tablet</t>
         </is>
       </c>
     </row>
     <row r="62" ht="35.05" customHeight="1" s="14">
       <c r="A62" s="19" t="inlineStr">
         <is>
+          <t>S7-07</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>Stale and missing data states: last updated, gaps shown as gaps</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>1. Show 'last updated' on every live box.
+2. Show missing data as a gap in charts, never as zero.
+3. Grey 'offline' state when DATOMS reports it.</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>Users can trust what they see</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I62" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>Risks: data quality</t>
+        </is>
+      </c>
+      <c r="K62" s="19" t="n"/>
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N62" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O62" s="19" t="inlineStr">
+        <is>
+          <t>No zeros shown for missing data</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="35.05" customHeight="1" s="14">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
           <t>S8-01</t>
         </is>
       </c>
-      <c r="B62" s="19" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E62" s="24" t="inlineStr">
+      <c r="E63" s="24" t="inlineStr">
         <is>
           <t>Load test 100+ sites and 1,000 users; fix bottlenecks</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>1. Run the S6-04 load test at 100+ sites and 1,000 users.
 2. Find slow endpoints; add indexes or caching.
 3. Re-run until pages load in under 2 seconds.</t>
         </is>
       </c>
-      <c r="G62" s="19" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
         <is>
           <t>Proven performance at scale</t>
         </is>
       </c>
-      <c r="H62" s="19" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
         <is>
           <t>QA engineer</t>
         </is>
       </c>
-      <c r="I62" s="19" t="inlineStr">
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J62" s="19" t="inlineStr">
+      <c r="J63" s="19" t="inlineStr">
         <is>
           <t>Innovo: scalable</t>
         </is>
       </c>
-      <c r="K62" s="19" t="inlineStr">
+      <c r="K63" s="19" t="inlineStr">
         <is>
           <t>S5-04</t>
         </is>
       </c>
-      <c r="L62" s="19" t="n"/>
-      <c r="M62" s="19" t="n">
+      <c r="L63" s="19" t="n"/>
+      <c r="M63" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N62" s="25" t="inlineStr">
+      <c r="N63" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O62" s="19" t="inlineStr">
+      <c r="O63" s="19" t="inlineStr">
         <is>
           <t>Pages under 2 s at target load</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="23.85" customHeight="1" s="14">
-      <c r="A63" s="19" t="inlineStr">
+    <row r="64" ht="23.85" customHeight="1" s="14">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>S8-02</t>
         </is>
       </c>
-      <c r="B63" s="19" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E63" s="24" t="inlineStr">
+      <c r="E64" s="24" t="inlineStr">
         <is>
           <t>Backups, restore test, monitoring alerts (sync stopped, error spikes)</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>1. Turn on daily database backups; do one restore test.
 2. Alerts in Application Insights: sync stopped, error spike, slow responses.</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>Backups and alerts working</t>
         </is>
       </c>
-      <c r="H63" s="19" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J63" s="19" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>Risks</t>
-        </is>
-      </c>
-      <c r="K63" s="19" t="n"/>
-      <c r="L63" s="19" t="n"/>
-      <c r="M63" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N63" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O63" s="19" t="inlineStr">
-        <is>
-          <t>Restore proven; alert fires on stopped sync</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="35.05" customHeight="1" s="14">
-      <c r="A64" s="19" t="inlineStr">
-        <is>
-          <t>S8-03</t>
-        </is>
-      </c>
-      <c r="B64" s="19" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="C64" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>Accessibility and performance pass</t>
-        </is>
-      </c>
-      <c r="F64" s="19" t="inlineStr">
-        <is>
-          <t>1. Keyboard navigation and visible focus.
-2. Check contrast.
-3. Reduce bundle size; lazy-load heavy pages.</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>Accessible and fast</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>UI/UX designer</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>Quality</t>
         </is>
       </c>
       <c r="K64" s="19" t="n"/>
@@ -6425,14 +6433,14 @@
       </c>
       <c r="O64" s="19" t="inlineStr">
         <is>
-          <t>Keyboard navigation; fast first load</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="23.85" customHeight="1" s="14">
+          <t>Restore proven; alert fires on stopped sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="35.05" customHeight="1" s="14">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>S8-04</t>
+          <t>S8-03</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
@@ -6452,23 +6460,24 @@
       </c>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>Report a data issue link</t>
+          <t>Accessibility and performance pass</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
         <is>
-          <t>1. 'Report a data issue' link on data boxes.
-2. Sends the site, asset and description to the site/technical team contact.</t>
+          <t>1. Keyboard navigation and visible focus.
+2. Check contrast.
+3. Reduce bundle size; lazy-load heavy pages.</t>
         </is>
       </c>
       <c r="G65" s="19" t="inlineStr">
         <is>
-          <t>Data problems reach the right team</t>
+          <t>Accessible and fast</t>
         </is>
       </c>
       <c r="H65" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>UI/UX designer</t>
         </is>
       </c>
       <c r="I65" s="19" t="inlineStr">
@@ -6478,178 +6487,179 @@
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t>Risks: data quality</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="K65" s="19" t="n"/>
       <c r="L65" s="19" t="n"/>
       <c r="M65" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O65" s="19" t="inlineStr">
+        <is>
+          <t>Keyboard navigation; fast first load</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="23.85" customHeight="1" s="14">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>S8-04</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>Report a data issue link</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>1. 'Report a data issue' link on data boxes.
+2. Sends the site, asset and description to the site/technical team contact.</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>Data problems reach the right team</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>Risks: data quality</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="n"/>
+      <c r="L66" s="19" t="n"/>
+      <c r="M66" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N65" s="25" t="inlineStr">
+      <c r="N66" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O65" s="19" t="inlineStr">
+      <c r="O66" s="19" t="inlineStr">
         <is>
           <t>Sends issue to site/technical team contact</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="35.05" customHeight="1" s="14">
-      <c r="A66" s="19" t="inlineStr">
+    <row r="67" ht="35.05" customHeight="1" s="14">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>S8-05</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D66" s="19" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E66" s="24" t="inlineStr">
+      <c r="E67" s="24" t="inlineStr">
         <is>
           <t>Penetration test and fixes</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>1. Book an external penetration test.
 2. Fix all high and critical findings.
 3. Re-test.</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G67" s="19" t="inlineStr">
         <is>
           <t>Security signed off</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="H67" s="19" t="inlineStr">
         <is>
           <t>Security engineer</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="I67" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="J67" s="19" t="inlineStr">
         <is>
           <t>Innovo: security</t>
         </is>
       </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="K67" s="19" t="inlineStr">
         <is>
           <t>S7-05</t>
         </is>
       </c>
-      <c r="L66" s="19" t="inlineStr">
+      <c r="L67" s="19" t="inlineStr">
         <is>
           <t>External pen-test slot</t>
         </is>
       </c>
-      <c r="M66" s="19" t="n">
+      <c r="M67" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N66" s="25" t="inlineStr">
+      <c r="N67" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O66" s="19" t="inlineStr">
+      <c r="O67" s="19" t="inlineStr">
         <is>
           <t>No high or critical findings open</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="23.85" customHeight="1" s="14">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>S8-06</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="inlineStr">
-        <is>
-          <t>Pilot</t>
-        </is>
-      </c>
-      <c r="E67" s="24" t="inlineStr">
-        <is>
-          <t>Short user guide</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>1. One-page guide per role: how to find a project, read the boxes, open details.</t>
-        </is>
-      </c>
-      <c r="G67" s="19" t="inlineStr">
-        <is>
-          <t>User guide</t>
-        </is>
-      </c>
-      <c r="H67" s="19" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="I67" s="19" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="J67" s="19" t="inlineStr">
-        <is>
-          <t>Adoption</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="n"/>
-      <c r="L67" s="19" t="n"/>
-      <c r="M67" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N67" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O67" s="19" t="inlineStr">
-        <is>
-          <t>One-page guide per role</t>
         </is>
       </c>
     </row>
     <row r="68" ht="23.85" customHeight="1" s="14">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>S9-01</t>
+          <t>S8-06</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="C68" s="19" t="inlineStr">
@@ -6664,32 +6674,32 @@
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>Runbook and handover docs</t>
+          <t>Short user guide</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
         <is>
-          <t>1. Write: how to deploy, how to restore, how to add a new data source, who to call when DATOMS is down.</t>
+          <t>1. One-page guide per role: how to find a project, read the boxes, open details.</t>
         </is>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
-          <t>Runbook so anyone can operate Nexus</t>
+          <t>User guide</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>Backend developer</t>
+          <t>Product owner</t>
         </is>
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>You (backend)</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>Risks: knowledge</t>
+          <t>Adoption</t>
         </is>
       </c>
       <c r="K68" s="19" t="n"/>
@@ -6704,194 +6714,194 @@
       </c>
       <c r="O68" s="19" t="inlineStr">
         <is>
+          <t>One-page guide per role</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="23.85" customHeight="1" s="14">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>S9-01</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>Runbook and handover docs</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="inlineStr">
+        <is>
+          <t>1. Write: how to deploy, how to restore, how to add a new data source, who to call when DATOMS is down.</t>
+        </is>
+      </c>
+      <c r="G69" s="19" t="inlineStr">
+        <is>
+          <t>Runbook so anyone can operate Nexus</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>Risks: knowledge</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="n"/>
+      <c r="L69" s="19" t="n"/>
+      <c r="M69" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O69" s="19" t="inlineStr">
+        <is>
           <t>New developer can deploy from the docs</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="35.05" customHeight="1" s="14">
-      <c r="A69" s="19" t="inlineStr">
+    <row r="70" ht="35.05" customHeight="1" s="14">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>S9-02</t>
         </is>
       </c>
-      <c r="B69" s="19" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="C69" s="19" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E69" s="24" t="inlineStr">
+      <c r="E70" s="24" t="inlineStr">
         <is>
           <t>User acceptance testing on GHAFWOODS with pilot users</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>1. Give pilot users access on GHAFWOODS in **prod** (there is no test environment, ADR 0008): only pilot users are assigned to the Entra app during the pilot.
 2. Walk through each screen with them.
 3. Record issues in the backlog.</t>
         </is>
       </c>
-      <c r="G69" s="19" t="inlineStr">
+      <c r="G70" s="19" t="inlineStr">
         <is>
           <t>Pilot feedback list</t>
         </is>
       </c>
-      <c r="H69" s="19" t="inlineStr">
+      <c r="H70" s="19" t="inlineStr">
         <is>
           <t>Product owner</t>
         </is>
       </c>
-      <c r="I69" s="19" t="inlineStr">
+      <c r="I70" s="19" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="J69" s="19" t="inlineStr">
+      <c r="J70" s="19" t="inlineStr">
         <is>
           <t>Brief objectives</t>
         </is>
       </c>
-      <c r="K69" s="19" t="n"/>
-      <c r="L69" s="19" t="inlineStr">
+      <c r="K70" s="19" t="n"/>
+      <c r="L70" s="19" t="inlineStr">
         <is>
           <t>Pilot users' time</t>
         </is>
       </c>
-      <c r="M69" s="19" t="n">
+      <c r="M70" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N69" s="25" t="inlineStr">
+      <c r="N70" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O69" s="19" t="inlineStr">
+      <c r="O70" s="19" t="inlineStr">
         <is>
           <t>Pilot users sign off each screen</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="14">
-      <c r="A70" s="19" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="14">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>S9-03</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="C70" s="19" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E70" s="24" t="inlineStr">
+      <c r="E71" s="24" t="inlineStr">
         <is>
           <t>Bug fixes from pilot (backend)</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>1. Fix backend issues from the pilot, most important first.</t>
         </is>
       </c>
-      <c r="G70" s="19" t="inlineStr">
+      <c r="G71" s="19" t="inlineStr">
         <is>
           <t>Backend pilot issues closed</t>
         </is>
       </c>
-      <c r="H70" s="19" t="inlineStr">
+      <c r="H71" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I70" s="19" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J70" s="19" t="n"/>
-      <c r="K70" s="19" t="inlineStr">
-        <is>
-          <t>S9-02</t>
-        </is>
-      </c>
-      <c r="L70" s="19" t="n"/>
-      <c r="M70" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N70" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O70" s="19" t="inlineStr">
-        <is>
-          <t>All pilot blockers fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="23.85" customHeight="1" s="14">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>S9-04</t>
-        </is>
-      </c>
-      <c r="B71" s="19" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="C71" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>Pilot</t>
-        </is>
-      </c>
-      <c r="E71" s="24" t="inlineStr">
-        <is>
-          <t>Bug fixes from pilot (frontend)</t>
-        </is>
-      </c>
-      <c r="F71" s="19" t="inlineStr">
-        <is>
-          <t>1. Fix frontend issues from the pilot, most important first.</t>
-        </is>
-      </c>
-      <c r="G71" s="19" t="inlineStr">
-        <is>
-          <t>Frontend pilot issues closed</t>
-        </is>
-      </c>
-      <c r="H71" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I71" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
         </is>
       </c>
       <c r="J71" s="19" t="n"/>
@@ -6918,58 +6928,53 @@
     <row r="72" ht="23.85" customHeight="1" s="14">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>S10-01</t>
+          <t>S9-04</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W1–W2</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>Rollout</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>Connect all DATOMS sites to production; verify auto-linking</t>
+          <t>Bug fixes from pilot (frontend)</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
         <is>
-          <t>1. Point production at all DATOMS sites.
-2. Check every site links to the right project; clear the admin to-do list.</t>
+          <t>1. Fix frontend issues from the pilot, most important first.</t>
         </is>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
-          <t>All sites live</t>
+          <t>Frontend pilot issues closed</t>
         </is>
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>Data / integration engineer</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="I72" s="19" t="inlineStr">
         <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J72" s="19" t="inlineStr">
-        <is>
-          <t>Innovo: many sites</t>
-        </is>
-      </c>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J72" s="19" t="n"/>
       <c r="K72" s="19" t="inlineStr">
         <is>
-          <t>S9-03</t>
+          <t>S9-02</t>
         </is>
       </c>
       <c r="L72" s="19" t="n"/>
@@ -6983,128 +6988,132 @@
       </c>
       <c r="O72" s="19" t="inlineStr">
         <is>
-          <t>Every DATOMS site visible with correct project</t>
+          <t>All pilot blockers fixed</t>
         </is>
       </c>
     </row>
     <row r="73" ht="23.85" customHeight="1" s="14">
       <c r="A73" s="19" t="inlineStr">
         <is>
+          <t>S10-01</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>Connect all DATOMS sites to production; verify auto-linking</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>1. Point production at all DATOMS sites.
+2. Check every site links to the right project; clear the admin to-do list.</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>All sites live</t>
+        </is>
+      </c>
+      <c r="H73" s="19" t="inlineStr">
+        <is>
+          <t>Data / integration engineer</t>
+        </is>
+      </c>
+      <c r="I73" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: many sites</t>
+        </is>
+      </c>
+      <c r="K73" s="19" t="inlineStr">
+        <is>
+          <t>S9-03</t>
+        </is>
+      </c>
+      <c r="L73" s="19" t="n"/>
+      <c r="M73" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O73" s="19" t="inlineStr">
+        <is>
+          <t>Every DATOMS site visible with correct project</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="23.85" customHeight="1" s="14">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
           <t>S10-02</t>
         </is>
       </c>
-      <c r="B73" s="19" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D73" s="19" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Rollout</t>
         </is>
       </c>
-      <c r="E73" s="24" t="inlineStr">
+      <c r="E74" s="24" t="inlineStr">
         <is>
           <t>Production monitoring and cost review</t>
         </is>
       </c>
-      <c r="F73" s="19" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>1. Set Azure cost alerts.
 2. Review first month's cost and performance.</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>Running costs under control</t>
         </is>
       </c>
-      <c r="H73" s="19" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I73" s="19" t="inlineStr">
+      <c r="I74" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J73" s="19" t="inlineStr">
+      <c r="J74" s="19" t="inlineStr">
         <is>
           <t>Risks: cost</t>
-        </is>
-      </c>
-      <c r="K73" s="19" t="n"/>
-      <c r="L73" s="19" t="n"/>
-      <c r="M73" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N73" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O73" s="19" t="inlineStr">
-        <is>
-          <t>Cost alerts set; first monthly review done</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="23.85" customHeight="1" s="14">
-      <c r="A74" s="19" t="inlineStr">
-        <is>
-          <t>S10-03</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Rollout</t>
-        </is>
-      </c>
-      <c r="E74" s="24" t="inlineStr">
-        <is>
-          <t>Onboarding sessions with site teams</t>
-        </is>
-      </c>
-      <c r="F74" s="19" t="inlineStr">
-        <is>
-          <t>1. Short session per site team.
-2. Name a champion per site.</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="inlineStr">
-        <is>
-          <t>Site teams using Nexus</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="inlineStr">
-        <is>
-          <t>Adoption</t>
         </is>
       </c>
       <c r="K74" s="19" t="n"/>
@@ -7119,14 +7128,14 @@
       </c>
       <c r="O74" s="19" t="inlineStr">
         <is>
-          <t>Each site has a champion trained</t>
+          <t>Cost alerts set; first monthly review done</t>
         </is>
       </c>
     </row>
     <row r="75" ht="23.85" customHeight="1" s="14">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>S10-04</t>
+          <t>S10-03</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
@@ -7136,7 +7145,7 @@
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1–W2</t>
         </is>
       </c>
       <c r="D75" s="19" t="inlineStr">
@@ -7146,18 +7155,18 @@
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Phase 2 backlog grooming (reporting feed, BIM, AI)</t>
+          <t>Onboarding sessions with site teams</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
         <is>
-          <t>1. List phase 2 items (reporting feed, BIM, AI).
-2. Estimate and order them.</t>
+          <t>1. Short session per site team.
+2. Name a champion per site.</t>
         </is>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
-          <t>Phase 2 backlog ready</t>
+          <t>Site teams using Nexus</t>
         </is>
       </c>
       <c r="H75" s="19" t="inlineStr">
@@ -7172,13 +7181,13 @@
       </c>
       <c r="J75" s="19" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Adoption</t>
         </is>
       </c>
       <c r="K75" s="19" t="n"/>
       <c r="L75" s="19" t="n"/>
       <c r="M75" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N75" s="25" t="inlineStr">
         <is>
@@ -7187,14 +7196,14 @@
       </c>
       <c r="O75" s="19" t="inlineStr">
         <is>
-          <t>Phase 2 backlog estimated</t>
+          <t>Each site has a champion trained</t>
         </is>
       </c>
     </row>
     <row r="76" ht="23.85" customHeight="1" s="14">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>S10-05</t>
+          <t>S10-04</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
@@ -7204,7 +7213,7 @@
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>W1–W2</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
@@ -7214,60 +7223,130 @@
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>UI fixes from rollout feedback</t>
+          <t>Phase 2 backlog grooming (reporting feed, BIM, AI)</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>1. Fix UI feedback from rollout, most important first.</t>
+          <t>1. List phase 2 items (reporting feed, BIM, AI).
+2. Estimate and order them.</t>
         </is>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
-          <t>Rollout feedback closed</t>
+          <t>Phase 2 backlog ready</t>
         </is>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>Product owner</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J76" s="19" t="n"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>Future</t>
+        </is>
+      </c>
       <c r="K76" s="19" t="n"/>
       <c r="L76" s="19" t="n"/>
       <c r="M76" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O76" s="19" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="23.85" customHeight="1" s="14">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>S10-05</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>UI fixes from rollout feedback</t>
+        </is>
+      </c>
+      <c r="F77" s="19" t="inlineStr">
+        <is>
+          <t>1. Fix UI feedback from rollout, most important first.</t>
+        </is>
+      </c>
+      <c r="G77" s="19" t="inlineStr">
+        <is>
+          <t>Rollout feedback closed</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I77" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J77" s="19" t="n"/>
+      <c r="K77" s="19" t="n"/>
+      <c r="L77" s="19" t="n"/>
+      <c r="M77" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N76" s="25" t="inlineStr">
+      <c r="N77" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O76" s="19" t="inlineStr">
+      <c r="O77" s="19" t="inlineStr">
         <is>
           <t>Feedback items closed</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="14">
-      <c r="L78" s="16" t="inlineStr">
+    <row r="78" s="14"/>
+    <row r="79" ht="15" customHeight="1" s="14">
+      <c r="L79" s="16" t="inlineStr">
         <is>
           <t>Total days</t>
         </is>
       </c>
-      <c r="M78" s="16">
-        <f>SUM(M2:M76)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="M79" s="16">
+        <f>SUM(M2:M77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" s="14"/>
   </sheetData>
-  <autoFilter ref="A1:O76"/>
-  <conditionalFormatting sqref="A2:O76">
+  <autoFilter ref="A1:O77"/>
+  <conditionalFormatting sqref="A2:O77">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="4" text="" percent="0" bottom="0">
       <formula>$N2="Blocked"</formula>
     </cfRule>
@@ -7276,7 +7355,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="N2:N77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>DATOMS sample bulk response + bulk field list (Q21, Q22)</t>
+          <t>None to start S2-02 (DATOMS test key received 2026-10-12; bulk access checked in S2-02, Q34). Site field names still pending (Q21, Q22)</t>
         </is>
       </c>
       <c r="F4" s="19">
@@ -2688,8 +2688,8 @@
       <c r="F13" s="19" t="inlineStr">
         <is>
           <t>1. Turn on NestJS Swagger/OpenAPI generation.
-2. Publish the spec at /api/docs on dev.
-3. Generate a TypeScript client into packages/shared.
+2. Publish the spec at /docs and /openapi.json on local and dev (not in prod).
+3. Generate the typed client (openapi-typescript + openapi-fetch) into apps/web/src/api/.
 4. Show the frontend how to use it.</t>
         </is>
       </c>
@@ -3265,11 +3265,12 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>1. Read the v4 PDF, plus the DATOMS sample bulk response (Q21) and bulk field list (Q22) once received.
+          <t>1. Read the v4 PDF, docs/07 section 3 (test key, what DATOMS has shared) and docs/source/datoms-parameters.md (parameter keys, names and units for DG Set, Fuel Tank, AC Sub-Meter, Solar Inverter; seeded per source type, ADR 0011). Use the DATOMS sample bulk response (Q21) and bulk field list (Q22) once received.
 2. Build packages/datoms-client: list assets (catalogue) and the bulk endpoint (fleet and id mode) as the ONLY telemetry source (ADR 0010). data/latest is for CLI checks only.
-3. Put ALL field mapping in src/mapping.ts. Until the sample arrives, build against the v4 PDF shape. Save the sample to fixtures/ with tokens removed.
-4. Handle paging, 422 halving (with the learned page size), retries, rate limits, and the credit budget with budget.max_share (ADR 0005).
-5. Test against GHAFWOODS on dev using fixtures or a small id-mode subset (never the full fleet from dev).</t>
+3. Bulk check with the provisional test key (DATOMS_TOKEN only in the local .env; DATOMS_LIVE=true on a developer machine): make ONE bulk call in id mode with a few ids from the Asset List. Record the result in docs/07 section 3.3 and Q34 (no token, no headers). If bulk is enabled, save the response to fixtures/. If it is not, record that and keep the worker on fixtures; never fall back to data/latest (ADR 0010).
+4. Put ALL field mapping in src/mapping.ts. Until the sample arrives, build against the v4 PDF shape. Save recorded responses (Asset List, the bulk call) to fixtures/ with tokens and headers removed.
+5. Handle paging, 422 halving (with the learned page size), retries, rate limits, and the credit budget with budget.max_share (ADR 0005).
+6. Test against GHAFWOODS using fixtures or a small id-mode subset from a developer machine (never the full fleet; the test key is not in Key Vault, so the cloud dev worker stays on fixtures).</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -3295,7 +3296,7 @@
       <c r="K21" s="19" t="n"/>
       <c r="L21" s="19" t="inlineStr">
         <is>
-          <t>DATOMS sample bulk response (Q21) + bulk field list (Q22) + read-only key. Needed before this task starts; they do not block S0 or S1.</t>
+          <t>None. Unblocked 2026-10-12: DATOMS provisional read-only test key for org 20283 (valid until 10 Nov 2026). Checked inside this task: whether the bulk endpoint is enabled for the key (Q34). Still pending, not blocking: site, location, status and alert field names (Q21, Q22); those mappings stay empty ("no data yet") until they arrive.</t>
         </is>
       </c>
       <c r="M21" s="19" t="n">
@@ -3308,7 +3309,7 @@
       </c>
       <c r="O21" s="19" t="inlineStr">
         <is>
-          <t>Client reads the GHAFWOODS demo fleet (generators and tower cranes) through the bulk endpoint in dev; DATOMS field names exist only in src/mapping.ts</t>
+          <t>One bulk call made with the test key and its result recorded in docs/07 section 3.3 and Q34. If bulk is enabled: the client reads a small id-mode subset of the live fleet through the bulk endpoint. If not: the client's tests pass on fixtures and the worker stays on fixtures. Either way: no data/latest call outside scripts/, and DATOMS field names exist only in src/mapping.ts</t>
         </is>
       </c>
     </row>

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -2541,7 +2541,8 @@
 3. Raw telemetry is telemetry.packet: one jsonb row per asset packet, daily partitions (no TimescaleDB).
 4. Every asset has project_id and optional building/level/zone ids (what BIM links to later).
 5. Add pnpm db:migrate / db:check / db:seed; run the 100-site seed and record query timings.
-6. From the S1-02 security review (L3, accepted for now): when roles, project scope or active status change, clear the access cache on every API instance (Postgres LISTEN/NOTIFY or a per-user access version), check is_active on a cache hit, and never cache a load that started before the change.</t>
+6. From the S1-02 security review (L3, accepted for now): when roles, project scope or active status change, clear the access cache on every API instance (Postgres LISTEN/NOTIFY or a per-user access version), check is_active on a cache hit, and never cache a load that started before the change.
+7. Wire db/seeds/dev-login-roles.sql into pnpm db:seed for APP_ENV=local only: the runner skips it in every other environment and sets nexus.app_env before running it (the file refuses otherwise). It creates passwordless LOGIN users nexus_api_local / nexus_worker_local, members of nexus_api / nexus_worker from db/roles.sql, and needs a role that can create roles (locally the superuser nexus). Locally the api connects as nexus_api_local and the worker as nexus_worker_local, each with its own DATABASE_URL (docs/04).</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -768,27 +768,27 @@
         </is>
       </c>
       <c r="F2" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A2)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A2)</f>
         <v/>
       </c>
       <c r="G2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J2" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A2,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A2,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A2,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L2" s="20">
@@ -823,27 +823,27 @@
         </is>
       </c>
       <c r="F3" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A3)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A3)</f>
         <v/>
       </c>
       <c r="G3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A3,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A3,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A3,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L3" s="20">
@@ -878,27 +878,27 @@
         </is>
       </c>
       <c r="F4" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A4)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A4)</f>
         <v/>
       </c>
       <c r="G4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J4" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A4,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A4,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A4,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L4" s="20">
@@ -933,27 +933,27 @@
         </is>
       </c>
       <c r="F5" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A5)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A5)</f>
         <v/>
       </c>
       <c r="G5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J5" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A5,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A5,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A5,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L5" s="20">
@@ -988,27 +988,27 @@
         </is>
       </c>
       <c r="F6" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A6)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A6)</f>
         <v/>
       </c>
       <c r="G6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J6" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A6,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A6,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A6,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L6" s="20">
@@ -1043,27 +1043,27 @@
         </is>
       </c>
       <c r="F7" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A7)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A7)</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J7" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A7,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A7,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A7,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L7" s="20">
@@ -1098,27 +1098,27 @@
         </is>
       </c>
       <c r="F8" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A8)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A8)</f>
         <v/>
       </c>
       <c r="G8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J8" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A8,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A8,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A8,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L8" s="20">
@@ -1153,27 +1153,27 @@
         </is>
       </c>
       <c r="F9" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A9)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A9)</f>
         <v/>
       </c>
       <c r="G9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J9" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A9,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A9,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A9,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L9" s="20">
@@ -1208,27 +1208,27 @@
         </is>
       </c>
       <c r="F10" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A10)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A10)</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J10" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A10,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A10,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A10,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L10" s="20">
@@ -1263,27 +1263,27 @@
         </is>
       </c>
       <c r="F11" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A11)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A11)</f>
         <v/>
       </c>
       <c r="G11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J11" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A11,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A11,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A11,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L11" s="20">
@@ -1318,27 +1318,27 @@
         </is>
       </c>
       <c r="F12" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$77,A12)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$80,A12)</f>
         <v/>
       </c>
       <c r="G12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$I$2:$I$77,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$I$2:$I$80,"You (backend)")</f>
         <v/>
       </c>
       <c r="H12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$I$2:$I$77,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$I$2:$I$77,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$I$2:$I$80,"Both")</f>
         <v/>
       </c>
       <c r="J12" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$77,A12,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$B$2:$B$80,A12,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="K12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$77,Backlog!$B$2:$B$77,A12,Backlog!$N$2:$N$77,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$N$2:$N$80,"Done")</f>
         <v/>
       </c>
       <c r="L12" s="20">
@@ -1381,6 +1381,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="14">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -1419,6 +1420,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="14">
       <c r="A3" s="23" t="inlineStr">
         <is>
@@ -1476,11 +1478,11 @@
         </is>
       </c>
       <c r="E4" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B4)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B4)</f>
         <v/>
       </c>
       <c r="F4" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B4,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B4,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -1509,11 +1511,11 @@
         </is>
       </c>
       <c r="E5" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B5)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B5)</f>
         <v/>
       </c>
       <c r="F5" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B5,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B5,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -1542,11 +1544,11 @@
         </is>
       </c>
       <c r="E6" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B6)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B6)</f>
         <v/>
       </c>
       <c r="F6" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B6,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B6,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -1575,11 +1577,11 @@
         </is>
       </c>
       <c r="E7" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B7)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B7)</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B7,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B7,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -1608,11 +1610,11 @@
         </is>
       </c>
       <c r="E8" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B8)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B8)</f>
         <v/>
       </c>
       <c r="F8" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B8,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B8,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1641,11 +1643,11 @@
         </is>
       </c>
       <c r="E9" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B9)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B9)</f>
         <v/>
       </c>
       <c r="F9" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B9,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B9,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1674,11 +1676,11 @@
         </is>
       </c>
       <c r="E10" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B10)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B10)</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B10,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B10,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1707,11 +1709,11 @@
         </is>
       </c>
       <c r="E11" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$77,B11)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$80,B11)</f>
         <v/>
       </c>
       <c r="F11" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$77,B11,Backlog!$M$2:$M$77)</f>
+        <f>SUMIF(Backlog!$H$2:$H$80,B11,Backlog!$M$2:$M$80)</f>
         <v/>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1754,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="13" min="1" max="1"/>
@@ -2024,7 +2026,8 @@
         <is>
           <t>1. Create a pipeline that runs on every pull request: install, lint, test.
 2. On merge to main: build Docker images for api and worker, push to Azure Container Registry, deploy to Container Apps (dev).
-3. Test by merging a small change and seeing it live.</t>
+3. Test by merging a small change and seeing it live.
+4. Add `pnpm audit --prod` to the PR pipeline. Check whether `@vaadin/vaadin-usage-statistics` (pulled in by `@arcgis/core`) sends usage data at run time, and disable it if it does (security review of S0-09, item I6, 2026-10-14). This step needs no Azure access and is done ahead of the rest of S0-03.</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -2316,7 +2319,9 @@
         <is>
           <t>1. Create Azure Static Web App for dev.
 2. Add a pipeline: on merge to main, build and deploy apps/web.
-3. Check the dev URL works.</t>
+3. Check the dev URL works.
+4. The deploy must build with `pnpm --filter @nexus/web build`, so the build-time guards run (no MSW, no sample data, no dev key in `dist/`; security review of S0-09, item L2, 2026-10-14).
+5. The static host must serve HTTP/2 or later, with a long immutable cache for the hashed files under `assets/` and `assets/arcgis/*` (about 1,000 ArcGIS chunks; QA of S0-09, 2026-10-14).</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -2390,7 +2395,8 @@
           <t>1. Install MSAL React.
 2. Use the 'Nexus Web' client ID from S0-04.
 3. Sign-in button redirects to Microsoft; after sign-in show the user's name.
-4. Test with a user outside the Nexus groups: they must be refused.</t>
+4. Test with a user outside the Nexus groups: they must be refused.
+5. On sign-out: `queryClient.clear()` (drops the previous user's cached data) and `esriConfig.apiKey = undefined` through the map adapter (security review of S0-09, item I3, 2026-10-14).</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -3164,107 +3170,182 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="68.65000000000001" customHeight="1" s="14">
+    <row r="20" ht="91.05" customHeight="1" s="14">
       <c r="A20" s="19" t="inlineStr">
         <is>
+          <t>S1-10</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>Current user and client config endpoints: GET /v1/me and GET /v1/config</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>1. `GET /v1/me` (`@AnySignedIn`): the signed-in user's name, roles, permissions and project scope from the access context (docs/08 §5, docs/10).
+2. `GET /v1/config` (`@AnySignedIn`): feature flags, enums and the ArcGIS settings, including the per-environment ArcGIS key from config / Key Vault (docs/09, docs/10).
+3. Add both to OpenAPI and regenerate the typed web client; the web app's interim `/v1/config` and `/v1/projects` calls (S0-09 `pendingClient.ts`) switch to the typed client.
+(Added 2026-10-14 (architect S1 plan, decision D2).)</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>The web app can read who the user is and its runtime config from the API</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: permissions; Brief: interactive map</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="inlineStr">
+        <is>
+          <t>S1-09</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O20" s="19" t="inlineStr">
+        <is>
+          <t>Tests: `/v1/me` returns the caller's permissions and nothing else; `/v1/config` needs a valid sign-in and never returns a secret other than the referrer-restricted ArcGIS key; both appear in the generated client</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="68.65000000000001" customHeight="1" s="14">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>Projects API: list, filter (status, type, district), search, scoped to user</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>1. Create GET /projects with filters: status, type, district, search text.
 2. Apply the project-scope filter from S1-02.
 3. Return the fields DATOMS provides for each site (name, location, type, status).
-4. Add seed data for 5 sample sites so the frontend can work before DATOMS is connected.</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
+4. Add seed data for 5 sample sites so the frontend can work before DATOMS is connected.
+5. Do not read any project source column (`source_system`, `external_id`, `source_payload`, `*_seen_at` on `core.project`): ADR 0012 drops them in S3-09. Source ids are not part of the normal project response.</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>Projects list endpoint the map uses</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>Sheet: Top level</t>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr">
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>S1-02, S1-09</t>
         </is>
       </c>
-      <c r="L20" s="19" t="n"/>
-      <c r="M20" s="19" t="n">
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="25" t="inlineStr">
+      <c r="N21" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O20" s="19" t="inlineStr">
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>Returns only the user's projects; search under 300 ms</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="68.65000000000001" customHeight="1" s="14">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="22" ht="79.84999999999999" customHeight="1" s="14">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>S2-02</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>DATOMS API client: bulk endpoint, paging, retries, rate-limit and credit handling</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>1. Read the v4 PDF, docs/07 section 3 (test key, what DATOMS has shared) and docs/source/datoms-parameters.md (parameter keys, names and units for DG Set, Fuel Tank, AC Sub-Meter, Solar Inverter; seeded per source type, ADR 0011). Use the DATOMS sample bulk response (Q21) and bulk field list (Q22) once received.
 2. Build packages/datoms-client: list assets (catalogue) and the bulk endpoint (fleet and id mode) as the ONLY telemetry source (ADR 0010). data/latest is for CLI checks only.
@@ -3274,367 +3355,368 @@
 6. Test against GHAFWOODS using fixtures or a small id-mode subset from a developer machine (never the full fleet; the test key is not in Key Vault, so the cloud dev worker stays on fixtures).</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>Code that can talk to DATOMS</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>Brief: energy, crane utilisation</t>
         </is>
       </c>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="inlineStr">
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <t>None. Unblocked 2026-10-12: DATOMS provisional read-only test key for org 20283 (valid until 10 Nov 2026). Checked inside this task: whether the bulk endpoint is enabled for the key (Q34). Still pending, not blocking: site, location, status and alert field names (Q21, Q22); those mappings stay empty ("no data yet") until they arrive.</t>
         </is>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="M22" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="25" t="inlineStr">
+      <c r="N22" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>One bulk call made with the test key and its result recorded in docs/07 section 3.3 and Q34. If bulk is enabled: the client reads a small id-mode subset of the live fleet through the bulk endpoint. If not: the client's tests pass on fixtures and the worker stays on fixtures. Either way: no data/latest call outside scripts/, and DATOMS field names exist only in src/mapping.ts</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="79.84999999999999" customHeight="1" s="14">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="23" ht="46.25" customHeight="1" s="14">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>S2-03</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>Portfolio map (chosen provider, through the map wrapper): one pin per DATOMS site, coloured Active green, Central Store blue, Finished grey, In bid yellow where DATOMS gives the status</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1. Use the MapView wrapper with the ArcGIS adapter from S0-09.
 2. Show a UAE map.
 3. Call GET /projects and draw one pin per project.
 4. Colour pins: Active green, Central Store blue, Finished grey, In bid yellow (structure sheet).
-5. Click a pin = zoom to that project.</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
+5. Click a pin = zoom to that project.
+6. Acceptance is split (decision S2 D3): part A (no key, test data, stubbed tiles) is the merge gate. Part B runs when the ArcGIS key arrives (Q23): the real-key spec checks there are no failed `arcgis.com` / `basemaps3d` responses, the marker or cluster count equals the 10 sample projects, and a screenshot comparison passes (QA of S0-09, 2026-10-14).</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>Top-level portfolio map</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>Sheet: Top level</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr">
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>S0-09</t>
         </is>
       </c>
-      <c r="L22" s="19" t="n"/>
-      <c r="M22" s="19" t="n">
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="25" t="inlineStr">
+      <c r="N23" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>All projects shown; colours match the sheet; click zooms to project</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="46.25" customHeight="1" s="14">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24" ht="35.05" customHeight="1" s="14">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>S2-04</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Project list panel and summary tiles (projects, districts)</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>1. Left panel: list of sites with the details DATOMS provides (name, location, type, status).
 2. Two summary tiles at the top: number of projects, number of districts.
 3. Click a project in the list = same as clicking its pin.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>Project list beside the map</t>
         </is>
       </c>
-      <c r="H23" s="19" t="inlineStr">
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>Brief mockups</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n">
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="25" t="inlineStr">
+      <c r="N24" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="O24" s="19" t="inlineStr">
         <is>
           <t>List matches mockup: name, district, type tag, client, consultant, PM</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="35.05" customHeight="1" s="14">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="25" ht="46.25" customHeight="1" s="14">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>S2-05</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>Search and filters</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>1. Search box filters the list and pins by name.
 2. Filter chips: status, type, district.
 3. Filters call GET /projects with parameters.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>Users can find any project fast</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr">
         <is>
           <t>Brief mockups</t>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="K25" s="19" t="inlineStr">
         <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n">
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="25" t="inlineStr">
+      <c r="N25" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O24" s="19" t="inlineStr">
+      <c r="O25" s="19" t="inlineStr">
         <is>
           <t>Filter by status, type, district; search by name</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="46.25" customHeight="1" s="14">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26" ht="35.05" customHeight="1" s="14">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>Users and roles API: group-to-role mapping, project assignment, extra permissions</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing Entra groups and their Nexus role.
 2. Endpoints to assign users to projects. Keep room for extra permissions that later modules will need.
 3. Admin only; every change goes to the audit log.</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>Backend for managing access</t>
         </is>
       </c>
-      <c r="H25" s="19" t="inlineStr">
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K25" s="19" t="inlineStr">
+      <c r="K26" s="19" t="inlineStr">
         <is>
           <t>S1-02</t>
         </is>
       </c>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n">
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="25" t="inlineStr">
+      <c r="N26" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O25" s="19" t="inlineStr">
+      <c r="O26" s="19" t="inlineStr">
         <is>
           <t>Changes take effect on next request</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="35.05" customHeight="1" s="14">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="27" ht="46.25" customHeight="1" s="14">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>Catalogue sync (hourly): sites, devices, parameters, units</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1. Scheduled job in apps/worker, every hour (and early when the poll sees unknown ids).
 2. Read all DATOMS assets (list assets: names, nameplate). Sites, asset types and parameters (name, unit) come in the bulk rows. The live poll (S3-03) upserts them the same way, so the catalogue job spends no bulk credits.
@@ -3642,150 +3724,150 @@
 4. Retire safely (docs/07 section 6): only after a complete walk; only rows missed in 2 consecutive complete walks; retire nothing and alert if more than 5% would go.</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Nexus always knows every DATOMS site and device</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H27" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J27" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K26" s="19" t="inlineStr">
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>S2-02</t>
         </is>
       </c>
-      <c r="L26" s="19" t="inlineStr">
+      <c r="L27" s="19" t="inlineStr">
         <is>
           <t>DATOMS sample + field list (Q21, Q22) + read-only key; id stability (Q11)</t>
         </is>
       </c>
-      <c r="M26" s="19" t="n">
+      <c r="M27" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="25" t="inlineStr">
+      <c r="N27" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O26" s="19" t="inlineStr">
-        <is>
-          <t>New DATOMS site appears in Nexus within 1 hour</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="46.25" customHeight="1" s="14">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="O27" s="19" t="inlineStr">
+        <is>
+          <t>A new DATOMS asset appears in Nexus within 1 hour of being added to DATOMS, typed from its catalogue category (unmapped categories go to `generic` plus a to-do); assets are retired only by the safe-retire rule. New DATOMS **sites** appear only once DATOMS sends site data (Q21, Q22); until then admins create projects (S3-09). (Reworded 2026-10-14, ADR 0012.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="46.25" customHeight="1" s="14">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>S3-02</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>Auto-link new sites and devices on exact match; others to admin to-do list</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1. When a new DATOMS site appears, link it to a Nexus project if the name matches exactly.
 2. Otherwise add it to an 'unlinked' list for admins.
 3. Same for devices → assets.</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>New sites appear automatically, no guessing</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J27" s="19" t="inlineStr">
+      <c r="J28" s="19" t="inlineStr">
         <is>
           <t>Innovo: sites added automatically</t>
         </is>
       </c>
-      <c r="K27" s="19" t="inlineStr">
-        <is>
-          <t>S3-01</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n">
+      <c r="K28" s="19" t="inlineStr">
+        <is>
+          <t>S3-01, S3-09 (ADR 0012 link table). Exact-name matching follows the `linking.name_match` setting (off / suggest / auto, default suggest; ADR 0012).</t>
+        </is>
+      </c>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="25" t="inlineStr">
+      <c r="N28" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O27" s="19" t="inlineStr">
+      <c r="O28" s="19" t="inlineStr">
         <is>
           <t>No guessed links; unmatched items listed</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="46.25" customHeight="1" s="14">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="29" ht="57.45" customHeight="1" s="14">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>Live sync (every minute by default): bulk endpoint → packets, latest values, statuses, locations, alerts</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>1. Job every 60 s by default (per-type interval, ADR 0006): bulk endpoint only (ADR 0010). Fleet mode when every asset is due, otherwise id mode. In dev, only the configured subset (ADR 0005).
 2. Write telemetry.packet (history) and telemetry.latest_packet (current); status, location and alerts on change only.
@@ -3793,73 +3875,73 @@
 4. Log how long each run takes and the credits used per window.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Live DATOMS data in Nexus within about 2 poll intervals</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="J29" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K28" s="19" t="inlineStr">
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="L28" s="19" t="n"/>
-      <c r="M28" s="19" t="n">
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="25" t="inlineStr">
+      <c r="N29" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O28" s="19" t="inlineStr">
+      <c r="O29" s="19" t="inlineStr">
         <is>
           <t>Value in Nexus within 2 poll intervals of DATOMS (N-03)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="57.45" customHeight="1" s="14">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="30" ht="23.85" customHeight="1" s="14">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>S3-04</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>History backfill and gap repair after outages (ON HOLD)</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1. On first run, copy all past data from DATOMS (since Jul 2026 for GHAFWOODS).
 2. Record the last time synced per device.
@@ -3867,294 +3949,442 @@
 4. Test by stopping the worker for an hour.</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Full history, no gaps after outages</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="J30" s="19" t="inlineStr">
         <is>
           <t>Brief: trends</t>
         </is>
       </c>
-      <c r="K29" s="19" t="inlineStr">
+      <c r="K30" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L29" s="19" t="inlineStr">
+      <c r="L30" s="19" t="inlineStr">
         <is>
           <t>ON HOLD (decided 2026-10-08). The bulk endpoint has no history (ADR 0010); Nexus builds its own history from polls from day one. Needs a DATOMS history feed (Q12) and a new ADR to use it. Until then, gaps stay gaps and charts show coverage (ADR 0007).</t>
         </is>
       </c>
-      <c r="M29" s="19" t="n">
+      <c r="M30" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="25" t="inlineStr">
+      <c r="N30" s="25" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O29" s="19" t="inlineStr">
+      <c r="O30" s="19" t="inlineStr">
         <is>
           <t>GHAFWOODS history since Jul 2026 loaded; gaps refilled after a forced outage</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="14">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="31" ht="35.05" customHeight="1" s="14">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>S3-05</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>Device linking to-do list</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>1. Page listing unlinked DATOMS sites/devices (from S4-02).
 2. Admin picks the project/asset to link each one to.</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Admins link anything not matched automatically</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I30" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>Innovo: sites added automatically</t>
         </is>
       </c>
-      <c r="K30" s="19" t="inlineStr">
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>S3-02</t>
         </is>
       </c>
-      <c r="L30" s="19" t="n"/>
-      <c r="M30" s="19" t="n">
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="25" t="inlineStr">
+      <c r="N31" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O30" s="19" t="inlineStr">
+      <c r="O31" s="19" t="inlineStr">
         <is>
           <t>Admin links an unmatched device to a project</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="35.05" customHeight="1" s="14">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="32" ht="35.05" customHeight="1" s="14">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>S3-06</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>Integration health page: last sync, errors, delay</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>1. Page showing: last successful sync time, number of errors, delay in minutes.
 2. Red warning if the sync has stopped.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Admins see if DATOMS data is flowing</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="H32" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I32" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J32" s="19" t="inlineStr">
         <is>
           <t>Risks: DATOMS outage</t>
         </is>
       </c>
-      <c r="K31" s="19" t="inlineStr">
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n">
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="25" t="inlineStr">
+      <c r="N32" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O31" s="19" t="inlineStr">
+      <c r="O32" s="19" t="inlineStr">
         <is>
           <t>Shows a stopped sync clearly</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="35.05" customHeight="1" s="14">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="33" ht="35.05" customHeight="1" s="14">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>S3-07</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>Users and roles screen: group-to-role mapping, project assignment</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>1. Page listing groups and roles (from S3-09).
 2. Assign users to projects.
 3. Show each user's role and projects.</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Admins manage who sees what</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H33" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I32" s="19" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K32" s="19" t="inlineStr">
+      <c r="K33" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="L32" s="19" t="n"/>
-      <c r="M32" s="19" t="n">
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="25" t="inlineStr">
+      <c r="N33" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O32" s="19" t="inlineStr">
+      <c r="O33" s="19" t="inlineStr">
         <is>
           <t>Admin assigns a user to a project</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="46.25" customHeight="1" s="14">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="34" ht="35.05" customHeight="1" s="14">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>S3-08</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>DATOMS connector</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>Partition maintenance job: create future partitions, drop expired ones (critical)</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>1. Worker job `maintenance` (docs/07 §5), daily at 02:00 Asia/Dubai and once at start-up, leader only.
+2. Create partitions ahead for every partitioned table (raw packets, API-call log, events, audit log) using the existing SQL functions; drop partitions past retention through `drop_partitions_before` (with its audit floor).
+3. Record each run in `integration.sync_run` and raise a health warning when tomorrow's (or next month's) partition is missing.
+(Added 2026-10-14 (architect S1 plan, decision D4).)</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>Inserts never fail for lack of a partition; retention runs on its own</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>Data / integration engineer</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>Foundation; N-10 retention</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="inlineStr">
+        <is>
+          <t>S1-01, S3-01 (worker scheduler and leader lock)</t>
+        </is>
+      </c>
+      <c r="L34" s="19" t="n"/>
+      <c r="M34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O34" s="19" t="inlineStr">
+        <is>
+          <t>Integration test: with the clock moved forward 40 days, every partitioned table still accepts inserts and expired partitions are gone; a missing partition raises the health warning. Merged before or with S3-03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="46.25" customHeight="1" s="14">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>S3-09</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Admin console</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>Admin projects API (R-63): create and edit projects, assign DATOMS assets</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>1. Write ADR 0012 (project source identity, link table) first.
+2. `/v1/admin/projects`: create, edit and retire projects with the admin-held fields (name, location, district, state, type, client / consultant / PM); never delete (hard rule 8).
+3. Assign DATOMS assets to projects from the linking to-do; every change goes to the audit log.
+(Added 2026-10-14 (architect S2 plan, decisions D2 and D10).)</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>Admins can build the portfolio until DATOMS sends site data (Q21, Q22, Q43)</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>R-63</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>ADR 0012 (accepted 2026-10-14), S2-06, S3-01</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O35" s="19" t="inlineStr">
+        <is>
+          <t>An admin creates a project and links an asset to it; a non-admin gets 403; the change is in the audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="57.45" customHeight="1" s="14">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>Chart summaries (5-minute, 1-hour, 1-day) as Nexus rollup tables</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>1. Use the rollup functions in db/schema.sql: telemetry.refresh_rollup_5m and refresh_rollup_combine (1 h, 1 day in Asia/Dubai).
 2. Worker rollups job (ADR 0007): refresh_rollup_5m once per CLOSED 5-minute bucket, 2 poll intervals after it ends; re-run only for closed buckets that get late packets; 1 h after the hour's last bucket; 1 d after the Dubai day. No sliding window, no in-memory accumulators.
@@ -4162,291 +4392,291 @@
 4. Check a 30-day query returns in under 1 second.</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>Fast data for every chart</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr">
+      <c r="H36" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I36" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="J36" s="19" t="inlineStr">
         <is>
           <t>Brief: trends</t>
         </is>
       </c>
-      <c r="K33" s="19" t="inlineStr">
+      <c r="K36" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n">
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="25" t="inlineStr">
+      <c r="N36" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O33" s="19" t="inlineStr">
+      <c r="O36" s="19" t="inlineStr">
         <is>
           <t>30-day chart query under 1 s</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="46.25" customHeight="1" s="14">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="37" ht="57.45" customHeight="1" s="14">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>S4-02</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>Live push: status changes sent to open browsers (Web PubSub)</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>1. When the worker sees a status or location change, publish a slim message to Azure Web PubSub (per project group): no parameter values; values.updated hint; summary.updated; chunked well under 1 MB (docs/10, ADR 0008).
 2. API gives the browser a Web PubSub token with no group-join rights. POST /v1/live/subscriptions checks permission and scope, then joins the connection to project groups on the server.
 3. On any Nexus access change, close the affected live connections so clients re-subscribe through the scope check. Settle with the security-reviewer how the API confirms a connectionId belongs to the caller.</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Changes pushed to browsers live</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H37" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I34" s="19" t="inlineStr">
+      <c r="I37" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="J37" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K34" s="19" t="inlineStr">
+      <c r="K37" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L34" s="19" t="n"/>
-      <c r="M34" s="19" t="n">
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N34" s="25" t="inlineStr">
+      <c r="N37" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O34" s="19" t="inlineStr">
+      <c r="O37" s="19" t="inlineStr">
         <is>
           <t>Pin colour changes without refresh; a user whose project access is removed stops receiving that project's messages at once; nothing project-specific is sent to the portfolio group</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="46.25" customHeight="1" s="14">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="38" ht="35.05" customHeight="1" s="14">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>S4-03</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Project summary APIs for the equipment and energy info boxes</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>1. Endpoints GET /projects/{id}/equipment/summary (Box 2) and GET /projects/{id}/energy/summary (Box 3), as in docs/10.
 2. Fill them from the latest DATOMS values: equipment counts from kind = 'physical' assets; energy site totals from site_metric records when DATOMS provides them. Manpower and materials are not built (slots only).</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>The project page loads its boxes</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H38" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I38" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="J38" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info boxes</t>
         </is>
       </c>
-      <c r="K35" s="19" t="inlineStr">
+      <c r="K38" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n">
+      <c r="L38" s="19" t="n"/>
+      <c r="M38" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N35" s="25" t="inlineStr">
+      <c r="N38" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O35" s="19" t="inlineStr">
+      <c r="O38" s="19" t="inlineStr">
         <is>
           <t>The two endpoints return Box 2 and Box 3 as reported; Boxes 1 and 4 are "coming later" slots</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="57.45" customHeight="1" s="14">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="39" ht="35.05" customHeight="1" s="14">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>S4-04</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E39" s="24" t="inlineStr">
         <is>
           <t>Project page layout: site map, side panel, equipment and energy info boxes (space kept for manpower and materials later)</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>1. Project page: site map in the centre, equipment and energy info boxes on the right (as structure sheet level 1); leave space for manpower and materials.
 2. Load data from S5-03.
 3. Back button returns to the portfolio map.</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>Level 1 project page</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H39" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr">
+      <c r="I39" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="J39" s="19" t="inlineStr">
         <is>
           <t>Sheet: Level 1</t>
         </is>
       </c>
-      <c r="K36" s="19" t="inlineStr">
+      <c r="K39" s="19" t="inlineStr">
         <is>
           <t>S4-03</t>
         </is>
       </c>
-      <c r="L36" s="19" t="n"/>
-      <c r="M36" s="19" t="n">
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="25" t="inlineStr">
+      <c r="N39" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O36" s="19" t="inlineStr">
+      <c r="O39" s="19" t="inlineStr">
         <is>
           <t>Matches structure sheet level 1</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="57.45" customHeight="1" s="14">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="40" ht="57.45" customHeight="1" s="14">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>S4-05</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>Asset pins: icon per type, colour per DATOMS status, clustering, map/satellite switch</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>1. Draw one pin per equipment asset (kind = 'physical') at its DATOMS location; no location = "Not on map".
 2. Icon by type: tower crane, hoist, equipment, generator; unknown types use the generic icon.
@@ -4454,325 +4684,105 @@
 4. Turn on clustering and a Map/Satellite switch. 3D uses the same icons with no callouts or pulse (ADR 0008).</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
         <is>
           <t>Live equipment pins on the site map</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H40" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J37" s="19" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 blinkers on map</t>
         </is>
       </c>
-      <c r="K37" s="19" t="inlineStr">
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L37" s="19" t="inlineStr">
+      <c r="L40" s="19" t="inlineStr">
         <is>
           <t>Bulk field names for location + status (Q22; DATOMS confirmed the data is in the bulk response); blink vs pulse (Q19)</t>
         </is>
       </c>
-      <c r="M37" s="19" t="n">
+      <c r="M40" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N37" s="25" t="inlineStr">
+      <c r="N40" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O37" s="19" t="inlineStr">
+      <c r="O40" s="19" t="inlineStr">
         <is>
           <t>Running green, Idle amber, Maintenance red, Off grey as reported</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="35.05" customHeight="1" s="14">
-      <c r="A38" s="19" t="inlineStr">
+    <row r="41" ht="35.05" customHeight="1" s="14">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>S4-06</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>Live updates on pins and boxes (WebSocket)</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>1. Connect to Web PubSub with the token from the API.
 2. When a message arrives, update that pin's colour and the info box numbers without reloading.</t>
         </is>
       </c>
-      <c r="G38" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
         <is>
           <t>Map and boxes update live</t>
         </is>
       </c>
-      <c r="H38" s="19" t="inlineStr">
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I38" s="19" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J38" s="19" t="inlineStr">
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K38" s="19" t="inlineStr">
+      <c r="K41" s="19" t="inlineStr">
         <is>
           <t>S4-02</t>
-        </is>
-      </c>
-      <c r="L38" s="19" t="n"/>
-      <c r="M38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O38" s="19" t="inlineStr">
-        <is>
-          <t>Update visible within a minute</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="35.05" customHeight="1" s="14">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>S4-07</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Project page</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>Asset side panel: live readings, faults, last run</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>1. Click a pin = side panel with the asset's latest readings, faults and last run.
-2. Link to the equipment detail page.</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>Asset details on click</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I39" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>DATOMS parity</t>
-        </is>
-      </c>
-      <c r="K39" s="19" t="inlineStr">
-        <is>
-          <t>S4-03</t>
-        </is>
-      </c>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O39" s="19" t="inlineStr">
-        <is>
-          <t>Opens on pin click</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="57.45" customHeight="1" s="14">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>S5-01</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>Energy API: generators, solar, mains, loads by area, site totals and CO2 as reported by DATOMS</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>1. Endpoint returning per project: generators (running/total), solar generation, mains, total load, loads by area, site totals and CO2 exactly as DATOMS gives them in the bulk response. Site totals are read from site_metric records (ADR 0009); anything missing shows "no data yet".
-2. Compare with the DATOMS Site View for GHAFWOODS; numbers must match.</t>
-        </is>
-      </c>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>Energy data for box 3 and the energy page</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>Brief: energy monitoring; Sheet: L2 Energy</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>S3-03</t>
-        </is>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>Whether DATOMS has site totals (Q3); bulk field names (Q22)</t>
-        </is>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O40" s="19" t="inlineStr">
-        <is>
-          <t>Figures match DATOMS Site View for GHAFWOODS</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="35.05" customHeight="1" s="14">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>S5-02</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>Energy equipment table data incl. owned / hired</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>1. Endpoint listing energy equipment: DG ID, description, type (DG/solar/mains), status, owned or hired.
-2. Ownership comes from a DATOMS field (R-31). If DATOMS lacks it, the column is hidden and reported (Q3). Nexus doesn't keep its own ownership register.</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="inlineStr">
-        <is>
-          <t>Data for the energy table</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Energy</t>
-        </is>
-      </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>S5-01</t>
         </is>
       </c>
       <c r="L41" s="19" t="n"/>
@@ -4786,19 +4796,19 @@
       </c>
       <c r="O41" s="19" t="inlineStr">
         <is>
-          <t>DG ID, description, status, ownership returned</t>
+          <t>Update visible within a minute</t>
         </is>
       </c>
     </row>
     <row r="42" ht="23.85" customHeight="1" s="14">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>S5-03</t>
+          <t>S4-07</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
@@ -4808,48 +4818,48 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Project page</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>Trend endpoints: day, week, month, year from summaries</t>
+          <t>Asset side panel: live readings, faults, last run</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>1. Endpoints for trends by day, week, month, year.
-2. Read from the rollup tables (S4-01), never raw readings for ranges over 6 h. 5-minute data only within 60 days; older ranges use hourly. Return the resolution used and data coverage per bucket.</t>
+          <t>1. Click a pin = side panel with the asset's latest readings, faults and last run.
+2. Link to the equipment detail page.</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>Trend data for charts</t>
+          <t>Asset details on click</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>Backend developer</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>You (backend)</t>
+          <t>Colleague (frontend)</t>
         </is>
       </c>
       <c r="J42" s="19" t="inlineStr">
         <is>
-          <t>Sheet: L2 trend graphs</t>
+          <t>DATOMS parity</t>
         </is>
       </c>
       <c r="K42" s="19" t="inlineStr">
         <is>
-          <t>S4-01</t>
+          <t>S4-03</t>
         </is>
       </c>
       <c r="L42" s="19" t="n"/>
       <c r="M42" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" s="25" t="inlineStr">
         <is>
@@ -4858,14 +4868,14 @@
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
-          <t>Each range under 1 s</t>
+          <t>Opens on pin click</t>
         </is>
       </c>
     </row>
     <row r="43" ht="35.05" customHeight="1" s="14">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>S5-04</t>
+          <t>S5-01</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
@@ -4875,33 +4885,33 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>Load-test harness: simulate 100+ sites and 1,000 users</t>
+          <t>Energy API: generators, solar, mains, loads by area, site totals and CO2 as reported by DATOMS</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>1. Write a script (e.g. k6) that simulates 100+ sites of data and 1,000 users opening pages.
-2. Run it against dev and record response times.</t>
+          <t>1. Endpoint returning per project: generators (running/total), solar generation, mains, total load, loads by area, site totals and CO2 exactly as DATOMS gives them in the bulk response. Site totals are read from site_metric records (ADR 0009); anything missing shows "no data yet".
+2. Compare with the DATOMS Site View for GHAFWOODS; numbers must match.</t>
         </is>
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>Repeatable load test</t>
+          <t>Energy data for box 3 and the energy page</t>
         </is>
       </c>
       <c r="H43" s="19" t="inlineStr">
         <is>
-          <t>QA engineer</t>
+          <t>Backend developer</t>
         </is>
       </c>
       <c r="I43" s="19" t="inlineStr">
@@ -4911,13 +4921,21 @@
       </c>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t>Innovo: scalable</t>
-        </is>
-      </c>
-      <c r="K43" s="19" t="n"/>
-      <c r="L43" s="19" t="n"/>
+          <t>Brief: energy monitoring; Sheet: L2 Energy</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="inlineStr">
+        <is>
+          <t>S3-03</t>
+        </is>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>Whether DATOMS has site totals (Q3); bulk field names (Q22)</t>
+        </is>
+      </c>
       <c r="M43" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43" s="25" t="inlineStr">
         <is>
@@ -4926,14 +4944,14 @@
       </c>
       <c r="O43" s="19" t="inlineStr">
         <is>
-          <t>Repeatable test script in repo</t>
+          <t>Figures match DATOMS Site View for GHAFWOODS</t>
         </is>
       </c>
     </row>
     <row r="44" ht="35.05" customHeight="1" s="14">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>S5-05</t>
+          <t>S5-02</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
@@ -4953,38 +4971,38 @@
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>Info box 3 Energy</t>
+          <t>Energy equipment table data incl. owned / hired</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>1. Info box 3 on the project page: DGs running/total, total energy load, solar generation, main:solar ratio (structure sheet).
-2. Click = open energy detail.</t>
+          <t>1. Endpoint listing energy equipment: DG ID, description, type (DG/solar/mains), status, owned or hired.
+2. Ownership comes from a DATOMS field (R-31). If DATOMS lacks it, the column is hidden and reported (Q3). Nexus doesn't keep its own ownership register.</t>
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>Energy info box</t>
+          <t>Data for the energy table</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>Backend developer</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
+          <t>You (backend)</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>Sheet: L1 Info box 3</t>
+          <t>Sheet: L2 Energy</t>
         </is>
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>S4-03</t>
+          <t>S5-01</t>
         </is>
       </c>
       <c r="L44" s="19" t="n"/>
@@ -4998,14 +5016,14 @@
       </c>
       <c r="O44" s="19" t="inlineStr">
         <is>
-          <t>DG running state, energy load, solar, main:solar ratio</t>
+          <t>DG ID, description, status, ownership returned</t>
         </is>
       </c>
     </row>
     <row r="45" ht="23.85" customHeight="1" s="14">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>S5-06</t>
+          <t>S5-03</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
@@ -5015,7 +5033,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -5025,43 +5043,43 @@
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>Energy detail: top ribbon of metrics</t>
+          <t>Trend endpoints: day, week, month, year from summaries</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
         <is>
-          <t>1. Top ribbon on the energy page with the key energy numbers.
-2. Data from S6-01.</t>
+          <t>1. Endpoints for trends by day, week, month, year.
+2. Read from the rollup tables (S4-01), never raw readings for ranges over 6 h. 5-minute data only within 60 days; older ranges use hourly. Return the resolution used and data coverage per bucket.</t>
         </is>
       </c>
       <c r="G45" s="19" t="inlineStr">
         <is>
-          <t>Energy summary ribbon</t>
+          <t>Trend data for charts</t>
         </is>
       </c>
       <c r="H45" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>Backend developer</t>
         </is>
       </c>
       <c r="I45" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
+          <t>You (backend)</t>
         </is>
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t>Sheet: L2 Energy</t>
+          <t>Sheet: L2 trend graphs</t>
         </is>
       </c>
       <c r="K45" s="19" t="inlineStr">
         <is>
-          <t>S5-01</t>
+          <t>S4-01</t>
         </is>
       </c>
       <c r="L45" s="19" t="n"/>
       <c r="M45" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" s="25" t="inlineStr">
         <is>
@@ -5070,14 +5088,14 @@
       </c>
       <c r="O45" s="19" t="inlineStr">
         <is>
-          <t>Matches sheet</t>
+          <t>Each range under 1 s</t>
         </is>
       </c>
     </row>
     <row r="46" ht="23.85" customHeight="1" s="14">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>S5-07</t>
+          <t>S5-04</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
@@ -5087,50 +5105,46 @@
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>W1–W2</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>Energy equipment table</t>
+          <t>Load-test harness: simulate 100+ sites and 1,000 users</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>1. Table: DG ID, description, status, ownership (owned/hired), running/off.
-2. Sort and filter.</t>
+          <t>1. Write a script (e.g. k6) that simulates 100+ sites of data and 1,000 users opening pages.
+2. Run it against dev and record response times.</t>
         </is>
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>Energy equipment table</t>
+          <t>Repeatable load test</t>
         </is>
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>QA engineer</t>
         </is>
       </c>
       <c r="I46" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
+          <t>You (backend)</t>
         </is>
       </c>
       <c r="J46" s="19" t="inlineStr">
         <is>
-          <t>Sheet: L2 Energy</t>
-        </is>
-      </c>
-      <c r="K46" s="19" t="inlineStr">
-        <is>
-          <t>S5-02</t>
-        </is>
-      </c>
+          <t>Innovo: scalable</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n"/>
       <c r="L46" s="19" t="n"/>
       <c r="M46" s="19" t="n">
         <v>2</v>
@@ -5142,834 +5156,1051 @@
       </c>
       <c r="O46" s="19" t="inlineStr">
         <is>
-          <t>Sortable; status live</t>
+          <t>Repeatable test script in repo</t>
         </is>
       </c>
     </row>
     <row r="47" ht="35.05" customHeight="1" s="14">
       <c r="A47" s="19" t="inlineStr">
         <is>
+          <t>S5-05</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>Info box 3 Energy</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>1. Info box 3 on the project page: DGs running/total, total energy load, solar generation, main:solar ratio (structure sheet).
+2. Click = open energy detail.</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>Energy info box</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L1 Info box 3</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="inlineStr">
+        <is>
+          <t>S4-03</t>
+        </is>
+      </c>
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O47" s="19" t="inlineStr">
+        <is>
+          <t>DG running state, energy load, solar, main:solar ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="35.05" customHeight="1" s="14">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>S5-06</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>Energy detail: top ribbon of metrics</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>1. Top ribbon on the energy page with the key energy numbers.
+2. Data from S6-01.</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>Energy summary ribbon</t>
+        </is>
+      </c>
+      <c r="H48" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L2 Energy</t>
+        </is>
+      </c>
+      <c r="K48" s="19" t="inlineStr">
+        <is>
+          <t>S5-01</t>
+        </is>
+      </c>
+      <c r="L48" s="19" t="n"/>
+      <c r="M48" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O48" s="19" t="inlineStr">
+        <is>
+          <t>Matches sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35.05" customHeight="1" s="14">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>S5-07</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>Energy equipment table</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>1. Table: DG ID, description, status, ownership (owned/hired), running/off.
+2. Sort and filter.</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>Energy equipment table</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L2 Energy</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>S5-02</t>
+        </is>
+      </c>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O49" s="19" t="inlineStr">
+        <is>
+          <t>Sortable; status live</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35.05" customHeight="1" s="14">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
           <t>S5-08</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>Energy charts: load trends, distribution, solar trends</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>1. Charts: load trend, load distribution, solar trend.
 2. Range buttons: day, week, month, year.
 3. Data from S6-03.</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>Energy charts</t>
         </is>
       </c>
-      <c r="H47" s="19" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I47" s="19" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K47" s="19" t="inlineStr">
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>S5-03</t>
         </is>
       </c>
-      <c r="L47" s="19" t="n"/>
-      <c r="M47" s="19" t="n">
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N47" s="25" t="inlineStr">
+      <c r="N50" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O47" s="19" t="inlineStr">
+      <c r="O50" s="19" t="inlineStr">
         <is>
           <t>Range switch day/week/month/year</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="35.05" customHeight="1" s="14">
-      <c r="A48" s="19" t="inlineStr">
+    <row r="51" ht="35.05" customHeight="1" s="14">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D48" s="19" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>Equipment API: ID, name, type, make/model, status + native DATOMS fields</t>
         </is>
       </c>
-      <c r="F48" s="19" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing equipment per project (kind = 'physical' only): ID, name, type, make/model, current status, plus extra nameplate fields as optional columns.
 2. Every parameter DATOMS sends for a device is available from GET /assets/{id} (device card). The list endpoint carries no live values (ADR 0008).</t>
         </is>
       </c>
-      <c r="G48" s="19" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>Data for the equipment table</t>
         </is>
       </c>
-      <c r="H48" s="19" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J48" s="19" t="inlineStr">
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t>Brief: crane utilisation, asset tracking; Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K48" s="19" t="inlineStr">
+      <c r="K51" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L48" s="19" t="n"/>
-      <c r="M48" s="19" t="n">
+      <c r="L51" s="19" t="n"/>
+      <c r="M51" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N48" s="25" t="inlineStr">
+      <c r="N51" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O48" s="19" t="inlineStr">
+      <c r="O51" s="19" t="inlineStr">
         <is>
           <t>All DATOMS parameters available per asset</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="35.05" customHeight="1" s="14">
-      <c r="A49" s="19" t="inlineStr">
+    <row r="52" ht="35.05" customHeight="1" s="14">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>S6-02</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>Device card API: latest values, today's running timeline</t>
         </is>
       </c>
-      <c r="F49" s="19" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint for one device: latest values of every parameter.
 2. Today's timeline of status changes (running, idle, off) as observed by Nexus in polls, labelled "observed by Nexus" (ADR 0007). DATOMS's own status history is used only if a later ADR adds it.</t>
         </is>
       </c>
-      <c r="G49" s="19" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>Data for the device card</t>
         </is>
       </c>
-      <c r="H49" s="19" t="inlineStr">
+      <c r="H52" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I49" s="19" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="J52" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K49" s="19" t="inlineStr">
+      <c r="K52" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="L49" s="19" t="n"/>
-      <c r="M49" s="19" t="n">
+      <c r="L52" s="19" t="n"/>
+      <c r="M52" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="25" t="inlineStr">
+      <c r="N52" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O49" s="19" t="inlineStr">
+      <c r="O52" s="19" t="inlineStr">
         <is>
           <t>Timeline shows the status changes Nexus observed, labelled "observed by Nexus", accurate to one poll interval</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="35.05" customHeight="1" s="14">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="53" ht="35.05" customHeight="1" s="14">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>S6-03</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D53" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E53" s="24" t="inlineStr">
         <is>
           <t>Info box 2 counts: tower cranes, hoists, all equipment (total / idle)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>1. Counts per project (kind = 'physical' only): tower cranes total/idle, hoists total/idle, all equipment total/idle, using DATOMS statuses.
 2. Add to the project summary (S5-03).</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="G53" s="19" t="inlineStr">
         <is>
           <t>Numbers for info box 2</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="H53" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="I53" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J50" s="19" t="inlineStr">
+      <c r="J53" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 2</t>
         </is>
       </c>
-      <c r="K50" s="19" t="inlineStr">
+      <c r="K53" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="L50" s="19" t="n"/>
-      <c r="M50" s="19" t="n">
+      <c r="L53" s="19" t="n"/>
+      <c r="M53" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="25" t="inlineStr">
+      <c r="N53" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O50" s="19" t="inlineStr">
+      <c r="O53" s="19" t="inlineStr">
         <is>
           <t>Counts follow DATOMS statuses</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="35.05" customHeight="1" s="14">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="54" ht="23.85" customHeight="1" s="14">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>S6-04</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>Notifications from the DATOMS bulk response, and API (filter by site, asset, type)</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>1. In the live poll: take DATOMS alerts and faults from the bulk response (ADR 0010; no separate events job).
 2. Store them; endpoint to list with filters: site, asset, type, date. "Mark all read" moves a read marker (docs/06 section 3, item 11).
 3. Show them exactly as DATOMS sends them.</t>
         </is>
       </c>
-      <c r="G51" s="19" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>Notifications in Nexus</t>
         </is>
       </c>
-      <c r="H51" s="19" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I51" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J51" s="19" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>Innovo: alerts as they come</t>
         </is>
       </c>
-      <c r="K51" s="19" t="inlineStr">
+      <c r="K54" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L51" s="19" t="inlineStr">
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>Alert field names in the bulk response (Q22)</t>
         </is>
       </c>
-      <c r="M51" s="19" t="n">
+      <c r="M54" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N51" s="25" t="inlineStr">
+      <c r="N54" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O51" s="19" t="inlineStr">
+      <c r="O54" s="19" t="inlineStr">
         <is>
           <t>Same notifications as DATOMS, newest first</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="35.05" customHeight="1" s="14">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="55" ht="23.85" customHeight="1" s="14">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>S6-05</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D52" s="19" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>Info box 2 component</t>
         </is>
       </c>
-      <c r="F52" s="19" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>1. Info box 2: tower cranes count/idle, hoists count/idle, total equipment/idle (structure sheet).
 2. Click = open equipment detail.</t>
         </is>
       </c>
-      <c r="G52" s="19" t="inlineStr">
+      <c r="G55" s="19" t="inlineStr">
         <is>
           <t>Equipment info box</t>
         </is>
       </c>
-      <c r="H52" s="19" t="inlineStr">
+      <c r="H55" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I52" s="19" t="inlineStr">
+      <c r="I55" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="J55" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 2</t>
         </is>
       </c>
-      <c r="K52" s="19" t="inlineStr">
+      <c r="K55" s="19" t="inlineStr">
         <is>
           <t>S6-03</t>
         </is>
       </c>
-      <c r="L52" s="19" t="n"/>
-      <c r="M52" s="19" t="n">
+      <c r="L55" s="19" t="n"/>
+      <c r="M55" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="25" t="inlineStr">
+      <c r="N55" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O52" s="19" t="inlineStr">
+      <c r="O55" s="19" t="inlineStr">
         <is>
           <t>Count / idle per type</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="35.05" customHeight="1" s="14">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="56" ht="46.25" customHeight="1" s="14">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>S6-06</t>
         </is>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D53" s="19" t="inlineStr">
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E53" s="24" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>Equipment detail table: sort, filter by type and status</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>1. Table with Equipment ID, Name, Type, Model/Make, Current Status + extra DATOMS fields.
 2. Filter by type and status; sort; search.</t>
         </is>
       </c>
-      <c r="G53" s="19" t="inlineStr">
+      <c r="G56" s="19" t="inlineStr">
         <is>
           <t>Equipment detail page</t>
         </is>
       </c>
-      <c r="H53" s="19" t="inlineStr">
+      <c r="H56" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I53" s="19" t="inlineStr">
+      <c r="I56" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K53" s="19" t="inlineStr">
+      <c r="K56" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="L53" s="19" t="n"/>
-      <c r="M53" s="19" t="n">
+      <c r="L56" s="19" t="n"/>
+      <c r="M56" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N53" s="25" t="inlineStr">
+      <c r="N56" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O53" s="19" t="inlineStr">
+      <c r="O56" s="19" t="inlineStr">
         <is>
           <t>All sheet columns plus native fields</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="23.85" customHeight="1" s="14">
-      <c r="A54" s="19" t="inlineStr">
+    <row r="57" ht="79.84999999999999" customHeight="1" s="14">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>S6-07</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>Device card</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>1. Card opened from a table row or a map pin.
 2. Shows all latest values and today's timeline.</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="G57" s="19" t="inlineStr">
         <is>
           <t>Device card</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J54" s="19" t="inlineStr">
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K54" s="19" t="inlineStr">
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <t>S6-02</t>
         </is>
       </c>
-      <c r="L54" s="19" t="n"/>
-      <c r="M54" s="19" t="n">
+      <c r="L57" s="19" t="n"/>
+      <c r="M57" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N54" s="25" t="inlineStr">
+      <c r="N57" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O54" s="19" t="inlineStr">
+      <c r="O57" s="19" t="inlineStr">
         <is>
           <t>Opens from table row or pin</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="23.85" customHeight="1" s="14">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="58" ht="57.45" customHeight="1" s="14">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>S6-08</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E58" s="24" t="inlineStr">
         <is>
           <t>Notifications bell and list with filters</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>1. Bell in header shows unread count.
 2. Click = list of notifications, newest first, with filters.</t>
         </is>
       </c>
-      <c r="G55" s="19" t="inlineStr">
+      <c r="G58" s="19" t="inlineStr">
         <is>
           <t>Notifications in the header</t>
         </is>
       </c>
-      <c r="H55" s="19" t="inlineStr">
+      <c r="H58" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I55" s="19" t="inlineStr">
+      <c r="I58" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="J58" s="19" t="inlineStr">
         <is>
           <t>Innovo: alerts as they come</t>
         </is>
       </c>
-      <c r="K55" s="19" t="inlineStr">
+      <c r="K58" s="19" t="inlineStr">
         <is>
           <t>S6-04</t>
         </is>
       </c>
-      <c r="L55" s="19" t="n"/>
-      <c r="M55" s="19" t="n">
+      <c r="L58" s="19" t="n"/>
+      <c r="M58" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N55" s="25" t="inlineStr">
+      <c r="N58" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O55" s="19" t="inlineStr">
+      <c r="O58" s="19" t="inlineStr">
         <is>
           <t>Unread count; filter by site and asset</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="46.25" customHeight="1" s="14">
-      <c r="A56" s="19" t="inlineStr">
+    <row r="59" ht="35.05" customHeight="1" s="14">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>S7-01</t>
         </is>
       </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C56" s="19" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>DATOMS explorer</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E59" s="24" t="inlineStr">
         <is>
           <t>Explorer API: any device, any parameter, time range, min / avg / max, compare</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint: for any device, list its parameters.
 2. Endpoint: values for chosen parameters and time range, with min / average / max.
 3. Works for any new parameter without code changes.</t>
         </is>
       </c>
-      <c r="G56" s="19" t="inlineStr">
+      <c r="G59" s="19" t="inlineStr">
         <is>
           <t>Data for 'all DATOMS data'</t>
         </is>
       </c>
-      <c r="H56" s="19" t="inlineStr">
+      <c r="H59" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I56" s="19" t="inlineStr">
+      <c r="I59" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J56" s="19" t="inlineStr">
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K56" s="19" t="inlineStr">
+      <c r="K59" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="L56" s="19" t="n"/>
-      <c r="M56" s="19" t="n">
+      <c r="L59" s="19" t="n"/>
+      <c r="M59" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N56" s="25" t="inlineStr">
+      <c r="N59" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O56" s="19" t="inlineStr">
+      <c r="O59" s="19" t="inlineStr">
         <is>
           <t>New parameter types appear with no code change</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="79.84999999999999" customHeight="1" s="14">
-      <c r="A57" s="19" t="inlineStr">
+    <row r="60" ht="23.85" customHeight="1" s="14">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>S7-02</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E60" s="24" t="inlineStr">
         <is>
           <t>Security hardening: private endpoints, key rotation, firewall rules, web security headers</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>1. Put PostgreSQL and Blob behind private endpoints.
 2. Rotate keys in Key Vault.
 3. Firewall: only Container Apps can reach the database.
-4. Web app security headers and CSP (docs/08 §6) in staticwebapp.config.json: a CSP that allows only the MSAL (Entra) and ArcGIS domains plus the API and Web PubSub hosts; HSTS, X-Content-Type-Options, Referrer-Policy, frame-ancestors none. (Added by the S0 plan, 2026-10-09.)</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="inlineStr">
+4. Web app security headers and CSP (docs/08 §6) in staticwebapp.config.json: a CSP that allows only the MSAL (Entra) and ArcGIS domains plus the API and Web PubSub hosts; HSTS, X-Content-Type-Options, Referrer-Policy, frame-ancestors none. (Added by the S0 plan, 2026-10-09.)
+5. ArcGIS (security review of S0-09, PR #19, accepted by Ahmed 2026-10-14): the ArcGIS SDK puts the key in tile, style and elevation URLs (`token=`). Exclude `*.arcgis.com` and `*.arcgisonline.com` from App Insights automatic dependency tracking and strip `token=` in a telemetry initializer. CSP for the map (assets self-hosted, decision L6): `script-src 'self' 'wasm-unsafe-eval'`; `worker-src 'self' blob:`; `img-src 'self' data: blob: https://*.arcgis.com`; `connect-src` with `https://*.arcgis.com` (basemapstyles-api, ibasemaps-api, elevation3d, basemaps3d, static); `font-src 'self'`; check Calcite styles under `style-src`; no `unsafe-eval` (verify with a report-only CSP first). `Referrer-Policy: strict-origin-when-cross-origin`, never `no-referrer` (the ArcGIS key is referrer-restricted). Details in docs/09.</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
         <is>
           <t>Data not reachable from the internet; the web app sends a CSP and security headers</t>
         </is>
       </c>
-      <c r="H57" s="19" t="inlineStr">
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I57" s="19" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J57" s="19" t="inlineStr">
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>Innovo: security</t>
         </is>
       </c>
-      <c r="K57" s="19" t="n"/>
-      <c r="L57" s="19" t="n"/>
-      <c r="M57" s="19" t="n">
+      <c r="K60" s="19" t="n"/>
+      <c r="L60" s="19" t="n"/>
+      <c r="M60" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N57" s="25" t="inlineStr">
+      <c r="N60" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O57" s="19" t="inlineStr">
+      <c r="O60" s="19" t="inlineStr">
         <is>
           <t>Databases unreachable from internet; a header scan of the prod web URL shows the CSP and security headers, and sign-in and the map still work with the CSP on</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="57.45" customHeight="1" s="14">
-      <c r="A58" s="19" t="inlineStr">
+    <row r="61" ht="23.85" customHeight="1" s="14">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>S7-03</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>DATOMS explorer</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E61" s="24" t="inlineStr">
         <is>
           <t>Explorer screens: site and device picker, parameter tiles, chart with ranges and compare</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>1. Pick site, then device.
 2. Tiles with latest value of every parameter.
@@ -5977,312 +6208,103 @@
 4. Compare several parameters on one chart.</t>
         </is>
       </c>
-      <c r="G58" s="19" t="inlineStr">
+      <c r="G61" s="19" t="inlineStr">
         <is>
           <t>Explorer showing all DATOMS data</t>
         </is>
       </c>
-      <c r="H58" s="19" t="inlineStr">
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I58" s="19" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J58" s="19" t="inlineStr">
+      <c r="J61" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K58" s="19" t="inlineStr">
+      <c r="K61" s="19" t="inlineStr">
         <is>
           <t>S7-01</t>
         </is>
       </c>
-      <c r="L58" s="19" t="n"/>
-      <c r="M58" s="19" t="n">
+      <c r="L61" s="19" t="n"/>
+      <c r="M61" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N58" s="25" t="inlineStr">
+      <c r="N61" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O58" s="19" t="inlineStr">
+      <c r="O61" s="19" t="inlineStr">
         <is>
           <t>Matches DATOMS parameter view</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="35.05" customHeight="1" s="14">
-      <c r="A59" s="19" t="inlineStr">
+    <row r="62" ht="35.05" customHeight="1" s="14">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>S7-04</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E62" s="24" t="inlineStr">
         <is>
           <t>Automated permission tests for every role</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>1. Create a test user for each role.
 2. Automated tests: each role can open what it should, and is refused everything else.</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
+      <c r="G62" s="19" t="inlineStr">
         <is>
           <t>Permissions proven by tests</t>
         </is>
       </c>
-      <c r="H59" s="19" t="inlineStr">
+      <c r="H62" s="19" t="inlineStr">
         <is>
           <t>QA engineer</t>
         </is>
       </c>
-      <c r="I59" s="19" t="inlineStr">
+      <c r="I62" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J59" s="19" t="inlineStr">
+      <c r="J62" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K59" s="19" t="inlineStr">
+      <c r="K62" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="L59" s="19" t="n"/>
-      <c r="M59" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N59" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O59" s="19" t="inlineStr">
-        <is>
-          <t>Every role's allowed and denied paths covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="23.85" customHeight="1" s="14">
-      <c r="A60" s="19" t="inlineStr">
-        <is>
-          <t>S7-05</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>Production environment from code</t>
-        </is>
-      </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>1. Deploy 'nexus-prod' from the same Bicep files.
-2. Separate keys and Entra settings for production.</t>
-        </is>
-      </c>
-      <c r="G60" s="19" t="inlineStr">
-        <is>
-          <t>Production environment ready</t>
-        </is>
-      </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>DevOps engineer</t>
-        </is>
-      </c>
-      <c r="I60" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="K60" s="19" t="inlineStr">
-        <is>
-          <t>S0-02</t>
-        </is>
-      </c>
-      <c r="L60" s="19" t="n"/>
-      <c r="M60" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O60" s="19" t="inlineStr">
-        <is>
-          <t>Prod built from the same Bicep files</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="23.85" customHeight="1" s="14">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>S7-06</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E61" s="24" t="inlineStr">
-        <is>
-          <t>Tablet and mobile polish</t>
-        </is>
-      </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>1. Test every screen on a phone and a tablet.
-2. Fix layouts, touch targets, drawers.</t>
-        </is>
-      </c>
-      <c r="G61" s="19" t="inlineStr">
-        <is>
-          <t>Polished tablet and mobile</t>
-        </is>
-      </c>
-      <c r="H61" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I61" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J61" s="19" t="inlineStr">
-        <is>
-          <t>Innovo: devices</t>
-        </is>
-      </c>
-      <c r="K61" s="19" t="n"/>
-      <c r="L61" s="19" t="n"/>
-      <c r="M61" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N61" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O61" s="19" t="inlineStr">
-        <is>
-          <t>All screens usable on phone and tablet</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="35.05" customHeight="1" s="14">
-      <c r="A62" s="19" t="inlineStr">
-        <is>
-          <t>S7-07</t>
-        </is>
-      </c>
-      <c r="B62" s="19" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>Stale and missing data states: last updated, gaps shown as gaps</t>
-        </is>
-      </c>
-      <c r="F62" s="19" t="inlineStr">
-        <is>
-          <t>1. Show 'last updated' on every live box.
-2. Show missing data as a gap in charts, never as zero.
-3. Grey 'offline' state when DATOMS reports it.</t>
-        </is>
-      </c>
-      <c r="G62" s="19" t="inlineStr">
-        <is>
-          <t>Users can trust what they see</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I62" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J62" s="19" t="inlineStr">
-        <is>
-          <t>Risks: data quality</t>
-        </is>
-      </c>
-      <c r="K62" s="19" t="n"/>
       <c r="L62" s="19" t="n"/>
       <c r="M62" s="19" t="n">
         <v>2</v>
@@ -6294,24 +6316,24 @@
       </c>
       <c r="O62" s="19" t="inlineStr">
         <is>
-          <t>No zeros shown for missing data</t>
+          <t>Every role's allowed and denied paths covered</t>
         </is>
       </c>
     </row>
     <row r="63" ht="35.05" customHeight="1" s="14">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>S8-01</t>
+          <t>S7-05</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -6321,24 +6343,23 @@
       </c>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>Load test 100+ sites and 1,000 users; fix bottlenecks</t>
+          <t>Production environment from code</t>
         </is>
       </c>
       <c r="F63" s="19" t="inlineStr">
         <is>
-          <t>1. Run the S6-04 load test at 100+ sites and 1,000 users.
-2. Find slow endpoints; add indexes or caching.
-3. Re-run until pages load in under 2 seconds.</t>
+          <t>1. Deploy 'nexus-prod' from the same Bicep files.
+2. Separate keys and Entra settings for production.</t>
         </is>
       </c>
       <c r="G63" s="19" t="inlineStr">
         <is>
-          <t>Proven performance at scale</t>
+          <t>Production environment ready</t>
         </is>
       </c>
       <c r="H63" s="19" t="inlineStr">
         <is>
-          <t>QA engineer</t>
+          <t>DevOps engineer</t>
         </is>
       </c>
       <c r="I63" s="19" t="inlineStr">
@@ -6348,17 +6369,17 @@
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t>Innovo: scalable</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="K63" s="19" t="inlineStr">
         <is>
-          <t>S5-04</t>
+          <t>S0-02</t>
         </is>
       </c>
       <c r="L63" s="19" t="n"/>
       <c r="M63" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N63" s="25" t="inlineStr">
         <is>
@@ -6367,24 +6388,24 @@
       </c>
       <c r="O63" s="19" t="inlineStr">
         <is>
-          <t>Pages under 2 s at target load</t>
+          <t>Prod built from the same Bicep files</t>
         </is>
       </c>
     </row>
     <row r="64" ht="23.85" customHeight="1" s="14">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>S8-02</t>
+          <t>S7-06</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
@@ -6394,33 +6415,33 @@
       </c>
       <c r="E64" s="24" t="inlineStr">
         <is>
-          <t>Backups, restore test, monitoring alerts (sync stopped, error spikes)</t>
+          <t>Tablet and mobile polish</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
-          <t>1. Turn on daily database backups; do one restore test.
-2. Alerts in Application Insights: sync stopped, error spike, slow responses.</t>
+          <t>1. Test every screen on a phone and a tablet.
+2. Fix layouts, touch targets, drawers.</t>
         </is>
       </c>
       <c r="G64" s="19" t="inlineStr">
         <is>
-          <t>Backups and alerts working</t>
+          <t>Polished tablet and mobile</t>
         </is>
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
-          <t>DevOps engineer</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
         <is>
-          <t>You (backend)</t>
+          <t>Colleague (frontend)</t>
         </is>
       </c>
       <c r="J64" s="19" t="inlineStr">
         <is>
-          <t>Risks</t>
+          <t>Innovo: devices</t>
         </is>
       </c>
       <c r="K64" s="19" t="n"/>
@@ -6435,24 +6456,24 @@
       </c>
       <c r="O64" s="19" t="inlineStr">
         <is>
-          <t>Restore proven; alert fires on stopped sync</t>
+          <t>All screens usable on phone and tablet</t>
         </is>
       </c>
     </row>
     <row r="65" ht="35.05" customHeight="1" s="14">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>S8-03</t>
+          <t>S7-07</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -6462,24 +6483,24 @@
       </c>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>Accessibility and performance pass</t>
+          <t>Stale and missing data states: last updated, gaps shown as gaps</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
         <is>
-          <t>1. Keyboard navigation and visible focus.
-2. Check contrast.
-3. Reduce bundle size; lazy-load heavy pages.</t>
+          <t>1. Show 'last updated' on every live box.
+2. Show missing data as a gap in charts, never as zero.
+3. Grey 'offline' state when DATOMS reports it.</t>
         </is>
       </c>
       <c r="G65" s="19" t="inlineStr">
         <is>
-          <t>Accessible and fast</t>
+          <t>Users can trust what they see</t>
         </is>
       </c>
       <c r="H65" s="19" t="inlineStr">
         <is>
-          <t>UI/UX designer</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="I65" s="19" t="inlineStr">
@@ -6489,7 +6510,7 @@
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Risks: data quality</t>
         </is>
       </c>
       <c r="K65" s="19" t="n"/>
@@ -6504,14 +6525,14 @@
       </c>
       <c r="O65" s="19" t="inlineStr">
         <is>
-          <t>Keyboard navigation; fast first load</t>
+          <t>No zeros shown for missing data</t>
         </is>
       </c>
     </row>
     <row r="66" ht="23.85" customHeight="1" s="14">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>S8-04</t>
+          <t>S8-01</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -6521,7 +6542,7 @@
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -6531,39 +6552,44 @@
       </c>
       <c r="E66" s="24" t="inlineStr">
         <is>
-          <t>Report a data issue link</t>
+          <t>Load test 100+ sites and 1,000 users; fix bottlenecks</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
-          <t>1. 'Report a data issue' link on data boxes.
-2. Sends the site, asset and description to the site/technical team contact.</t>
+          <t>1. Run the S6-04 load test at 100+ sites and 1,000 users.
+2. Find slow endpoints; add indexes or caching.
+3. Re-run until pages load in under 2 seconds.</t>
         </is>
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
-          <t>Data problems reach the right team</t>
+          <t>Proven performance at scale</t>
         </is>
       </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>QA engineer</t>
         </is>
       </c>
       <c r="I66" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
+          <t>You (backend)</t>
         </is>
       </c>
       <c r="J66" s="19" t="inlineStr">
         <is>
-          <t>Risks: data quality</t>
-        </is>
-      </c>
-      <c r="K66" s="19" t="n"/>
+          <t>Innovo: scalable</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr">
+        <is>
+          <t>S5-04</t>
+        </is>
+      </c>
       <c r="L66" s="19" t="n"/>
       <c r="M66" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N66" s="25" t="inlineStr">
         <is>
@@ -6572,14 +6598,14 @@
       </c>
       <c r="O66" s="19" t="inlineStr">
         <is>
-          <t>Sends issue to site/technical team contact</t>
+          <t>Pages under 2 s at target load</t>
         </is>
       </c>
     </row>
     <row r="67" ht="35.05" customHeight="1" s="14">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>S8-05</t>
+          <t>S8-02</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
@@ -6589,34 +6615,33 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Hardening</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>Penetration test and fixes</t>
+          <t>Backups, restore test, monitoring alerts (sync stopped, error spikes)</t>
         </is>
       </c>
       <c r="F67" s="19" t="inlineStr">
         <is>
-          <t>1. Book an external penetration test.
-2. Fix all high and critical findings.
-3. Re-test.</t>
+          <t>1. Turn on daily database backups; do one restore test.
+2. Alerts in Application Insights: sync stopped, error spike, slow responses.</t>
         </is>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
-          <t>Security signed off</t>
+          <t>Backups and alerts working</t>
         </is>
       </c>
       <c r="H67" s="19" t="inlineStr">
         <is>
-          <t>Security engineer</t>
+          <t>DevOps engineer</t>
         </is>
       </c>
       <c r="I67" s="19" t="inlineStr">
@@ -6626,21 +6651,13 @@
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t>Innovo: security</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="inlineStr">
-        <is>
-          <t>S7-05</t>
-        </is>
-      </c>
-      <c r="L67" s="19" t="inlineStr">
-        <is>
-          <t>External pen-test slot</t>
-        </is>
-      </c>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="n"/>
+      <c r="L67" s="19" t="n"/>
       <c r="M67" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" s="25" t="inlineStr">
         <is>
@@ -6649,14 +6666,14 @@
       </c>
       <c r="O67" s="19" t="inlineStr">
         <is>
-          <t>No high or critical findings open</t>
+          <t>Restore proven; alert fires on stopped sync</t>
         </is>
       </c>
     </row>
     <row r="68" ht="23.85" customHeight="1" s="14">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>S8-06</t>
+          <t>S8-03</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
@@ -6671,37 +6688,39 @@
       </c>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Hardening</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>Short user guide</t>
+          <t>Accessibility and performance pass</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
         <is>
-          <t>1. One-page guide per role: how to find a project, read the boxes, open details.</t>
+          <t>1. Keyboard navigation and visible focus.
+2. Check contrast.
+3. Reduce bundle size; lazy-load heavy pages.</t>
         </is>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
-          <t>User guide</t>
+          <t>Accessible and fast</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>Product owner</t>
+          <t>UI/UX designer</t>
         </is>
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Colleague (frontend)</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>Adoption</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="K68" s="19" t="n"/>
@@ -6716,19 +6735,19 @@
       </c>
       <c r="O68" s="19" t="inlineStr">
         <is>
-          <t>One-page guide per role</t>
+          <t>Keyboard navigation; fast first load</t>
         </is>
       </c>
     </row>
     <row r="69" ht="23.85" customHeight="1" s="14">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>S9-01</t>
+          <t>S8-04</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
@@ -6738,43 +6757,44 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Hardening</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>Runbook and handover docs</t>
+          <t>Report a data issue link</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
-          <t>1. Write: how to deploy, how to restore, how to add a new data source, who to call when DATOMS is down.</t>
+          <t>1. 'Report a data issue' link on data boxes.
+2. Sends the site, asset and description to the site/technical team contact.</t>
         </is>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>Runbook so anyone can operate Nexus</t>
+          <t>Data problems reach the right team</t>
         </is>
       </c>
       <c r="H69" s="19" t="inlineStr">
         <is>
-          <t>Backend developer</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="I69" s="19" t="inlineStr">
         <is>
-          <t>You (backend)</t>
+          <t>Colleague (frontend)</t>
         </is>
       </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t>Risks: knowledge</t>
+          <t>Risks: data quality</t>
         </is>
       </c>
       <c r="K69" s="19" t="n"/>
       <c r="L69" s="19" t="n"/>
       <c r="M69" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N69" s="25" t="inlineStr">
         <is>
@@ -6783,572 +6803,782 @@
       </c>
       <c r="O69" s="19" t="inlineStr">
         <is>
-          <t>New developer can deploy from the docs</t>
+          <t>Sends issue to site/technical team contact</t>
         </is>
       </c>
     </row>
     <row r="70" ht="35.05" customHeight="1" s="14">
       <c r="A70" s="19" t="inlineStr">
         <is>
+          <t>S8-05</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>Penetration test and fixes</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>1. Book an external penetration test.
+2. Fix all high and critical findings.
+3. Re-test.</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
+        <is>
+          <t>Security signed off</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="inlineStr">
+        <is>
+          <t>Security engineer</t>
+        </is>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: security</t>
+        </is>
+      </c>
+      <c r="K70" s="19" t="inlineStr">
+        <is>
+          <t>S7-05</t>
+        </is>
+      </c>
+      <c r="L70" s="19" t="inlineStr">
+        <is>
+          <t>External pen-test slot</t>
+        </is>
+      </c>
+      <c r="M70" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O70" s="19" t="inlineStr">
+        <is>
+          <t>No high or critical findings open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="14">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>S8-06</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>Short user guide</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>1. One-page guide per role: how to find a project, read the boxes, open details.</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>User guide</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="inlineStr">
+        <is>
+          <t>Product owner</t>
+        </is>
+      </c>
+      <c r="I71" s="19" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="K71" s="19" t="n"/>
+      <c r="L71" s="19" t="n"/>
+      <c r="M71" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O71" s="19" t="inlineStr">
+        <is>
+          <t>One-page guide per role</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="23.85" customHeight="1" s="14">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>S9-01</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>Runbook and handover docs</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>1. Write: how to deploy, how to restore, how to add a new data source, who to call when DATOMS is down.</t>
+        </is>
+      </c>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>Runbook so anyone can operate Nexus</t>
+        </is>
+      </c>
+      <c r="H72" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I72" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>Risks: knowledge</t>
+        </is>
+      </c>
+      <c r="K72" s="19" t="n"/>
+      <c r="L72" s="19" t="n"/>
+      <c r="M72" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O72" s="19" t="inlineStr">
+        <is>
+          <t>New developer can deploy from the docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="23.85" customHeight="1" s="14">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
           <t>S9-02</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="C70" s="19" t="inlineStr">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr">
+      <c r="D73" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E70" s="24" t="inlineStr">
+      <c r="E73" s="24" t="inlineStr">
         <is>
           <t>User acceptance testing on GHAFWOODS with pilot users</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>1. Give pilot users access on GHAFWOODS in **prod** (there is no test environment, ADR 0008): only pilot users are assigned to the Entra app during the pilot.
 2. Walk through each screen with them.
 3. Record issues in the backlog.</t>
         </is>
       </c>
-      <c r="G70" s="19" t="inlineStr">
+      <c r="G73" s="19" t="inlineStr">
         <is>
           <t>Pilot feedback list</t>
         </is>
       </c>
-      <c r="H70" s="19" t="inlineStr">
+      <c r="H73" s="19" t="inlineStr">
         <is>
           <t>Product owner</t>
         </is>
       </c>
-      <c r="I70" s="19" t="inlineStr">
+      <c r="I73" s="19" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="J70" s="19" t="inlineStr">
+      <c r="J73" s="19" t="inlineStr">
         <is>
           <t>Brief objectives</t>
         </is>
       </c>
-      <c r="K70" s="19" t="n"/>
-      <c r="L70" s="19" t="inlineStr">
+      <c r="K73" s="19" t="n"/>
+      <c r="L73" s="19" t="inlineStr">
         <is>
           <t>Pilot users' time</t>
         </is>
       </c>
-      <c r="M70" s="19" t="n">
+      <c r="M73" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N70" s="25" t="inlineStr">
+      <c r="N73" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O70" s="19" t="inlineStr">
+      <c r="O73" s="19" t="inlineStr">
         <is>
           <t>Pilot users sign off each screen</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="14">
-      <c r="A71" s="19" t="inlineStr">
+    <row r="74" ht="23.85" customHeight="1" s="14">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>S9-03</t>
         </is>
       </c>
-      <c r="B71" s="19" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="C71" s="19" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E71" s="24" t="inlineStr">
+      <c r="E74" s="24" t="inlineStr">
         <is>
           <t>Bug fixes from pilot (backend)</t>
         </is>
       </c>
-      <c r="F71" s="19" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>1. Fix backend issues from the pilot, most important first.</t>
         </is>
       </c>
-      <c r="G71" s="19" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>Backend pilot issues closed</t>
         </is>
       </c>
-      <c r="H71" s="19" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I71" s="19" t="inlineStr">
+      <c r="I74" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J71" s="19" t="n"/>
-      <c r="K71" s="19" t="inlineStr">
+      <c r="J74" s="19" t="n"/>
+      <c r="K74" s="19" t="inlineStr">
         <is>
           <t>S9-02</t>
         </is>
       </c>
-      <c r="L71" s="19" t="n"/>
-      <c r="M71" s="19" t="n">
+      <c r="L74" s="19" t="n"/>
+      <c r="M74" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N71" s="25" t="inlineStr">
+      <c r="N74" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O71" s="19" t="inlineStr">
+      <c r="O74" s="19" t="inlineStr">
         <is>
           <t>All pilot blockers fixed</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="23.85" customHeight="1" s="14">
-      <c r="A72" s="19" t="inlineStr">
+    <row r="75" ht="23.85" customHeight="1" s="14">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>S9-04</t>
         </is>
       </c>
-      <c r="B72" s="19" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="C72" s="19" t="inlineStr">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D72" s="19" t="inlineStr">
+      <c r="D75" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E72" s="24" t="inlineStr">
+      <c r="E75" s="24" t="inlineStr">
         <is>
           <t>Bug fixes from pilot (frontend)</t>
         </is>
       </c>
-      <c r="F72" s="19" t="inlineStr">
+      <c r="F75" s="19" t="inlineStr">
         <is>
           <t>1. Fix frontend issues from the pilot, most important first.</t>
         </is>
       </c>
-      <c r="G72" s="19" t="inlineStr">
+      <c r="G75" s="19" t="inlineStr">
         <is>
           <t>Frontend pilot issues closed</t>
         </is>
       </c>
-      <c r="H72" s="19" t="inlineStr">
+      <c r="H75" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I72" s="19" t="inlineStr">
+      <c r="I75" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J72" s="19" t="n"/>
-      <c r="K72" s="19" t="inlineStr">
+      <c r="J75" s="19" t="n"/>
+      <c r="K75" s="19" t="inlineStr">
         <is>
           <t>S9-02</t>
         </is>
       </c>
-      <c r="L72" s="19" t="n"/>
-      <c r="M72" s="19" t="n">
+      <c r="L75" s="19" t="n"/>
+      <c r="M75" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N72" s="25" t="inlineStr">
+      <c r="N75" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O72" s="19" t="inlineStr">
+      <c r="O75" s="19" t="inlineStr">
         <is>
           <t>All pilot blockers fixed</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="23.85" customHeight="1" s="14">
-      <c r="A73" s="19" t="inlineStr">
+    <row r="76" ht="23.85" customHeight="1" s="14">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>S10-01</t>
         </is>
       </c>
-      <c r="B73" s="19" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D73" s="19" t="inlineStr">
+      <c r="D76" s="19" t="inlineStr">
         <is>
           <t>Rollout</t>
         </is>
       </c>
-      <c r="E73" s="24" t="inlineStr">
+      <c r="E76" s="24" t="inlineStr">
         <is>
           <t>Connect all DATOMS sites to production; verify auto-linking</t>
         </is>
       </c>
-      <c r="F73" s="19" t="inlineStr">
+      <c r="F76" s="19" t="inlineStr">
         <is>
           <t>1. Point production at all DATOMS sites.
 2. Check every site links to the right project; clear the admin to-do list.</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
+      <c r="G76" s="19" t="inlineStr">
         <is>
           <t>All sites live</t>
         </is>
       </c>
-      <c r="H73" s="19" t="inlineStr">
+      <c r="H76" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I73" s="19" t="inlineStr">
+      <c r="I76" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J73" s="19" t="inlineStr">
+      <c r="J76" s="19" t="inlineStr">
         <is>
           <t>Innovo: many sites</t>
         </is>
       </c>
-      <c r="K73" s="19" t="inlineStr">
+      <c r="K76" s="19" t="inlineStr">
         <is>
           <t>S9-03</t>
         </is>
       </c>
-      <c r="L73" s="19" t="n"/>
-      <c r="M73" s="19" t="n">
+      <c r="L76" s="19" t="n"/>
+      <c r="M76" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N73" s="25" t="inlineStr">
+      <c r="N76" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O73" s="19" t="inlineStr">
+      <c r="O76" s="19" t="inlineStr">
         <is>
           <t>Every DATOMS site visible with correct project</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="23.85" customHeight="1" s="14">
-      <c r="A74" s="19" t="inlineStr">
+    <row r="77" ht="23.85" customHeight="1" s="14">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>S10-02</t>
         </is>
       </c>
-      <c r="B74" s="19" t="inlineStr">
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="C74" s="19" t="inlineStr">
+      <c r="C77" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D74" s="19" t="inlineStr">
+      <c r="D77" s="19" t="inlineStr">
         <is>
           <t>Rollout</t>
         </is>
       </c>
-      <c r="E74" s="24" t="inlineStr">
+      <c r="E77" s="24" t="inlineStr">
         <is>
           <t>Production monitoring and cost review</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>1. Set Azure cost alerts.
 2. Review first month's cost and performance.</t>
         </is>
       </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="G77" s="19" t="inlineStr">
         <is>
           <t>Running costs under control</t>
         </is>
       </c>
-      <c r="H74" s="19" t="inlineStr">
+      <c r="H77" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I74" s="19" t="inlineStr">
+      <c r="I77" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J74" s="19" t="inlineStr">
+      <c r="J77" s="19" t="inlineStr">
         <is>
           <t>Risks: cost</t>
         </is>
       </c>
-      <c r="K74" s="19" t="n"/>
-      <c r="L74" s="19" t="n"/>
-      <c r="M74" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N74" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O74" s="19" t="inlineStr">
-        <is>
-          <t>Cost alerts set; first monthly review done</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="23.85" customHeight="1" s="14">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>S10-03</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D75" s="19" t="inlineStr">
-        <is>
-          <t>Rollout</t>
-        </is>
-      </c>
-      <c r="E75" s="24" t="inlineStr">
-        <is>
-          <t>Onboarding sessions with site teams</t>
-        </is>
-      </c>
-      <c r="F75" s="19" t="inlineStr">
-        <is>
-          <t>1. Short session per site team.
-2. Name a champion per site.</t>
-        </is>
-      </c>
-      <c r="G75" s="19" t="inlineStr">
-        <is>
-          <t>Site teams using Nexus</t>
-        </is>
-      </c>
-      <c r="H75" s="19" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="J75" s="19" t="inlineStr">
-        <is>
-          <t>Adoption</t>
-        </is>
-      </c>
-      <c r="K75" s="19" t="n"/>
-      <c r="L75" s="19" t="n"/>
-      <c r="M75" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O75" s="19" t="inlineStr">
-        <is>
-          <t>Each site has a champion trained</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="23.85" customHeight="1" s="14">
-      <c r="A76" s="19" t="inlineStr">
-        <is>
-          <t>S10-04</t>
-        </is>
-      </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C76" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D76" s="19" t="inlineStr">
-        <is>
-          <t>Rollout</t>
-        </is>
-      </c>
-      <c r="E76" s="24" t="inlineStr">
-        <is>
-          <t>Phase 2 backlog grooming (reporting feed, BIM, AI)</t>
-        </is>
-      </c>
-      <c r="F76" s="19" t="inlineStr">
-        <is>
-          <t>1. List phase 2 items (reporting feed, BIM, AI).
-2. Estimate and order them.</t>
-        </is>
-      </c>
-      <c r="G76" s="19" t="inlineStr">
-        <is>
-          <t>Phase 2 backlog ready</t>
-        </is>
-      </c>
-      <c r="H76" s="19" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="I76" s="19" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="J76" s="19" t="inlineStr">
-        <is>
-          <t>Future</t>
-        </is>
-      </c>
-      <c r="K76" s="19" t="n"/>
-      <c r="L76" s="19" t="n"/>
-      <c r="M76" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O76" s="19" t="inlineStr">
-        <is>
-          <t>Phase 2 backlog estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="23.85" customHeight="1" s="14">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>S10-05</t>
-        </is>
-      </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>Rollout</t>
-        </is>
-      </c>
-      <c r="E77" s="24" t="inlineStr">
-        <is>
-          <t>UI fixes from rollout feedback</t>
-        </is>
-      </c>
-      <c r="F77" s="19" t="inlineStr">
-        <is>
-          <t>1. Fix UI feedback from rollout, most important first.</t>
-        </is>
-      </c>
-      <c r="G77" s="19" t="inlineStr">
-        <is>
-          <t>Rollout feedback closed</t>
-        </is>
-      </c>
-      <c r="H77" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I77" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J77" s="19" t="n"/>
       <c r="K77" s="19" t="n"/>
       <c r="L77" s="19" t="n"/>
       <c r="M77" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O77" s="19" t="inlineStr">
+        <is>
+          <t>Cost alerts set; first monthly review done</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" s="14">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>S10-03</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>Onboarding sessions with site teams</t>
+        </is>
+      </c>
+      <c r="F78" s="19" t="inlineStr">
+        <is>
+          <t>1. Short session per site team.
+2. Name a champion per site.</t>
+        </is>
+      </c>
+      <c r="G78" s="19" t="inlineStr">
+        <is>
+          <t>Site teams using Nexus</t>
+        </is>
+      </c>
+      <c r="H78" s="19" t="inlineStr">
+        <is>
+          <t>Product owner</t>
+        </is>
+      </c>
+      <c r="I78" s="19" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="K78" s="19" t="n"/>
+      <c r="L78" s="19" t="n"/>
+      <c r="M78" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O78" s="19" t="inlineStr">
+        <is>
+          <t>Each site has a champion trained</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="14">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>S10-04</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog grooming (reporting feed, BIM, AI)</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="inlineStr">
+        <is>
+          <t>1. List phase 2 items (reporting feed, BIM, AI).
+2. Estimate and order them.</t>
+        </is>
+      </c>
+      <c r="G79" s="19" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog ready</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="inlineStr">
+        <is>
+          <t>Product owner</t>
+        </is>
+      </c>
+      <c r="I79" s="19" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>Future</t>
+        </is>
+      </c>
+      <c r="K79" s="19" t="n"/>
+      <c r="L79" s="19" t="n"/>
+      <c r="M79" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O79" s="19" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" s="14">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>S10-05</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>UI fixes from rollout feedback</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>1. Fix UI feedback from rollout, most important first.</t>
+        </is>
+      </c>
+      <c r="G80" s="19" t="inlineStr">
+        <is>
+          <t>Rollout feedback closed</t>
+        </is>
+      </c>
+      <c r="H80" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I80" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J80" s="19" t="n"/>
+      <c r="K80" s="19" t="n"/>
+      <c r="L80" s="19" t="n"/>
+      <c r="M80" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N77" s="25" t="inlineStr">
+      <c r="N80" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O77" s="19" t="inlineStr">
+      <c r="O80" s="19" t="inlineStr">
         <is>
           <t>Feedback items closed</t>
         </is>
       </c>
     </row>
-    <row r="78" s="14"/>
-    <row r="79" ht="15" customHeight="1" s="14">
-      <c r="L79" s="16" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="L82" s="16" t="inlineStr">
         <is>
           <t>Total days</t>
         </is>
       </c>
-      <c r="M79" s="16">
-        <f>SUM(M2:M77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" s="14"/>
+      <c r="M82" s="16">
+        <f>SUM(M2:M80)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O77"/>
-  <conditionalFormatting sqref="A2:O77">
+  <conditionalFormatting sqref="A2:O80">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="4" text="" percent="0" bottom="0">
       <formula>$N2="Blocked"</formula>
     </cfRule>
@@ -7357,7 +7587,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="N2:N80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
+++ b/docs/source/Nexus_Phase1_Sprint_Plan.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Future" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -532,6 +532,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="35.05" customHeight="1" s="14">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -768,27 +769,27 @@
         </is>
       </c>
       <c r="F2" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A2)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A2)</f>
         <v/>
       </c>
       <c r="G2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A2,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A2,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A2,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J2" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A2,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A2,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K2" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A2,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A2,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L2" s="20">
@@ -823,27 +824,27 @@
         </is>
       </c>
       <c r="F3" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A3)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A3)</f>
         <v/>
       </c>
       <c r="G3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A3,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A3,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A3,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A3,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A3,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K3" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A3,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A3,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L3" s="20">
@@ -878,27 +879,27 @@
         </is>
       </c>
       <c r="F4" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A4)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A4)</f>
         <v/>
       </c>
       <c r="G4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A4,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A4,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A4,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J4" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A4,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A4,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K4" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A4,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A4,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L4" s="20">
@@ -933,27 +934,27 @@
         </is>
       </c>
       <c r="F5" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A5)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A5)</f>
         <v/>
       </c>
       <c r="G5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A5,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A5,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A5,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J5" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A5,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A5,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K5" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A5,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A5,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L5" s="20">
@@ -988,27 +989,27 @@
         </is>
       </c>
       <c r="F6" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A6)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A6)</f>
         <v/>
       </c>
       <c r="G6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A6,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A6,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A6,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J6" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A6,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A6,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K6" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A6,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A6,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L6" s="20">
@@ -1043,27 +1044,27 @@
         </is>
       </c>
       <c r="F7" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A7)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A7)</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A7,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A7,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A7,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J7" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A7,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A7,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K7" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A7,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A7,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L7" s="20">
@@ -1098,27 +1099,27 @@
         </is>
       </c>
       <c r="F8" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A8)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A8)</f>
         <v/>
       </c>
       <c r="G8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A8,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A8,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A8,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J8" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A8,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A8,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K8" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A8,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A8,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L8" s="20">
@@ -1153,27 +1154,27 @@
         </is>
       </c>
       <c r="F9" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A9)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A9)</f>
         <v/>
       </c>
       <c r="G9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A9,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A9,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A9,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J9" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A9,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A9,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K9" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A9,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A9,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L9" s="20">
@@ -1208,27 +1209,27 @@
         </is>
       </c>
       <c r="F10" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A10)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A10)</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A10,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A10,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A10,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J10" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A10,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A10,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K10" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A10,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A10,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L10" s="20">
@@ -1263,27 +1264,27 @@
         </is>
       </c>
       <c r="F11" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A11)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A11)</f>
         <v/>
       </c>
       <c r="G11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A11,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A11,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A11,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J11" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A11,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A11,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K11" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A11,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A11,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L11" s="20">
@@ -1318,27 +1319,27 @@
         </is>
       </c>
       <c r="F12" s="19">
-        <f>COUNTIF(Backlog!$B$2:$B$80,A12)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$81,A12)</f>
         <v/>
       </c>
       <c r="G12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$I$2:$I$80,"You (backend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A12,Backlog!$I$2:$I$81,"You (backend)")</f>
         <v/>
       </c>
       <c r="H12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$I$2:$I$80,"Colleague (frontend)")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A12,Backlog!$I$2:$I$81,"Colleague (frontend)")</f>
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$I$2:$I$80,"Both")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A12,Backlog!$I$2:$I$81,"Both")</f>
         <v/>
       </c>
       <c r="J12" s="19">
-        <f>SUMIF(Backlog!$B$2:$B$80,A12,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$B$2:$B$81,A12,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="K12" s="19">
-        <f>SUMIFS(Backlog!$M$2:$M$80,Backlog!$B$2:$B$80,A12,Backlog!$N$2:$N$80,"Done")</f>
+        <f>SUMIFS(Backlog!$M$2:$M$81,Backlog!$B$2:$B$81,A12,Backlog!$N$2:$N$81,"Done")</f>
         <v/>
       </c>
       <c r="L12" s="20">
@@ -1478,11 +1479,11 @@
         </is>
       </c>
       <c r="E4" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B4)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B4)</f>
         <v/>
       </c>
       <c r="F4" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B4,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B4,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -1511,11 +1512,11 @@
         </is>
       </c>
       <c r="E5" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B5)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B5)</f>
         <v/>
       </c>
       <c r="F5" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B5,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B5,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -1544,11 +1545,11 @@
         </is>
       </c>
       <c r="E6" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B6)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B6)</f>
         <v/>
       </c>
       <c r="F6" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B6,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B6,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -1577,11 +1578,11 @@
         </is>
       </c>
       <c r="E7" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B7)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B7)</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B7,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B7,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -1610,11 +1611,11 @@
         </is>
       </c>
       <c r="E8" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B8)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B8)</f>
         <v/>
       </c>
       <c r="F8" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B8,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B8,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1643,11 +1644,11 @@
         </is>
       </c>
       <c r="E9" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B9)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B9)</f>
         <v/>
       </c>
       <c r="F9" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B9,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B9,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1676,11 +1677,11 @@
         </is>
       </c>
       <c r="E10" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B10)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B10)</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B10,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B10,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1709,11 +1710,11 @@
         </is>
       </c>
       <c r="E11" s="19">
-        <f>COUNTIF(Backlog!$H$2:$H$80,B11)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$81,B11)</f>
         <v/>
       </c>
       <c r="F11" s="19">
-        <f>SUMIF(Backlog!$H$2:$H$80,B11,Backlog!$M$2:$M$80)</f>
+        <f>SUMIF(Backlog!$H$2:$H$81,B11,Backlog!$M$2:$M$81)</f>
         <v/>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1756,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="13" min="1" max="1"/>
@@ -3244,33 +3245,103 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="68.65000000000001" customHeight="1" s="14">
+    <row r="21" ht="91.05" customHeight="1" s="14">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>S1-11</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>Web app on the typed API client: switch pendingClient.ts to the generated client, then remove the /v1/config MSW mock and VITE_DEV_ARCGIS_API_KEY</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>1. Fix the base-URL mismatch first: the generated `schema.d.ts` paths include `/v1` (`/v1/me`, `/v1/config`) and `VITE_API_BASE_URL` also ends in `/v1`, so the typed client would call `/v1/v1/...`. Choose one fix (generate the paths without the `/v1` prefix, or give the typed client the API origin as its base URL), add a test for it, and record the choice in docs/10 "OpenAPI and the typed client".
+2. Move `/v1/config` and `/v1/me` (useConfig, useCurrentUser) from `pendingClient.ts` to the typed client (`api` in apps/web/src/api/client.ts). `/v1/projects` stays in `pendingClient.ts` until S2-01 publishes it; then delete the file.
+3. Remove the dev-mode MSW `/v1/config` mock and `VITE_DEV_ARCGIS_API_KEY` (main.tsx, test/handlers.ts, vite-env.d.ts, the env guards and the checkDist allow-list, .env.example, docs/04, docs/runbooks/arcgis-key.md section 4). Test-only MSW handlers stay. Locally the map key then comes from the API's `/v1/config` (S1-10).
+(Added 2026-10-22 (decision by Ahmed).)</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>The web app reads /v1/me and /v1/config through the generated client; no local ArcGIS key path is left in the web app</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
+        <is>
+          <t>S1-10</t>
+        </is>
+      </c>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O21" s="19" t="inlineStr">
+        <is>
+          <t>`pnpm typecheck` fails when the `/v1/me` or `/v1/config` contract changes; a test shows the typed client requests `/v1/config`, not `/v1/v1/config`; `VITE_DEV_ARCGIS_API_KEY` is gone from apps/web, .env.example and docs/04; with the API running locally the map gets its key from `/v1/config`</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="68.65000000000001" customHeight="1" s="14">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Projects API: list, filter (status, type, district), search, scoped to user</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>1. Create GET /projects with filters: status, type, district, search text.
 2. Apply the project-scope filter from S1-02.
@@ -3279,73 +3350,73 @@
 5. Do not read any project source column (`source_system`, `external_id`, `source_payload`, `*_seen_at` on `core.project`): ADR 0012 drops them in S3-09. Source ids are not part of the normal project response.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>Projects list endpoint the map uses</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>Sheet: Top level</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr">
+      <c r="K22" s="19" t="inlineStr">
         <is>
           <t>S1-02, S1-09</t>
         </is>
       </c>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n">
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N21" s="25" t="inlineStr">
+      <c r="N22" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>Returns only the user's projects; search under 300 ms</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="79.84999999999999" customHeight="1" s="14">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="23" ht="79.84999999999999" customHeight="1" s="14">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>S2-02</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>DATOMS API client: bulk endpoint, paging, retries, rate-limit and credit handling</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1. Read the v4 PDF, docs/07 section 3 (test key, what DATOMS has shared) and docs/source/datoms-parameters.md (parameter keys, names and units for DG Set, Fuel Tank, AC Sub-Meter, Solar Inverter; seeded per source type, ADR 0011). Use the DATOMS sample bulk response (Q21) and bulk field list (Q22) once received.
 2. Build packages/datoms-client: list assets (catalogue) and the bulk endpoint (fleet and id mode) as the ONLY telemetry source (ADR 0010). data/latest is for CLI checks only.
@@ -3355,73 +3426,73 @@
 6. Test against GHAFWOODS using fixtures or a small id-mode subset from a developer machine (never the full fleet; the test key is not in Key Vault, so the cloud dev worker stays on fixtures).</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>Code that can talk to DATOMS</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>Brief: energy, crane utilisation</t>
         </is>
       </c>
-      <c r="K22" s="19" t="n"/>
-      <c r="L22" s="19" t="inlineStr">
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="inlineStr">
         <is>
           <t>None. Unblocked 2026-10-12: DATOMS provisional read-only test key for org 20283 (valid until 10 Nov 2026). Checked inside this task: whether the bulk endpoint is enabled for the key (Q34). Still pending, not blocking: site, location, status and alert field names (Q21, Q22); those mappings stay empty ("no data yet") until they arrive.</t>
         </is>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M23" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="25" t="inlineStr">
+      <c r="N23" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>One bulk call made with the test key and its result recorded in docs/07 section 3.3 and Q34. If bulk is enabled: the client reads a small id-mode subset of the live fleet through the bulk endpoint. If not: the client's tests pass on fixtures and the worker stays on fixtures. Either way: no data/latest call outside scripts/, and DATOMS field names exist only in src/mapping.ts</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="46.25" customHeight="1" s="14">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24" ht="46.25" customHeight="1" s="14">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>S2-03</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Portfolio map (chosen provider, through the map wrapper): one pin per DATOMS site, coloured Active green, Central Store blue, Finished grey, In bid yellow where DATOMS gives the status</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>1. Use the MapView wrapper with the ArcGIS adapter from S0-09.
 2. Show a UAE map.
@@ -3431,292 +3502,292 @@
 6. Acceptance is split (decision S2 D3): part A (no key, test data, stubbed tiles) is the merge gate. Part B runs when the ArcGIS key arrives (Q23): the real-key spec checks there are no failed `arcgis.com` / `basemaps3d` responses, the marker or cluster count equals the 10 sample projects, and a screenshot comparison passes (QA of S0-09, 2026-10-14).</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>Top-level portfolio map</t>
         </is>
       </c>
-      <c r="H23" s="19" t="inlineStr">
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>Sheet: Top level</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>S0-09</t>
         </is>
       </c>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n">
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N23" s="25" t="inlineStr">
+      <c r="N24" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="O24" s="19" t="inlineStr">
         <is>
           <t>All projects shown; colours match the sheet; click zooms to project</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="35.05" customHeight="1" s="14">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="25" ht="35.05" customHeight="1" s="14">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>S2-04</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>Project list panel and summary tiles (projects, districts)</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>1. Left panel: list of sites with the details DATOMS provides (name, location, type, status).
 2. Two summary tiles at the top: number of projects, number of districts.
 3. Click a project in the list = same as clicking its pin.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>Project list beside the map</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr">
         <is>
           <t>Brief mockups</t>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="K25" s="19" t="inlineStr">
         <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n">
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="25" t="inlineStr">
+      <c r="N25" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O24" s="19" t="inlineStr">
+      <c r="O25" s="19" t="inlineStr">
         <is>
           <t>List matches mockup: name, district, type tag, client, consultant, PM</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="46.25" customHeight="1" s="14">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26" ht="46.25" customHeight="1" s="14">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>S2-05</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>Portfolio map</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>Search and filters</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>1. Search box filters the list and pins by name.
 2. Filter chips: status, type, district.
 3. Filters call GET /projects with parameters.</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>Users can find any project fast</t>
         </is>
       </c>
-      <c r="H25" s="19" t="inlineStr">
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>Brief mockups</t>
         </is>
       </c>
-      <c r="K25" s="19" t="inlineStr">
+      <c r="K26" s="19" t="inlineStr">
         <is>
           <t>S2-01</t>
         </is>
       </c>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n">
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="25" t="inlineStr">
+      <c r="N26" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O25" s="19" t="inlineStr">
+      <c r="O26" s="19" t="inlineStr">
         <is>
           <t>Filter by status, type, district; search by name</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="35.05" customHeight="1" s="14">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="27" ht="35.05" customHeight="1" s="14">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>Users and roles API: group-to-role mapping, project assignment, extra permissions</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing Entra groups and their Nexus role.
 2. Endpoints to assign users to projects. Keep room for extra permissions that later modules will need.
 3. Admin only; every change goes to the audit log.</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Backend for managing access</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H27" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J27" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K26" s="19" t="inlineStr">
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>S1-02</t>
         </is>
       </c>
-      <c r="L26" s="19" t="n"/>
-      <c r="M26" s="19" t="n">
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="25" t="inlineStr">
+      <c r="N27" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O26" s="19" t="inlineStr">
+      <c r="O27" s="19" t="inlineStr">
         <is>
           <t>Changes take effect on next request</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="46.25" customHeight="1" s="14">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="28" ht="46.25" customHeight="1" s="14">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>Catalogue sync (hourly): sites, devices, parameters, units</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1. Scheduled job in apps/worker, every hour (and early when the poll sees unknown ids).
 2. Read all DATOMS assets (list assets: names, nameplate). Sites, asset types and parameters (name, unit) come in the bulk rows. The live poll (S3-03) upserts them the same way, so the catalogue job spends no bulk credits.
@@ -3724,224 +3795,225 @@
 4. Retire safely (docs/07 section 6): only after a complete walk; only rows missed in 2 consecutive complete walks; retire nothing and alert if more than 5% would go.</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>Nexus always knows every DATOMS site and device</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J27" s="19" t="inlineStr">
+      <c r="J28" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K27" s="19" t="inlineStr">
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>S2-02</t>
         </is>
       </c>
-      <c r="L27" s="19" t="inlineStr">
+      <c r="L28" s="19" t="inlineStr">
         <is>
           <t>DATOMS sample + field list (Q21, Q22) + read-only key; id stability (Q11)</t>
         </is>
       </c>
-      <c r="M27" s="19" t="n">
+      <c r="M28" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="25" t="inlineStr">
+      <c r="N28" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O27" s="19" t="inlineStr">
+      <c r="O28" s="19" t="inlineStr">
         <is>
           <t>A new DATOMS asset appears in Nexus within 1 hour of being added to DATOMS, typed from its catalogue category (unmapped categories go to `generic` plus a to-do); assets are retired only by the safe-retire rule. New DATOMS **sites** appear only once DATOMS sends site data (Q21, Q22); until then admins create projects (S3-09). (Reworded 2026-10-14, ADR 0012.)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="46.25" customHeight="1" s="14">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="29" ht="46.25" customHeight="1" s="14">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>S3-02</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>Auto-link new sites and devices on exact match; others to admin to-do list</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>1. When a new DATOMS site appears, link it to a Nexus project if the name matches exactly.
 2. Otherwise add it to an 'unlinked' list for admins.
 3. Same for devices → assets.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>New sites appear automatically, no guessing</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="J29" s="19" t="inlineStr">
         <is>
           <t>Innovo: sites added automatically</t>
         </is>
       </c>
-      <c r="K28" s="19" t="inlineStr">
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>S3-01, S3-09 (ADR 0012 link table). Exact-name matching follows the `linking.name_match` setting (off / suggest / auto, default suggest; ADR 0012).</t>
         </is>
       </c>
-      <c r="L28" s="19" t="n"/>
-      <c r="M28" s="19" t="n">
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="25" t="inlineStr">
+      <c r="N29" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O28" s="19" t="inlineStr">
+      <c r="O29" s="19" t="inlineStr">
         <is>
           <t>No guessed links; unmatched items listed</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="57.45" customHeight="1" s="14">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="30" ht="57.45" customHeight="1" s="14">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>Live sync (every minute by default): bulk endpoint → packets, latest values, statuses, locations, alerts</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1. Job every 60 s by default (per-type interval, ADR 0006): bulk endpoint only (ADR 0010). Fleet mode when every asset is due, otherwise id mode. In dev, only the configured subset (ADR 0005).
 2. Write telemetry.packet (history) and telemetry.latest_packet (current); status, location and alerts on change only.
 3. Insert in batches. No per-poll bookkeeping writes (asset_parameter is insert-only; status observed_at only on change).
-4. Log how long each run takes and the credits used per window.</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
+4. Log how long each run takes and the credits used per window.
+5. DATOMS key for local live runs (decided by Ahmed, 2026-10-22; not built yet): move it from the root `.env` to a git-ignored `packages/datoms-client/.env.datoms`. The same change adds the `.gitignore` entry, points the CLI and the local worker at that file, and updates docs/07 section 3.1 and .env.example.</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Live DATOMS data in Nexus within about 2 poll intervals</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="J30" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K29" s="19" t="inlineStr">
+      <c r="K30" s="19" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n">
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="25" t="inlineStr">
+      <c r="N30" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O29" s="19" t="inlineStr">
+      <c r="O30" s="19" t="inlineStr">
         <is>
           <t>Value in Nexus within 2 poll intervals of DATOMS (N-03)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="14">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="31" ht="23.85" customHeight="1" s="14">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>S3-04</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>History backfill and gap repair after outages (ON HOLD)</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>1. On first run, copy all past data from DATOMS (since Jul 2026 for GHAFWOODS).
 2. Record the last time synced per device.
@@ -3949,294 +4021,294 @@
 4. Test by stopping the worker for an hour.</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Full history, no gaps after outages</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I30" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>Brief: trends</t>
         </is>
       </c>
-      <c r="K30" s="19" t="inlineStr">
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L30" s="19" t="inlineStr">
+      <c r="L31" s="19" t="inlineStr">
         <is>
           <t>ON HOLD (decided 2026-10-08). The bulk endpoint has no history (ADR 0010); Nexus builds its own history from polls from day one. Needs a DATOMS history feed (Q12) and a new ADR to use it. Until then, gaps stay gaps and charts show coverage (ADR 0007).</t>
         </is>
       </c>
-      <c r="M30" s="19" t="n">
+      <c r="M31" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="25" t="inlineStr">
+      <c r="N31" s="25" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O30" s="19" t="inlineStr">
+      <c r="O31" s="19" t="inlineStr">
         <is>
           <t>GHAFWOODS history since Jul 2026 loaded; gaps refilled after a forced outage</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="35.05" customHeight="1" s="14">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="32" ht="35.05" customHeight="1" s="14">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>S3-05</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>Device linking to-do list</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>1. Page listing unlinked DATOMS sites/devices (from S4-02).
 2. Admin picks the project/asset to link each one to.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Admins link anything not matched automatically</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="H32" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I32" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J32" s="19" t="inlineStr">
         <is>
           <t>Innovo: sites added automatically</t>
         </is>
       </c>
-      <c r="K31" s="19" t="inlineStr">
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <t>S3-02</t>
         </is>
       </c>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n">
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="25" t="inlineStr">
+      <c r="N32" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O31" s="19" t="inlineStr">
+      <c r="O32" s="19" t="inlineStr">
         <is>
           <t>Admin links an unmatched device to a project</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="35.05" customHeight="1" s="14">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="33" ht="35.05" customHeight="1" s="14">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>S3-06</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>Integration health page: last sync, errors, delay</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>1. Page showing: last successful sync time, number of errors, delay in minutes.
 2. Red warning if the sync has stopped.</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Admins see if DATOMS data is flowing</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H33" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I32" s="19" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>Risks: DATOMS outage</t>
         </is>
       </c>
-      <c r="K32" s="19" t="inlineStr">
+      <c r="K33" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L32" s="19" t="n"/>
-      <c r="M32" s="19" t="n">
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="25" t="inlineStr">
+      <c r="N33" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O32" s="19" t="inlineStr">
+      <c r="O33" s="19" t="inlineStr">
         <is>
           <t>Shows a stopped sync clearly</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="35.05" customHeight="1" s="14">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="34" ht="35.05" customHeight="1" s="14">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>S3-07</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>Users and roles screen: group-to-role mapping, project assignment</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>1. Page listing groups and roles (from S3-09).
 2. Assign users to projects.
 3. Show each user's role and projects.</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>Admins manage who sees what</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr">
+      <c r="H34" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I34" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="J34" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K33" s="19" t="inlineStr">
+      <c r="K34" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n">
+      <c r="L34" s="19" t="n"/>
+      <c r="M34" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="25" t="inlineStr">
+      <c r="N34" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O33" s="19" t="inlineStr">
+      <c r="O34" s="19" t="inlineStr">
         <is>
           <t>Admin assigns a user to a project</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="35.05" customHeight="1" s="14">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="35" ht="35.05" customHeight="1" s="14">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>S3-08</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>DATOMS connector</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>Partition maintenance job: create future partitions, drop expired ones (critical)</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>1. Worker job `maintenance` (docs/07 §5), daily at 02:00 Asia/Dubai and once at start-up, leader only.
 2. Create partitions ahead for every partitioned table (raw packets, API-call log, events, audit log) using the existing SQL functions; drop partitions past retention through `drop_partitions_before` (with its audit floor).
@@ -4244,73 +4316,73 @@
 (Added 2026-10-14 (architect S1 plan, decision D4).)</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>Inserts never fail for lack of a partition; retention runs on its own</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H35" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I34" s="19" t="inlineStr">
+      <c r="I35" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="J35" s="19" t="inlineStr">
         <is>
           <t>Foundation; N-10 retention</t>
         </is>
       </c>
-      <c r="K34" s="19" t="inlineStr">
+      <c r="K35" s="19" t="inlineStr">
         <is>
           <t>S1-01, S3-01 (worker scheduler and leader lock)</t>
         </is>
       </c>
-      <c r="L34" s="19" t="n"/>
-      <c r="M34" s="19" t="n">
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="25" t="inlineStr">
+      <c r="N35" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O34" s="19" t="inlineStr">
+      <c r="O35" s="19" t="inlineStr">
         <is>
           <t>Integration test: with the clock moved forward 40 days, every partitioned table still accepts inserts and expired partitions are gone; a missing partition raises the health warning. Merged before or with S3-03.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="46.25" customHeight="1" s="14">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="36" ht="46.25" customHeight="1" s="14">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>S3-09</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Admin console</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>Admin projects API (R-63): create and edit projects, assign DATOMS assets</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>1. Write ADR 0012 (project source identity, link table) first.
 2. `/v1/admin/projects`: create, edit and retire projects with the admin-held fields (name, location, district, state, type, client / consultant / PM); never delete (hard rule 8).
@@ -4318,243 +4390,172 @@
 (Added 2026-10-14 (architect S2 plan, decisions D2 and D10).)</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>Admins can build the portfolio until DATOMS sends site data (Q21, Q22, Q43)</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H36" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I36" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="J36" s="19" t="inlineStr">
         <is>
           <t>R-63</t>
         </is>
       </c>
-      <c r="K35" s="19" t="inlineStr">
+      <c r="K36" s="19" t="inlineStr">
         <is>
           <t>ADR 0012 (accepted 2026-10-14), S2-06, S3-01</t>
         </is>
       </c>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n">
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N35" s="25" t="inlineStr">
+      <c r="N36" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O35" s="19" t="inlineStr">
+      <c r="O36" s="19" t="inlineStr">
         <is>
           <t>An admin creates a project and links an asset to it; a non-admin gets 403; the change is in the audit log</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="57.45" customHeight="1" s="14">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37" ht="57.45" customHeight="1" s="14">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>Chart summaries (5-minute, 1-hour, 1-day) as Nexus rollup tables</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>1. Use the rollup functions in db/schema.sql: telemetry.refresh_rollup_5m and refresh_rollup_combine (1 h, 1 day in Asia/Dubai).
 2. Worker rollups job (ADR 0007): refresh_rollup_5m once per CLOSED 5-minute bucket, 2 poll intervals after it ends; re-run only for closed buckets that get late packets; 1 h after the hour's last bucket; 1 d after the Dubai day. No sliding window, no in-memory accumulators.
 3. Return data coverage (packets / expectedPackets) with each bucket.
-4. Check a 30-day query returns in under 1 second.</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="inlineStr">
+4. Check a 30-day query returns in under 1 second.
+5. Note (S3-08 review I6): `refresh_rollup_combine` must not run for an hour whose 5-minute rows were already dropped by retention (older than `retention.rollup_5m_days`). Skip or refuse such hours, or a good hourly row is overwritten with an empty one. See docs/06 section 6a.</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Fast data for every chart</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H37" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr">
+      <c r="I37" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="J37" s="19" t="inlineStr">
         <is>
           <t>Brief: trends</t>
         </is>
       </c>
-      <c r="K36" s="19" t="inlineStr">
+      <c r="K37" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L36" s="19" t="n"/>
-      <c r="M36" s="19" t="n">
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="25" t="inlineStr">
+      <c r="N37" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O36" s="19" t="inlineStr">
+      <c r="O37" s="19" t="inlineStr">
         <is>
           <t>30-day chart query under 1 s</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="57.45" customHeight="1" s="14">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="38" ht="57.45" customHeight="1" s="14">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>S4-02</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Live push: status changes sent to open browsers (Web PubSub)</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>1. When the worker sees a status or location change, publish a slim message to Azure Web PubSub (per project group): no parameter values; values.updated hint; summary.updated; chunked well under 1 MB (docs/10, ADR 0008).
 2. API gives the browser a Web PubSub token with no group-join rights. POST /v1/live/subscriptions checks permission and scope, then joins the connection to project groups on the server.
 3. On any Nexus access change, close the affected live connections so clients re-subscribe through the scope check. Settle with the security-reviewer how the API confirms a connectionId belongs to the caller.</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Changes pushed to browsers live</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H38" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr">
+      <c r="I38" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J37" s="19" t="inlineStr">
+      <c r="J38" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
-        </is>
-      </c>
-      <c r="K37" s="19" t="inlineStr">
-        <is>
-          <t>S3-03</t>
-        </is>
-      </c>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O37" s="19" t="inlineStr">
-        <is>
-          <t>Pin colour changes without refresh; a user whose project access is removed stops receiving that project's messages at once; nothing project-specific is sent to the portfolio group</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="35.05" customHeight="1" s="14">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>S4-03</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>Project page</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>Project summary APIs for the equipment and energy info boxes</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>1. Endpoints GET /projects/{id}/equipment/summary (Box 2) and GET /projects/{id}/energy/summary (Box 3), as in docs/10.
-2. Fill them from the latest DATOMS values: equipment counts from kind = 'physical' assets; energy site totals from site_metric records when DATOMS provides them. Manpower and materials are not built (slots only).</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>The project page loads its boxes</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L1 Info boxes</t>
         </is>
       </c>
       <c r="K38" s="19" t="inlineStr">
@@ -4573,110 +4574,182 @@
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
-          <t>The two endpoints return Box 2 and Box 3 as reported; Boxes 1 and 4 are "coming later" slots</t>
+          <t>Pin colour changes without refresh; a user whose project access is removed stops receiving that project's messages at once; nothing project-specific is sent to the portfolio group</t>
         </is>
       </c>
     </row>
     <row r="39" ht="35.05" customHeight="1" s="14">
       <c r="A39" s="19" t="inlineStr">
         <is>
+          <t>S4-03</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Project page</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>Project summary APIs for the equipment and energy info boxes</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>1. Endpoints GET /projects/{id}/equipment/summary (Box 2) and GET /projects/{id}/energy/summary (Box 3), as in docs/10.
+2. Fill them from the latest DATOMS values: equipment counts from kind = 'physical' assets; energy site totals from site_metric records when DATOMS provides them. Manpower and materials are not built (slots only).</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>The project page loads its boxes</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L1 Info boxes</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="inlineStr">
+        <is>
+          <t>S3-03</t>
+        </is>
+      </c>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O39" s="19" t="inlineStr">
+        <is>
+          <t>The two endpoints return Box 2 and Box 3 as reported; Boxes 1 and 4 are "coming later" slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="35.05" customHeight="1" s="14">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
           <t>S4-04</t>
         </is>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>Project page layout: site map, side panel, equipment and energy info boxes (space kept for manpower and materials later)</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>1. Project page: site map in the centre, equipment and energy info boxes on the right (as structure sheet level 1); leave space for manpower and materials.
 2. Load data from S5-03.
 3. Back button returns to the portfolio map.</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
         <is>
           <t>Level 1 project page</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr">
+      <c r="H40" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J39" s="19" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
         <is>
           <t>Sheet: Level 1</t>
         </is>
       </c>
-      <c r="K39" s="19" t="inlineStr">
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <t>S4-03</t>
         </is>
       </c>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n">
+      <c r="L40" s="19" t="n"/>
+      <c r="M40" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N39" s="25" t="inlineStr">
+      <c r="N40" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O39" s="19" t="inlineStr">
+      <c r="O40" s="19" t="inlineStr">
         <is>
           <t>Matches structure sheet level 1</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="57.45" customHeight="1" s="14">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="41" ht="57.45" customHeight="1" s="14">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>S4-05</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>Asset pins: icon per type, colour per DATOMS status, clustering, map/satellite switch</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>1. Draw one pin per equipment asset (kind = 'physical') at its DATOMS location; no location = "Not on map".
 2. Icon by type: tower crane, hoist, equipment, generator; unknown types use the generic icon.
@@ -4684,177 +4757,105 @@
 4. Turn on clustering and a Map/Satellite switch. 3D uses the same icons with no callouts or pulse (ADR 0008).</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
         <is>
           <t>Live equipment pins on the site map</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J40" s="19" t="inlineStr">
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 blinkers on map</t>
         </is>
       </c>
-      <c r="K40" s="19" t="inlineStr">
+      <c r="K41" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L40" s="19" t="inlineStr">
+      <c r="L41" s="19" t="inlineStr">
         <is>
           <t>Bulk field names for location + status (Q22; DATOMS confirmed the data is in the bulk response); blink vs pulse (Q19)</t>
         </is>
       </c>
-      <c r="M40" s="19" t="n">
+      <c r="M41" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N40" s="25" t="inlineStr">
+      <c r="N41" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O40" s="19" t="inlineStr">
+      <c r="O41" s="19" t="inlineStr">
         <is>
           <t>Running green, Idle amber, Maintenance red, Off grey as reported</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="35.05" customHeight="1" s="14">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="42" ht="35.05" customHeight="1" s="14">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>S4-06</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>Project page</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>Live updates on pins and boxes (WebSocket)</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>1. Connect to Web PubSub with the token from the API.
 2. When a message arrives, update that pin's colour and the info box numbers without reloading.</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Map and boxes update live</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="H42" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="I42" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J41" s="19" t="inlineStr">
+      <c r="J42" s="19" t="inlineStr">
         <is>
           <t>Brief: real-time visibility</t>
         </is>
       </c>
-      <c r="K41" s="19" t="inlineStr">
+      <c r="K42" s="19" t="inlineStr">
         <is>
           <t>S4-02</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="n"/>
-      <c r="M41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O41" s="19" t="inlineStr">
-        <is>
-          <t>Update visible within a minute</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="23.85" customHeight="1" s="14">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>S4-07</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Project page</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>Asset side panel: live readings, faults, last run</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>1. Click a pin = side panel with the asset's latest readings, faults and last run.
-2. Link to the equipment detail page.</t>
-        </is>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
-        <is>
-          <t>Asset details on click</t>
-        </is>
-      </c>
-      <c r="H42" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>DATOMS parity</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="inlineStr">
-        <is>
-          <t>S4-03</t>
         </is>
       </c>
       <c r="L42" s="19" t="n"/>
@@ -4868,283 +4869,287 @@
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
+          <t>Update visible within a minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="23.85" customHeight="1" s="14">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>S4-07</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Project page</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>Asset side panel: live readings, faults, last run</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>1. Click a pin = side panel with the asset's latest readings, faults and last run.
+2. Link to the equipment detail page.</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>Asset details on click</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>DATOMS parity</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="inlineStr">
+        <is>
+          <t>S4-03</t>
+        </is>
+      </c>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O43" s="19" t="inlineStr">
+        <is>
           <t>Opens on pin click</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="35.05" customHeight="1" s="14">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="44" ht="35.05" customHeight="1" s="14">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>S5-01</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>Energy API: generators, solar, mains, loads by area, site totals and CO2 as reported by DATOMS</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint returning per project: generators (running/total), solar generation, mains, total load, loads by area, site totals and CO2 exactly as DATOMS gives them in the bulk response. Site totals are read from site_metric records (ADR 0009); anything missing shows "no data yet".
 2. Compare with the DATOMS Site View for GHAFWOODS; numbers must match.</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G44" s="19" t="inlineStr">
         <is>
           <t>Energy data for box 3 and the energy page</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="H44" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I44" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="J44" s="19" t="inlineStr">
         <is>
           <t>Brief: energy monitoring; Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K43" s="19" t="inlineStr">
+      <c r="K44" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L43" s="19" t="inlineStr">
+      <c r="L44" s="19" t="inlineStr">
         <is>
           <t>Whether DATOMS has site totals (Q3); bulk field names (Q22)</t>
         </is>
       </c>
-      <c r="M43" s="19" t="n">
+      <c r="M44" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N43" s="25" t="inlineStr">
+      <c r="N44" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O43" s="19" t="inlineStr">
+      <c r="O44" s="19" t="inlineStr">
         <is>
           <t>Figures match DATOMS Site View for GHAFWOODS</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="35.05" customHeight="1" s="14">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="45" ht="35.05" customHeight="1" s="14">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>S5-02</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D44" s="19" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E45" s="24" t="inlineStr">
         <is>
           <t>Energy equipment table data incl. owned / hired</t>
         </is>
       </c>
-      <c r="F44" s="19" t="inlineStr">
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing energy equipment: DG ID, description, type (DG/solar/mains), status, owned or hired.
 2. Ownership comes from a DATOMS field (R-31). If DATOMS lacks it, the column is hidden and reported (Q3). Nexus doesn't keep its own ownership register.</t>
         </is>
       </c>
-      <c r="G44" s="19" t="inlineStr">
+      <c r="G45" s="19" t="inlineStr">
         <is>
           <t>Data for the energy table</t>
         </is>
       </c>
-      <c r="H44" s="19" t="inlineStr">
+      <c r="H45" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I44" s="19" t="inlineStr">
+      <c r="I45" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J44" s="19" t="inlineStr">
+      <c r="J45" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K44" s="19" t="inlineStr">
+      <c r="K45" s="19" t="inlineStr">
         <is>
           <t>S5-01</t>
         </is>
       </c>
-      <c r="L44" s="19" t="n"/>
-      <c r="M44" s="19" t="n">
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="25" t="inlineStr">
+      <c r="N45" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O44" s="19" t="inlineStr">
+      <c r="O45" s="19" t="inlineStr">
         <is>
           <t>DG ID, description, status, ownership returned</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="23.85" customHeight="1" s="14">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="46" ht="23.85" customHeight="1" s="14">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>S5-03</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>Trend endpoints: day, week, month, year from summaries</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>1. Endpoints for trends by day, week, month, year.
 2. Read from the rollup tables (S4-01), never raw readings for ranges over 6 h. 5-minute data only within 60 days; older ranges use hourly. Return the resolution used and data coverage per bucket.</t>
         </is>
       </c>
-      <c r="G45" s="19" t="inlineStr">
+      <c r="G46" s="19" t="inlineStr">
         <is>
           <t>Trend data for charts</t>
         </is>
       </c>
-      <c r="H45" s="19" t="inlineStr">
+      <c r="H46" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I45" s="19" t="inlineStr">
+      <c r="I46" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J45" s="19" t="inlineStr">
+      <c r="J46" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 trend graphs</t>
         </is>
       </c>
-      <c r="K45" s="19" t="inlineStr">
+      <c r="K46" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="L45" s="19" t="n"/>
-      <c r="M45" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O45" s="19" t="inlineStr">
-        <is>
-          <t>Each range under 1 s</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="23.85" customHeight="1" s="14">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>S5-04</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D46" s="19" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>Load-test harness: simulate 100+ sites and 1,000 users</t>
-        </is>
-      </c>
-      <c r="F46" s="19" t="inlineStr">
-        <is>
-          <t>1. Write a script (e.g. k6) that simulates 100+ sites of data and 1,000 users opening pages.
-2. Run it against dev and record response times.</t>
-        </is>
-      </c>
-      <c r="G46" s="19" t="inlineStr">
-        <is>
-          <t>Repeatable load test</t>
-        </is>
-      </c>
-      <c r="H46" s="19" t="inlineStr">
-        <is>
-          <t>QA engineer</t>
-        </is>
-      </c>
-      <c r="I46" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J46" s="19" t="inlineStr">
-        <is>
-          <t>Innovo: scalable</t>
-        </is>
-      </c>
-      <c r="K46" s="19" t="n"/>
       <c r="L46" s="19" t="n"/>
       <c r="M46" s="19" t="n">
         <v>2</v>
@@ -5156,137 +5161,133 @@
       </c>
       <c r="O46" s="19" t="inlineStr">
         <is>
+          <t>Each range under 1 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="23.85" customHeight="1" s="14">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>S5-04</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>Load-test harness: simulate 100+ sites and 1,000 users</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>1. Write a script (e.g. k6) that simulates 100+ sites of data and 1,000 users opening pages.
+2. Run it against dev and record response times.</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>Repeatable load test</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="inlineStr">
+        <is>
+          <t>QA engineer</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: scalable</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="n"/>
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O47" s="19" t="inlineStr">
+        <is>
           <t>Repeatable test script in repo</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="35.05" customHeight="1" s="14">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="48" ht="35.05" customHeight="1" s="14">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>S5-05</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>Info box 3 Energy</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>1. Info box 3 on the project page: DGs running/total, total energy load, solar generation, main:solar ratio (structure sheet).
 2. Click = open energy detail.</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="G48" s="19" t="inlineStr">
         <is>
           <t>Energy info box</t>
         </is>
       </c>
-      <c r="H47" s="19" t="inlineStr">
+      <c r="H48" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I47" s="19" t="inlineStr">
+      <c r="I48" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="J48" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 3</t>
         </is>
       </c>
-      <c r="K47" s="19" t="inlineStr">
+      <c r="K48" s="19" t="inlineStr">
         <is>
           <t>S4-03</t>
-        </is>
-      </c>
-      <c r="L47" s="19" t="n"/>
-      <c r="M47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O47" s="19" t="inlineStr">
-        <is>
-          <t>DG running state, energy load, solar, main:solar ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="35.05" customHeight="1" s="14">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>S5-06</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>Energy detail: top ribbon of metrics</t>
-        </is>
-      </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>1. Top ribbon on the energy page with the key energy numbers.
-2. Data from S6-01.</t>
-        </is>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>Energy summary ribbon</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Energy</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>S5-01</t>
         </is>
       </c>
       <c r="L48" s="19" t="n"/>
@@ -5300,282 +5301,282 @@
       </c>
       <c r="O48" s="19" t="inlineStr">
         <is>
-          <t>Matches sheet</t>
+          <t>DG running state, energy load, solar, main:solar ratio</t>
         </is>
       </c>
     </row>
     <row r="49" ht="35.05" customHeight="1" s="14">
       <c r="A49" s="19" t="inlineStr">
         <is>
+          <t>S5-06</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>Energy detail: top ribbon of metrics</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>1. Top ribbon on the energy page with the key energy numbers.
+2. Data from S6-01.</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>Energy summary ribbon</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L2 Energy</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>S5-01</t>
+        </is>
+      </c>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O49" s="19" t="inlineStr">
+        <is>
+          <t>Matches sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35.05" customHeight="1" s="14">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
           <t>S5-07</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>Energy equipment table</t>
         </is>
       </c>
-      <c r="F49" s="19" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>1. Table: DG ID, description, status, ownership (owned/hired), running/off.
 2. Sort and filter.</t>
         </is>
       </c>
-      <c r="G49" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>Energy equipment table</t>
         </is>
       </c>
-      <c r="H49" s="19" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I49" s="19" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K49" s="19" t="inlineStr">
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>S5-02</t>
         </is>
       </c>
-      <c r="L49" s="19" t="n"/>
-      <c r="M49" s="19" t="n">
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="25" t="inlineStr">
+      <c r="N50" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O49" s="19" t="inlineStr">
+      <c r="O50" s="19" t="inlineStr">
         <is>
           <t>Sortable; status live</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="35.05" customHeight="1" s="14">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="51" ht="35.05" customHeight="1" s="14">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>S5-08</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>Energy charts: load trends, distribution, solar trends</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>1. Charts: load trend, load distribution, solar trend.
 2. Range buttons: day, week, month, year.
 3. Data from S6-03.</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>Energy charts</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J50" s="19" t="inlineStr">
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Energy</t>
         </is>
       </c>
-      <c r="K50" s="19" t="inlineStr">
+      <c r="K51" s="19" t="inlineStr">
         <is>
           <t>S5-03</t>
         </is>
       </c>
-      <c r="L50" s="19" t="n"/>
-      <c r="M50" s="19" t="n">
+      <c r="L51" s="19" t="n"/>
+      <c r="M51" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N50" s="25" t="inlineStr">
+      <c r="N51" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O50" s="19" t="inlineStr">
+      <c r="O51" s="19" t="inlineStr">
         <is>
           <t>Range switch day/week/month/year</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="35.05" customHeight="1" s="14">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="52" ht="35.05" customHeight="1" s="14">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>Equipment API: ID, name, type, make/model, status + native DATOMS fields</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint listing equipment per project (kind = 'physical' only): ID, name, type, make/model, current status, plus extra nameplate fields as optional columns.
 2. Every parameter DATOMS sends for a device is available from GET /assets/{id} (device card). The list endpoint carries no live values (ADR 0008).</t>
         </is>
       </c>
-      <c r="G51" s="19" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>Data for the equipment table</t>
         </is>
       </c>
-      <c r="H51" s="19" t="inlineStr">
+      <c r="H52" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I51" s="19" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J51" s="19" t="inlineStr">
+      <c r="J52" s="19" t="inlineStr">
         <is>
           <t>Brief: crane utilisation, asset tracking; Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K51" s="19" t="inlineStr">
+      <c r="K52" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
-        </is>
-      </c>
-      <c r="L51" s="19" t="n"/>
-      <c r="M51" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N51" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O51" s="19" t="inlineStr">
-        <is>
-          <t>All DATOMS parameters available per asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="35.05" customHeight="1" s="14">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>S6-02</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>Device card API: latest values, today's running timeline</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>1. Endpoint for one device: latest values of every parameter.
-2. Today's timeline of status changes (running, idle, off) as observed by Nexus in polls, labelled "observed by Nexus" (ADR 0007). DATOMS's own status history is used only if a later ADR adds it.</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>Data for the device card</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Equipment</t>
-        </is>
-      </c>
-      <c r="K52" s="19" t="inlineStr">
-        <is>
-          <t>S6-01</t>
         </is>
       </c>
       <c r="L52" s="19" t="n"/>
@@ -5589,358 +5590,358 @@
       </c>
       <c r="O52" s="19" t="inlineStr">
         <is>
-          <t>Timeline shows the status changes Nexus observed, labelled "observed by Nexus", accurate to one poll interval</t>
+          <t>All DATOMS parameters available per asset</t>
         </is>
       </c>
     </row>
     <row r="53" ht="35.05" customHeight="1" s="14">
       <c r="A53" s="19" t="inlineStr">
         <is>
+          <t>S6-02</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>Device card API: latest values, today's running timeline</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>1. Endpoint for one device: latest values of every parameter.
+2. Today's timeline of status changes (running, idle, off) as observed by Nexus in polls, labelled "observed by Nexus" (ADR 0007). DATOMS's own status history is used only if a later ADR adds it.</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>Data for the device card</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I53" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>Sheet: L2 Equipment</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="inlineStr">
+        <is>
+          <t>S6-01</t>
+        </is>
+      </c>
+      <c r="L53" s="19" t="n"/>
+      <c r="M53" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O53" s="19" t="inlineStr">
+        <is>
+          <t>Timeline shows the status changes Nexus observed, labelled "observed by Nexus", accurate to one poll interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="35.05" customHeight="1" s="14">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
           <t>S6-03</t>
         </is>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D53" s="19" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E53" s="24" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>Info box 2 counts: tower cranes, hoists, all equipment (total / idle)</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>1. Counts per project (kind = 'physical' only): tower cranes total/idle, hoists total/idle, all equipment total/idle, using DATOMS statuses.
 2. Add to the project summary (S5-03).</t>
         </is>
       </c>
-      <c r="G53" s="19" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>Numbers for info box 2</t>
         </is>
       </c>
-      <c r="H53" s="19" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>Backend developer</t>
         </is>
       </c>
-      <c r="I53" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 2</t>
         </is>
       </c>
-      <c r="K53" s="19" t="inlineStr">
+      <c r="K54" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
         </is>
       </c>
-      <c r="L53" s="19" t="n"/>
-      <c r="M53" s="19" t="n">
+      <c r="L54" s="19" t="n"/>
+      <c r="M54" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="25" t="inlineStr">
+      <c r="N54" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O53" s="19" t="inlineStr">
+      <c r="O54" s="19" t="inlineStr">
         <is>
           <t>Counts follow DATOMS statuses</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="23.85" customHeight="1" s="14">
-      <c r="A54" s="19" t="inlineStr">
+    <row r="55" ht="23.85" customHeight="1" s="14">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>S6-04</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>Notifications from the DATOMS bulk response, and API (filter by site, asset, type)</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>1. In the live poll: take DATOMS alerts and faults from the bulk response (ADR 0010; no separate events job).
 2. Store them; endpoint to list with filters: site, asset, type, date. "Mark all read" moves a read marker (docs/06 section 3, item 11).
 3. Show them exactly as DATOMS sends them.</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="G55" s="19" t="inlineStr">
         <is>
           <t>Notifications in Nexus</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
+      <c r="H55" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="I55" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J54" s="19" t="inlineStr">
+      <c r="J55" s="19" t="inlineStr">
         <is>
           <t>Innovo: alerts as they come</t>
         </is>
       </c>
-      <c r="K54" s="19" t="inlineStr">
+      <c r="K55" s="19" t="inlineStr">
         <is>
           <t>S3-03</t>
         </is>
       </c>
-      <c r="L54" s="19" t="inlineStr">
+      <c r="L55" s="19" t="inlineStr">
         <is>
           <t>Alert field names in the bulk response (Q22)</t>
         </is>
       </c>
-      <c r="M54" s="19" t="n">
+      <c r="M55" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N54" s="25" t="inlineStr">
+      <c r="N55" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O54" s="19" t="inlineStr">
+      <c r="O55" s="19" t="inlineStr">
         <is>
           <t>Same notifications as DATOMS, newest first</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="23.85" customHeight="1" s="14">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="56" ht="23.85" customHeight="1" s="14">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>S6-05</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>Info box 2 component</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>1. Info box 2: tower cranes count/idle, hoists count/idle, total equipment/idle (structure sheet).
 2. Click = open equipment detail.</t>
         </is>
       </c>
-      <c r="G55" s="19" t="inlineStr">
+      <c r="G56" s="19" t="inlineStr">
         <is>
           <t>Equipment info box</t>
         </is>
       </c>
-      <c r="H55" s="19" t="inlineStr">
+      <c r="H56" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I55" s="19" t="inlineStr">
+      <c r="I56" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>Sheet: L1 Info box 2</t>
         </is>
       </c>
-      <c r="K55" s="19" t="inlineStr">
+      <c r="K56" s="19" t="inlineStr">
         <is>
           <t>S6-03</t>
         </is>
       </c>
-      <c r="L55" s="19" t="n"/>
-      <c r="M55" s="19" t="n">
+      <c r="L56" s="19" t="n"/>
+      <c r="M56" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N55" s="25" t="inlineStr">
+      <c r="N56" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O55" s="19" t="inlineStr">
+      <c r="O56" s="19" t="inlineStr">
         <is>
           <t>Count / idle per type</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="46.25" customHeight="1" s="14">
-      <c r="A56" s="19" t="inlineStr">
+    <row r="57" ht="46.25" customHeight="1" s="14">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>S6-06</t>
         </is>
       </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C56" s="19" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>Equipment detail table: sort, filter by type and status</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>1. Table with Equipment ID, Name, Type, Model/Make, Current Status + extra DATOMS fields.
 2. Filter by type and status; sort; search.</t>
         </is>
       </c>
-      <c r="G56" s="19" t="inlineStr">
+      <c r="G57" s="19" t="inlineStr">
         <is>
           <t>Equipment detail page</t>
         </is>
       </c>
-      <c r="H56" s="19" t="inlineStr">
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I56" s="19" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J56" s="19" t="inlineStr">
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>Sheet: L2 Equipment</t>
         </is>
       </c>
-      <c r="K56" s="19" t="inlineStr">
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <t>S6-01</t>
-        </is>
-      </c>
-      <c r="L56" s="19" t="n"/>
-      <c r="M56" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N56" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O56" s="19" t="inlineStr">
-        <is>
-          <t>All sheet columns plus native fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="79.84999999999999" customHeight="1" s="14">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>S6-07</t>
-        </is>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>Device card</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>1. Card opened from a table row or a map pin.
-2. Shows all latest values and today's timeline.</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="inlineStr">
-        <is>
-          <t>Device card</t>
-        </is>
-      </c>
-      <c r="H57" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>Sheet: L2 Equipment</t>
-        </is>
-      </c>
-      <c r="K57" s="19" t="inlineStr">
-        <is>
-          <t>S6-02</t>
         </is>
       </c>
       <c r="L57" s="19" t="n"/>
@@ -5954,14 +5955,14 @@
       </c>
       <c r="O57" s="19" t="inlineStr">
         <is>
-          <t>Opens from table row or pin</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="57.45" customHeight="1" s="14">
+          <t>All sheet columns plus native fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="79.84999999999999" customHeight="1" s="14">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>S6-08</t>
+          <t>S6-07</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
@@ -5976,23 +5977,23 @@
       </c>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>Notifications bell and list with filters</t>
+          <t>Device card</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>1. Bell in header shows unread count.
-2. Click = list of notifications, newest first, with filters.</t>
+          <t>1. Card opened from a table row or a map pin.
+2. Shows all latest values and today's timeline.</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>Notifications in the header</t>
+          <t>Device card</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
@@ -6007,12 +6008,12 @@
       </c>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>Innovo: alerts as they come</t>
+          <t>Sheet: L2 Equipment</t>
         </is>
       </c>
       <c r="K58" s="19" t="inlineStr">
         <is>
-          <t>S6-04</t>
+          <t>S6-02</t>
         </is>
       </c>
       <c r="L58" s="19" t="n"/>
@@ -6026,181 +6027,254 @@
       </c>
       <c r="O58" s="19" t="inlineStr">
         <is>
+          <t>Opens from table row or pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="57.45" customHeight="1" s="14">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>S6-08</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>Notifications bell and list with filters</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>1. Bell in header shows unread count.
+2. Click = list of notifications, newest first, with filters.</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>Notifications in the header</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I59" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: alerts as they come</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="inlineStr">
+        <is>
+          <t>S6-04</t>
+        </is>
+      </c>
+      <c r="L59" s="19" t="n"/>
+      <c r="M59" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N59" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O59" s="19" t="inlineStr">
+        <is>
           <t>Unread count; filter by site and asset</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="35.05" customHeight="1" s="14">
-      <c r="A59" s="19" t="inlineStr">
+    <row r="60" ht="35.05" customHeight="1" s="14">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>S7-01</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>DATOMS explorer</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E60" s="24" t="inlineStr">
         <is>
           <t>Explorer API: any device, any parameter, time range, min / avg / max, compare</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>1. Endpoint: for any device, list its parameters.
 2. Endpoint: values for chosen parameters and time range, with min / average / max.
 3. Works for any new parameter without code changes.</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
+      <c r="G60" s="19" t="inlineStr">
         <is>
           <t>Data for 'all DATOMS data'</t>
         </is>
       </c>
-      <c r="H59" s="19" t="inlineStr">
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>Data / integration engineer</t>
         </is>
       </c>
-      <c r="I59" s="19" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J59" s="19" t="inlineStr">
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K59" s="19" t="inlineStr">
+      <c r="K60" s="19" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="L59" s="19" t="n"/>
-      <c r="M59" s="19" t="n">
+      <c r="L60" s="19" t="n"/>
+      <c r="M60" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N59" s="25" t="inlineStr">
+      <c r="N60" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O59" s="19" t="inlineStr">
+      <c r="O60" s="19" t="inlineStr">
         <is>
           <t>New parameter types appear with no code change</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="23.85" customHeight="1" s="14">
-      <c r="A60" s="19" t="inlineStr">
+    <row r="61" ht="23.85" customHeight="1" s="14">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>S7-02</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E60" s="24" t="inlineStr">
+      <c r="E61" s="24" t="inlineStr">
         <is>
           <t>Security hardening: private endpoints, key rotation, firewall rules, web security headers</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>1. Put PostgreSQL and Blob behind private endpoints.
 2. Rotate keys in Key Vault.
 3. Firewall: only Container Apps can reach the database.
 4. Web app security headers and CSP (docs/08 §6) in staticwebapp.config.json: a CSP that allows only the MSAL (Entra) and ArcGIS domains plus the API and Web PubSub hosts; HSTS, X-Content-Type-Options, Referrer-Policy, frame-ancestors none. (Added by the S0 plan, 2026-10-09.)
-5. ArcGIS (security review of S0-09, PR #19, accepted by Ahmed 2026-10-14): the ArcGIS SDK puts the key in tile, style and elevation URLs (`token=`). Exclude `*.arcgis.com` and `*.arcgisonline.com` from App Insights automatic dependency tracking and strip `token=` in a telemetry initializer. CSP for the map (assets self-hosted, decision L6): `script-src 'self' 'wasm-unsafe-eval'`; `worker-src 'self' blob:`; `img-src 'self' data: blob: https://*.arcgis.com`; `connect-src` with `https://*.arcgis.com` (basemapstyles-api, ibasemaps-api, elevation3d, basemaps3d, static); `font-src 'self'`; check Calcite styles under `style-src`; no `unsafe-eval` (verify with a report-only CSP first). `Referrer-Policy: strict-origin-when-cross-origin`, never `no-referrer` (the ArcGIS key is referrer-restricted). Details in docs/09.</t>
-        </is>
-      </c>
-      <c r="G60" s="19" t="inlineStr">
+5. ArcGIS (security review of S0-09, PR #19, accepted by Ahmed 2026-10-14): the ArcGIS SDK puts the key in tile, style and elevation URLs (`token=`). Exclude `*.arcgis.com` and `*.arcgisonline.com` from App Insights automatic dependency tracking and strip `token=` in a telemetry initializer. CSP for the map (assets self-hosted, decision L6): `script-src 'self' 'wasm-unsafe-eval'`; `worker-src 'self' blob:`; `img-src 'self' data: blob: https://*.arcgis.com`; `connect-src` with `https://*.arcgis.com` (basemapstyles-api, ibasemaps-api, elevation3d, basemaps3d, static); `font-src 'self'`; check Calcite styles under `style-src`; no `unsafe-eval` (verify with a report-only CSP first). `Referrer-Policy: strict-origin-when-cross-origin`, never `no-referrer` (the ArcGIS key is referrer-restricted). Details in docs/09.
+6. ArcGIS asset self-hosting (decision L6, Ahmed 2026-10-22) is a separate PR merged before this task: copy the needed `@arcgis/core` assets and set `esriConfig.assetsPath`, so the CSP in step 5 needs no Esri CDN (docs/09 section 1).</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
         <is>
           <t>Data not reachable from the internet; the web app sends a CSP and security headers</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="J61" s="19" t="inlineStr">
         <is>
           <t>Innovo: security</t>
         </is>
       </c>
-      <c r="K60" s="19" t="n"/>
-      <c r="L60" s="19" t="n"/>
-      <c r="M60" s="19" t="n">
+      <c r="K61" s="19" t="n"/>
+      <c r="L61" s="19" t="n"/>
+      <c r="M61" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N60" s="25" t="inlineStr">
+      <c r="N61" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O60" s="19" t="inlineStr">
+      <c r="O61" s="19" t="inlineStr">
         <is>
           <t>Databases unreachable from internet; a header scan of the prod web URL shows the CSP and security headers, and sign-in and the map still work with the CSP on</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="23.85" customHeight="1" s="14">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="62" ht="23.85" customHeight="1" s="14">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>S7-03</t>
         </is>
       </c>
-      <c r="B61" s="19" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>DATOMS explorer</t>
         </is>
       </c>
-      <c r="E61" s="24" t="inlineStr">
+      <c r="E62" s="24" t="inlineStr">
         <is>
           <t>Explorer screens: site and device picker, parameter tiles, chart with ranges and compare</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>1. Pick site, then device.
 2. Tiles with latest value of every parameter.
@@ -6208,309 +6282,240 @@
 4. Compare several parameters on one chart.</t>
         </is>
       </c>
-      <c r="G61" s="19" t="inlineStr">
+      <c r="G62" s="19" t="inlineStr">
         <is>
           <t>Explorer showing all DATOMS data</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
+      <c r="H62" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I61" s="19" t="inlineStr">
+      <c r="I62" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J61" s="19" t="inlineStr">
+      <c r="J62" s="19" t="inlineStr">
         <is>
           <t>Innovo: show all DATOMS data</t>
         </is>
       </c>
-      <c r="K61" s="19" t="inlineStr">
+      <c r="K62" s="19" t="inlineStr">
         <is>
           <t>S7-01</t>
         </is>
       </c>
-      <c r="L61" s="19" t="n"/>
-      <c r="M61" s="19" t="n">
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N61" s="25" t="inlineStr">
+      <c r="N62" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O61" s="19" t="inlineStr">
+      <c r="O62" s="19" t="inlineStr">
         <is>
           <t>Matches DATOMS parameter view</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="35.05" customHeight="1" s="14">
-      <c r="A62" s="19" t="inlineStr">
+    <row r="63" ht="35.05" customHeight="1" s="14">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>S7-04</t>
         </is>
       </c>
-      <c r="B62" s="19" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E62" s="24" t="inlineStr">
+      <c r="E63" s="24" t="inlineStr">
         <is>
           <t>Automated permission tests for every role</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>1. Create a test user for each role.
 2. Automated tests: each role can open what it should, and is refused everything else.</t>
         </is>
       </c>
-      <c r="G62" s="19" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
         <is>
           <t>Permissions proven by tests</t>
         </is>
       </c>
-      <c r="H62" s="19" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
         <is>
           <t>QA engineer</t>
         </is>
       </c>
-      <c r="I62" s="19" t="inlineStr">
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J62" s="19" t="inlineStr">
+      <c r="J63" s="19" t="inlineStr">
         <is>
           <t>Innovo: permissions</t>
         </is>
       </c>
-      <c r="K62" s="19" t="inlineStr">
+      <c r="K63" s="19" t="inlineStr">
         <is>
           <t>S2-06</t>
         </is>
       </c>
-      <c r="L62" s="19" t="n"/>
-      <c r="M62" s="19" t="n">
+      <c r="L63" s="19" t="n"/>
+      <c r="M63" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N62" s="25" t="inlineStr">
+      <c r="N63" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O62" s="19" t="inlineStr">
+      <c r="O63" s="19" t="inlineStr">
         <is>
           <t>Every role's allowed and denied paths covered</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="35.05" customHeight="1" s="14">
-      <c r="A63" s="19" t="inlineStr">
+    <row r="64" ht="35.05" customHeight="1" s="14">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>S7-05</t>
         </is>
       </c>
-      <c r="B63" s="19" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E63" s="24" t="inlineStr">
+      <c r="E64" s="24" t="inlineStr">
         <is>
           <t>Production environment from code</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>1. Deploy 'nexus-prod' from the same Bicep files.
 2. Separate keys and Entra settings for production.</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>Production environment ready</t>
         </is>
       </c>
-      <c r="H63" s="19" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J63" s="19" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
       </c>
-      <c r="K63" s="19" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <t>S0-02</t>
         </is>
       </c>
-      <c r="L63" s="19" t="n"/>
-      <c r="M63" s="19" t="n">
+      <c r="L64" s="19" t="n"/>
+      <c r="M64" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N63" s="25" t="inlineStr">
+      <c r="N64" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O63" s="19" t="inlineStr">
+      <c r="O64" s="19" t="inlineStr">
         <is>
           <t>Prod built from the same Bicep files</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="23.85" customHeight="1" s="14">
-      <c r="A64" s="19" t="inlineStr">
+    <row r="65" ht="23.85" customHeight="1" s="14">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>S7-06</t>
         </is>
       </c>
-      <c r="B64" s="19" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E64" s="24" t="inlineStr">
+      <c r="E65" s="24" t="inlineStr">
         <is>
           <t>Tablet and mobile polish</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>1. Test every screen on a phone and a tablet.
 2. Fix layouts, touch targets, drawers.</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="G65" s="19" t="inlineStr">
         <is>
           <t>Polished tablet and mobile</t>
         </is>
       </c>
-      <c r="H64" s="19" t="inlineStr">
+      <c r="H65" s="19" t="inlineStr">
         <is>
           <t>Frontend developer</t>
         </is>
       </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="I65" s="19" t="inlineStr">
         <is>
           <t>Colleague (frontend)</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="J65" s="19" t="inlineStr">
         <is>
           <t>Innovo: devices</t>
-        </is>
-      </c>
-      <c r="K64" s="19" t="n"/>
-      <c r="L64" s="19" t="n"/>
-      <c r="M64" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O64" s="19" t="inlineStr">
-        <is>
-          <t>All screens usable on phone and tablet</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="35.05" customHeight="1" s="14">
-      <c r="A65" s="19" t="inlineStr">
-        <is>
-          <t>S7-07</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E65" s="24" t="inlineStr">
-        <is>
-          <t>Stale and missing data states: last updated, gaps shown as gaps</t>
-        </is>
-      </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>1. Show 'last updated' on every live box.
-2. Show missing data as a gap in charts, never as zero.
-3. Grey 'offline' state when DATOMS reports it.</t>
-        </is>
-      </c>
-      <c r="G65" s="19" t="inlineStr">
-        <is>
-          <t>Users can trust what they see</t>
-        </is>
-      </c>
-      <c r="H65" s="19" t="inlineStr">
-        <is>
-          <t>Frontend developer</t>
-        </is>
-      </c>
-      <c r="I65" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J65" s="19" t="inlineStr">
-        <is>
-          <t>Risks: data quality</t>
         </is>
       </c>
       <c r="K65" s="19" t="n"/>
@@ -6525,202 +6530,202 @@
       </c>
       <c r="O65" s="19" t="inlineStr">
         <is>
+          <t>All screens usable on phone and tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="35.05" customHeight="1" s="14">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>S7-07</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>Stale and missing data states: last updated, gaps shown as gaps</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>1. Show 'last updated' on every live box.
+2. Show missing data as a gap in charts, never as zero.
+3. Grey 'offline' state when DATOMS reports it.</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>Users can trust what they see</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>Risks: data quality</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="n"/>
+      <c r="L66" s="19" t="n"/>
+      <c r="M66" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O66" s="19" t="inlineStr">
+        <is>
           <t>No zeros shown for missing data</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="23.85" customHeight="1" s="14">
-      <c r="A66" s="19" t="inlineStr">
+    <row r="67" ht="23.85" customHeight="1" s="14">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>S8-01</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D66" s="19" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E66" s="24" t="inlineStr">
+      <c r="E67" s="24" t="inlineStr">
         <is>
           <t>Load test 100+ sites and 1,000 users; fix bottlenecks</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>1. Run the S6-04 load test at 100+ sites and 1,000 users.
 2. Find slow endpoints; add indexes or caching.
 3. Re-run until pages load in under 2 seconds.</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G67" s="19" t="inlineStr">
         <is>
           <t>Proven performance at scale</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="H67" s="19" t="inlineStr">
         <is>
           <t>QA engineer</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="I67" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="J67" s="19" t="inlineStr">
         <is>
           <t>Innovo: scalable</t>
         </is>
       </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="K67" s="19" t="inlineStr">
         <is>
           <t>S5-04</t>
         </is>
       </c>
-      <c r="L66" s="19" t="n"/>
-      <c r="M66" s="19" t="n">
+      <c r="L67" s="19" t="n"/>
+      <c r="M67" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N66" s="25" t="inlineStr">
+      <c r="N67" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O66" s="19" t="inlineStr">
+      <c r="O67" s="19" t="inlineStr">
         <is>
           <t>Pages under 2 s at target load</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="35.05" customHeight="1" s="14">
-      <c r="A67" s="19" t="inlineStr">
+    <row r="68" ht="35.05" customHeight="1" s="14">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>S8-02</t>
         </is>
       </c>
-      <c r="B67" s="19" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C67" s="19" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>Hardening</t>
         </is>
       </c>
-      <c r="E67" s="24" t="inlineStr">
+      <c r="E68" s="24" t="inlineStr">
         <is>
           <t>Backups, restore test, monitoring alerts (sync stopped, error spikes)</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>1. Turn on daily database backups; do one restore test.
 2. Alerts in Application Insights: sync stopped, error spike, slow responses.</t>
         </is>
       </c>
-      <c r="G67" s="19" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>Backups and alerts working</t>
         </is>
       </c>
-      <c r="H67" s="19" t="inlineStr">
+      <c r="H68" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I67" s="19" t="inlineStr">
+      <c r="I68" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J67" s="19" t="inlineStr">
+      <c r="J68" s="19" t="inlineStr">
         <is>
           <t>Risks</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="n"/>
-      <c r="L67" s="19" t="n"/>
-      <c r="M67" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N67" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O67" s="19" t="inlineStr">
-        <is>
-          <t>Restore proven; alert fires on stopped sync</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="23.85" customHeight="1" s="14">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>S8-03</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>Accessibility and performance pass</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>1. Keyboard navigation and visible focus.
-2. Check contrast.
-3. Reduce bundle size; lazy-load heavy pages.</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>Accessible and fast</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
-        <is>
-          <t>UI/UX designer</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
-        <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>Quality</t>
         </is>
       </c>
       <c r="K68" s="19" t="n"/>
@@ -6735,14 +6740,14 @@
       </c>
       <c r="O68" s="19" t="inlineStr">
         <is>
-          <t>Keyboard navigation; fast first load</t>
+          <t>Restore proven; alert fires on stopped sync</t>
         </is>
       </c>
     </row>
     <row r="69" ht="23.85" customHeight="1" s="14">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>S8-04</t>
+          <t>S8-03</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
@@ -6762,23 +6767,24 @@
       </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>Report a data issue link</t>
+          <t>Accessibility and performance pass</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
-          <t>1. 'Report a data issue' link on data boxes.
-2. Sends the site, asset and description to the site/technical team contact.</t>
+          <t>1. Keyboard navigation and visible focus.
+2. Check contrast.
+3. Reduce bundle size; lazy-load heavy pages.</t>
         </is>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>Data problems reach the right team</t>
+          <t>Accessible and fast</t>
         </is>
       </c>
       <c r="H69" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>UI/UX designer</t>
         </is>
       </c>
       <c r="I69" s="19" t="inlineStr">
@@ -6788,218 +6794,219 @@
       </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t>Risks: data quality</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="K69" s="19" t="n"/>
       <c r="L69" s="19" t="n"/>
       <c r="M69" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O69" s="19" t="inlineStr">
+        <is>
+          <t>Keyboard navigation; fast first load</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="23.85" customHeight="1" s="14">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>S8-04</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>Report a data issue link</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>1. 'Report a data issue' link on data boxes.
+2. Sends the site, asset and description to the site/technical team contact.</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
+        <is>
+          <t>Data problems reach the right team</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>Risks: data quality</t>
+        </is>
+      </c>
+      <c r="K70" s="19" t="n"/>
+      <c r="L70" s="19" t="n"/>
+      <c r="M70" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N69" s="25" t="inlineStr">
+      <c r="N70" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O69" s="19" t="inlineStr">
+      <c r="O70" s="19" t="inlineStr">
         <is>
           <t>Sends issue to site/technical team contact</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="35.05" customHeight="1" s="14">
-      <c r="A70" s="19" t="inlineStr">
+    <row r="71" ht="35.05" customHeight="1" s="14">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>S8-05</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C70" s="19" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E70" s="24" t="inlineStr">
+      <c r="E71" s="24" t="inlineStr">
         <is>
           <t>Penetration test and fixes</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>1. Book an external penetration test.
 2. Fix all high and critical findings.
 3. Re-test.</t>
         </is>
       </c>
-      <c r="G70" s="19" t="inlineStr">
+      <c r="G71" s="19" t="inlineStr">
         <is>
           <t>Security signed off</t>
         </is>
       </c>
-      <c r="H70" s="19" t="inlineStr">
+      <c r="H71" s="19" t="inlineStr">
         <is>
           <t>Security engineer</t>
         </is>
       </c>
-      <c r="I70" s="19" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J70" s="19" t="inlineStr">
+      <c r="J71" s="19" t="inlineStr">
         <is>
           <t>Innovo: security</t>
         </is>
       </c>
-      <c r="K70" s="19" t="inlineStr">
+      <c r="K71" s="19" t="inlineStr">
         <is>
           <t>S7-05</t>
         </is>
       </c>
-      <c r="L70" s="19" t="inlineStr">
+      <c r="L71" s="19" t="inlineStr">
         <is>
           <t>External pen-test slot</t>
         </is>
       </c>
-      <c r="M70" s="19" t="n">
+      <c r="M71" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N70" s="25" t="inlineStr">
+      <c r="N71" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O70" s="19" t="inlineStr">
+      <c r="O71" s="19" t="inlineStr">
         <is>
           <t>No high or critical findings open</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="14">
-      <c r="A71" s="19" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="14">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>S8-06</t>
         </is>
       </c>
-      <c r="B71" s="19" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="C71" s="19" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E71" s="24" t="inlineStr">
+      <c r="E72" s="24" t="inlineStr">
         <is>
           <t>Short user guide</t>
         </is>
       </c>
-      <c r="F71" s="19" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>1. One-page guide per role: how to find a project, read the boxes, open details.</t>
         </is>
       </c>
-      <c r="G71" s="19" t="inlineStr">
+      <c r="G72" s="19" t="inlineStr">
         <is>
           <t>User guide</t>
         </is>
       </c>
-      <c r="H71" s="19" t="inlineStr">
+      <c r="H72" s="19" t="inlineStr">
         <is>
           <t>Product owner</t>
         </is>
       </c>
-      <c r="I71" s="19" t="inlineStr">
+      <c r="I72" s="19" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="J71" s="19" t="inlineStr">
+      <c r="J72" s="19" t="inlineStr">
         <is>
           <t>Adoption</t>
-        </is>
-      </c>
-      <c r="K71" s="19" t="n"/>
-      <c r="L71" s="19" t="n"/>
-      <c r="M71" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N71" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O71" s="19" t="inlineStr">
-        <is>
-          <t>One-page guide per role</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="23.85" customHeight="1" s="14">
-      <c r="A72" s="19" t="inlineStr">
-        <is>
-          <t>S9-01</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="C72" s="19" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D72" s="19" t="inlineStr">
-        <is>
-          <t>Pilot</t>
-        </is>
-      </c>
-      <c r="E72" s="24" t="inlineStr">
-        <is>
-          <t>Runbook and handover docs</t>
-        </is>
-      </c>
-      <c r="F72" s="19" t="inlineStr">
-        <is>
-          <t>1. Write: how to deploy, how to restore, how to add a new data source, who to call when DATOMS is down.</t>
-        </is>
-      </c>
-      <c r="G72" s="19" t="inlineStr">
-        <is>
-          <t>Runbook so anyone can operate Nexus</t>
-        </is>
-      </c>
-      <c r="H72" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I72" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J72" s="19" t="inlineStr">
-        <is>
-          <t>Risks: knowledge</t>
         </is>
       </c>
       <c r="K72" s="19" t="n"/>
@@ -7014,154 +7021,154 @@
       </c>
       <c r="O72" s="19" t="inlineStr">
         <is>
-          <t>New developer can deploy from the docs</t>
+          <t>One-page guide per role</t>
         </is>
       </c>
     </row>
     <row r="73" ht="23.85" customHeight="1" s="14">
       <c r="A73" s="19" t="inlineStr">
         <is>
+          <t>S9-01</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>Runbook and handover docs</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>1. Write: how to deploy, how to restore, how to add a new data source, who to call when DATOMS is down.</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>Runbook so anyone can operate Nexus</t>
+        </is>
+      </c>
+      <c r="H73" s="19" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="I73" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>Risks: knowledge</t>
+        </is>
+      </c>
+      <c r="K73" s="19" t="n"/>
+      <c r="L73" s="19" t="n"/>
+      <c r="M73" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N73" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O73" s="19" t="inlineStr">
+        <is>
+          <t>New developer can deploy from the docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="23.85" customHeight="1" s="14">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
           <t>S9-02</t>
         </is>
       </c>
-      <c r="B73" s="19" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="D73" s="19" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="E73" s="24" t="inlineStr">
+      <c r="E74" s="24" t="inlineStr">
         <is>
           <t>User acceptance testing on GHAFWOODS with pilot users</t>
         </is>
       </c>
-      <c r="F73" s="19" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>1. Give pilot users access on GHAFWOODS in **prod** (there is no test environment, ADR 0008): only pilot users are assigned to the Entra app during the pilot.
 2. Walk through each screen with them.
 3. Record issues in the backlog.</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>Pilot feedback list</t>
         </is>
       </c>
-      <c r="H73" s="19" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
         <is>
           <t>Product owner</t>
         </is>
       </c>
-      <c r="I73" s="19" t="inlineStr">
+      <c r="I74" s="19" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="J73" s="19" t="inlineStr">
+      <c r="J74" s="19" t="inlineStr">
         <is>
           <t>Brief objectives</t>
         </is>
       </c>
-      <c r="K73" s="19" t="n"/>
-      <c r="L73" s="19" t="inlineStr">
+      <c r="K74" s="19" t="n"/>
+      <c r="L74" s="19" t="inlineStr">
         <is>
           <t>Pilot users' time</t>
         </is>
       </c>
-      <c r="M73" s="19" t="n">
+      <c r="M74" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N73" s="25" t="inlineStr">
+      <c r="N74" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O73" s="19" t="inlineStr">
+      <c r="O74" s="19" t="inlineStr">
         <is>
           <t>Pilot users sign off each screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="23.85" customHeight="1" s="14">
-      <c r="A74" s="19" t="inlineStr">
-        <is>
-          <t>S9-03</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Pilot</t>
-        </is>
-      </c>
-      <c r="E74" s="24" t="inlineStr">
-        <is>
-          <t>Bug fixes from pilot (backend)</t>
-        </is>
-      </c>
-      <c r="F74" s="19" t="inlineStr">
-        <is>
-          <t>1. Fix backend issues from the pilot, most important first.</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="inlineStr">
-        <is>
-          <t>Backend pilot issues closed</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>Backend developer</t>
-        </is>
-      </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="n"/>
-      <c r="K74" s="19" t="inlineStr">
-        <is>
-          <t>S9-02</t>
-        </is>
-      </c>
-      <c r="L74" s="19" t="n"/>
-      <c r="M74" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N74" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O74" s="19" t="inlineStr">
-        <is>
-          <t>All pilot blockers fixed</t>
         </is>
       </c>
     </row>
     <row r="75" ht="23.85" customHeight="1" s="14">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>S9-04</t>
+          <t>S9-03</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
@@ -7181,27 +7188,27 @@
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Bug fixes from pilot (frontend)</t>
+          <t>Bug fixes from pilot (backend)</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
         <is>
-          <t>1. Fix frontend issues from the pilot, most important first.</t>
+          <t>1. Fix backend issues from the pilot, most important first.</t>
         </is>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
-          <t>Frontend pilot issues closed</t>
+          <t>Backend pilot issues closed</t>
         </is>
       </c>
       <c r="H75" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>Backend developer</t>
         </is>
       </c>
       <c r="I75" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
+          <t>You (backend)</t>
         </is>
       </c>
       <c r="J75" s="19" t="n"/>
@@ -7228,58 +7235,53 @@
     <row r="76" ht="23.85" customHeight="1" s="14">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>S10-01</t>
+          <t>S9-04</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>W1–W2</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>Rollout</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>Connect all DATOMS sites to production; verify auto-linking</t>
+          <t>Bug fixes from pilot (frontend)</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>1. Point production at all DATOMS sites.
-2. Check every site links to the right project; clear the admin to-do list.</t>
+          <t>1. Fix frontend issues from the pilot, most important first.</t>
         </is>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
-          <t>All sites live</t>
+          <t>Frontend pilot issues closed</t>
         </is>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>Data / integration engineer</t>
+          <t>Frontend developer</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
-          <t>You (backend)</t>
-        </is>
-      </c>
-      <c r="J76" s="19" t="inlineStr">
-        <is>
-          <t>Innovo: many sites</t>
-        </is>
-      </c>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="n"/>
       <c r="K76" s="19" t="inlineStr">
         <is>
-          <t>S9-03</t>
+          <t>S9-02</t>
         </is>
       </c>
       <c r="L76" s="19" t="n"/>
@@ -7293,128 +7295,132 @@
       </c>
       <c r="O76" s="19" t="inlineStr">
         <is>
-          <t>Every DATOMS site visible with correct project</t>
+          <t>All pilot blockers fixed</t>
         </is>
       </c>
     </row>
     <row r="77" ht="23.85" customHeight="1" s="14">
       <c r="A77" s="19" t="inlineStr">
         <is>
+          <t>S10-01</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>Connect all DATOMS sites to production; verify auto-linking</t>
+        </is>
+      </c>
+      <c r="F77" s="19" t="inlineStr">
+        <is>
+          <t>1. Point production at all DATOMS sites.
+2. Check every site links to the right project; clear the admin to-do list.</t>
+        </is>
+      </c>
+      <c r="G77" s="19" t="inlineStr">
+        <is>
+          <t>All sites live</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="inlineStr">
+        <is>
+          <t>Data / integration engineer</t>
+        </is>
+      </c>
+      <c r="I77" s="19" t="inlineStr">
+        <is>
+          <t>You (backend)</t>
+        </is>
+      </c>
+      <c r="J77" s="19" t="inlineStr">
+        <is>
+          <t>Innovo: many sites</t>
+        </is>
+      </c>
+      <c r="K77" s="19" t="inlineStr">
+        <is>
+          <t>S9-03</t>
+        </is>
+      </c>
+      <c r="L77" s="19" t="n"/>
+      <c r="M77" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O77" s="19" t="inlineStr">
+        <is>
+          <t>Every DATOMS site visible with correct project</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="23.85" customHeight="1" s="14">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
           <t>S10-02</t>
         </is>
       </c>
-      <c r="B77" s="19" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="C77" s="19" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="D77" s="19" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
         <is>
           <t>Rollout</t>
         </is>
       </c>
-      <c r="E77" s="24" t="inlineStr">
+      <c r="E78" s="24" t="inlineStr">
         <is>
           <t>Production monitoring and cost review</t>
         </is>
       </c>
-      <c r="F77" s="19" t="inlineStr">
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>1. Set Azure cost alerts.
 2. Review first month's cost and performance.</t>
         </is>
       </c>
-      <c r="G77" s="19" t="inlineStr">
+      <c r="G78" s="19" t="inlineStr">
         <is>
           <t>Running costs under control</t>
         </is>
       </c>
-      <c r="H77" s="19" t="inlineStr">
+      <c r="H78" s="19" t="inlineStr">
         <is>
           <t>DevOps engineer</t>
         </is>
       </c>
-      <c r="I77" s="19" t="inlineStr">
+      <c r="I78" s="19" t="inlineStr">
         <is>
           <t>You (backend)</t>
         </is>
       </c>
-      <c r="J77" s="19" t="inlineStr">
+      <c r="J78" s="19" t="inlineStr">
         <is>
           <t>Risks: cost</t>
-        </is>
-      </c>
-      <c r="K77" s="19" t="n"/>
-      <c r="L77" s="19" t="n"/>
-      <c r="M77" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N77" s="25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="O77" s="19" t="inlineStr">
-        <is>
-          <t>Cost alerts set; first monthly review done</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" s="14">
-      <c r="A78" s="19" t="inlineStr">
-        <is>
-          <t>S10-03</t>
-        </is>
-      </c>
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C78" s="19" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="D78" s="19" t="inlineStr">
-        <is>
-          <t>Rollout</t>
-        </is>
-      </c>
-      <c r="E78" s="24" t="inlineStr">
-        <is>
-          <t>Onboarding sessions with site teams</t>
-        </is>
-      </c>
-      <c r="F78" s="19" t="inlineStr">
-        <is>
-          <t>1. Short session per site team.
-2. Name a champion per site.</t>
-        </is>
-      </c>
-      <c r="G78" s="19" t="inlineStr">
-        <is>
-          <t>Site teams using Nexus</t>
-        </is>
-      </c>
-      <c r="H78" s="19" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="I78" s="19" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="J78" s="19" t="inlineStr">
-        <is>
-          <t>Adoption</t>
         </is>
       </c>
       <c r="K78" s="19" t="n"/>
@@ -7429,14 +7435,14 @@
       </c>
       <c r="O78" s="19" t="inlineStr">
         <is>
-          <t>Each site has a champion trained</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="14">
+          <t>Cost alerts set; first monthly review done</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" s="14">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>S10-04</t>
+          <t>S10-03</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
@@ -7446,7 +7452,7 @@
       </c>
       <c r="C79" s="19" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1–W2</t>
         </is>
       </c>
       <c r="D79" s="19" t="inlineStr">
@@ -7456,18 +7462,18 @@
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Phase 2 backlog grooming (reporting feed, BIM, AI)</t>
+          <t>Onboarding sessions with site teams</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
         <is>
-          <t>1. List phase 2 items (reporting feed, BIM, AI).
-2. Estimate and order them.</t>
+          <t>1. Short session per site team.
+2. Name a champion per site.</t>
         </is>
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
-          <t>Phase 2 backlog ready</t>
+          <t>Site teams using Nexus</t>
         </is>
       </c>
       <c r="H79" s="19" t="inlineStr">
@@ -7482,13 +7488,13 @@
       </c>
       <c r="J79" s="19" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Adoption</t>
         </is>
       </c>
       <c r="K79" s="19" t="n"/>
       <c r="L79" s="19" t="n"/>
       <c r="M79" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79" s="25" t="inlineStr">
         <is>
@@ -7497,14 +7503,14 @@
       </c>
       <c r="O79" s="19" t="inlineStr">
         <is>
-          <t>Phase 2 backlog estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" s="14">
+          <t>Each site has a champion trained</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="14">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>S10-05</t>
+          <t>S10-04</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
@@ -7514,7 +7520,7 @@
       </c>
       <c r="C80" s="19" t="inlineStr">
         <is>
-          <t>W1–W2</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
@@ -7524,61 +7530,129 @@
       </c>
       <c r="E80" s="24" t="inlineStr">
         <is>
-          <t>UI fixes from rollout feedback</t>
+          <t>Phase 2 backlog grooming (reporting feed, BIM, AI)</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>1. Fix UI feedback from rollout, most important first.</t>
+          <t>1. List phase 2 items (reporting feed, BIM, AI).
+2. Estimate and order them.</t>
         </is>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
-          <t>Rollout feedback closed</t>
+          <t>Phase 2 backlog ready</t>
         </is>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>Frontend developer</t>
+          <t>Product owner</t>
         </is>
       </c>
       <c r="I80" s="19" t="inlineStr">
         <is>
-          <t>Colleague (frontend)</t>
-        </is>
-      </c>
-      <c r="J80" s="19" t="n"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>Future</t>
+        </is>
+      </c>
       <c r="K80" s="19" t="n"/>
       <c r="L80" s="19" t="n"/>
       <c r="M80" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O80" s="19" t="inlineStr">
+        <is>
+          <t>Phase 2 backlog estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" s="14">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>S10-05</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Rollout</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>UI fixes from rollout feedback</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>1. Fix UI feedback from rollout, most important first.</t>
+        </is>
+      </c>
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>Rollout feedback closed</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
+        <is>
+          <t>Frontend developer</t>
+        </is>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>Colleague (frontend)</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="n"/>
+      <c r="K81" s="19" t="n"/>
+      <c r="L81" s="19" t="n"/>
+      <c r="M81" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N80" s="25" t="inlineStr">
+      <c r="N81" s="25" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="O80" s="19" t="inlineStr">
+      <c r="O81" s="19" t="inlineStr">
         <is>
           <t>Feedback items closed</t>
         </is>
       </c>
     </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="L82" s="16" t="inlineStr">
+    <row r="82"/>
+    <row r="83">
+      <c r="L83" s="16" t="inlineStr">
         <is>
           <t>Total days</t>
         </is>
       </c>
-      <c r="M82" s="16">
-        <f>SUM(M2:M80)</f>
+      <c r="M83" s="16">
+        <f>SUM(M2:M81)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
-  <conditionalFormatting sqref="A2:O80">
+  <autoFilter ref="A1:O78"/>
+  <conditionalFormatting sqref="A2:O81">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="4" text="" percent="0" bottom="0">
       <formula>$N2="Blocked"</formula>
     </cfRule>
@@ -7587,7 +7661,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="N2:N81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7619,6 +7693,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="14">
       <c r="A3" s="26" t="inlineStr">
         <is>
@@ -7933,6 +8008,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="14">
       <c r="A3" s="26" t="inlineStr">
         <is>
